--- a/PV_ICE/baselines/SupportingMaterial/Manual Files/Inverter_Gallium_Calcs.xlsx
+++ b/PV_ICE/baselines/SupportingMaterial/Manual Files/Inverter_Gallium_Calcs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmirletz\Documents\GitHub\PV_ICE\PV_ICE\baselines\SupportingMaterial\Manual Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10AD4139-A07E-493C-B61C-73C7F0854806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898D25E6-5F9D-4382-A9CF-FCE690525C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28575" yWindow="1095" windowWidth="26715" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28590" yWindow="4395" windowWidth="24915" windowHeight="10680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="97">
   <si>
     <t>year</t>
   </si>
@@ -55,16 +55,10 @@
     <t>Chips per inverter [#/inverter type]</t>
   </si>
   <si>
-    <t>Inverter Type</t>
-  </si>
-  <si>
     <t>Source2</t>
   </si>
   <si>
     <t>Notes2</t>
-  </si>
-  <si>
-    <t>GaN FET/ 10 kW single phase</t>
   </si>
   <si>
     <t>GaN FET/ 1.6kW microinverter</t>
@@ -415,26 +409,82 @@
     <t>see google sheet for avg calc</t>
   </si>
   <si>
-    <t>Micro</t>
-  </si>
-  <si>
-    <t>String</t>
-  </si>
-  <si>
-    <t>Utility</t>
-  </si>
-  <si>
     <t>[g/FET]</t>
   </si>
   <si>
     <t>% GaN HEMT in PV application market</t>
+  </si>
+  <si>
+    <t>Silvana counted 6 in the circuit diagram</t>
+  </si>
+  <si>
+    <t>GaN FET/ 10 kW single phase with Battery</t>
+  </si>
+  <si>
+    <t>*Heather will go back and inventory all the GaN TI ref designs adding # of phases and Voltage</t>
+  </si>
+  <si>
+    <t>SELECTED AS REPRESENTATIVE DESIGN</t>
+  </si>
+  <si>
+    <t>MICRO</t>
+  </si>
+  <si>
+    <t>UTILITY</t>
+  </si>
+  <si>
+    <t>STRING</t>
+  </si>
+  <si>
+    <t># of Phases</t>
+  </si>
+  <si>
+    <t>500 V</t>
+  </si>
+  <si>
+    <t>600, 800, 1000 V</t>
+  </si>
+  <si>
+    <t>Voltages [V]</t>
+  </si>
+  <si>
+    <t>Inverter Description</t>
+  </si>
+  <si>
+    <t>60 Vdc, 240 Vac</t>
+  </si>
+  <si>
+    <t>*check for a material value</t>
+  </si>
+  <si>
+    <t>Micro [g/inverter]</t>
+  </si>
+  <si>
+    <t>String [g/inverter]</t>
+  </si>
+  <si>
+    <t>Utility [g/inverter]</t>
+  </si>
+  <si>
+    <t>https://www.ti.com/tool/TIDA-010949</t>
+  </si>
+  <si>
+    <t>80 V</t>
+  </si>
+  <si>
+    <t>600W solar power optimizer reference design based on GaN with wired and wireless communication</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <numFmts count="3">
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.000%"/>
+    <numFmt numFmtId="171" formatCode="0.000000000E+00"/>
+  </numFmts>
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -509,13 +559,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -613,7 +677,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -625,15 +689,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -643,6 +703,28 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -967,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V112"/>
+  <dimension ref="A1:Y112"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.81640625" bestFit="1" customWidth="1"/>
@@ -975,17 +1057,20 @@
     <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="1.453125" customWidth="1"/>
     <col min="7" max="7" width="15.81640625" customWidth="1"/>
-    <col min="8" max="8" width="36" customWidth="1"/>
-    <col min="11" max="11" width="1.08984375" customWidth="1"/>
-    <col min="12" max="12" width="12.08984375" customWidth="1"/>
-    <col min="13" max="13" width="4.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.08984375" customWidth="1"/>
-    <col min="15" max="15" width="16.90625" customWidth="1"/>
-    <col min="16" max="16" width="1.1796875" customWidth="1"/>
-    <col min="17" max="19" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.90625" customWidth="1"/>
-    <col min="21" max="22" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36" customWidth="1"/>
+    <col min="11" max="11" width="17" style="4" customWidth="1"/>
+    <col min="14" max="14" width="1.08984375" customWidth="1"/>
+    <col min="15" max="15" width="12.08984375" customWidth="1"/>
+    <col min="16" max="16" width="4.36328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.08984375" customWidth="1"/>
+    <col min="18" max="18" width="16.90625" customWidth="1"/>
+    <col min="19" max="19" width="1.1796875" customWidth="1"/>
+    <col min="20" max="22" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.90625" customWidth="1"/>
+    <col min="24" max="25" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="18.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
@@ -993,10 +1078,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>2</v>
@@ -1008,43 +1093,43 @@
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="T1" s="3" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
@@ -1122,57 +1207,62 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2005</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2006</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2007</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2008</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2009</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2010</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2011</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2012</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2013</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2014</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="G26" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2015</v>
       </c>
@@ -1180,16 +1270,16 @@
         <v>5.12</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E27" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2016</v>
       </c>
@@ -1198,297 +1288,261 @@
         <v>1E-4</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E28" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2017</v>
       </c>
-      <c r="L29" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="O29" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2018</v>
       </c>
-      <c r="L30" s="18">
-        <v>2.3529411764705885E-3</v>
-      </c>
-      <c r="M30" t="s">
+      <c r="O30" s="14">
+        <v>3.1809145129224651E-5</v>
+      </c>
+      <c r="P30" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>72</v>
+      </c>
+      <c r="R30" t="s">
         <v>73</v>
       </c>
-      <c r="N30" t="s">
-        <v>74</v>
-      </c>
-      <c r="O30" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q30">
-        <f>$B$37*$G$35*L30</f>
-        <v>7.9529411764705882E-7</v>
-      </c>
-      <c r="R30">
-        <f>$B$37*$G$34*L30</f>
-        <v>4.7717647058823531E-7</v>
-      </c>
-      <c r="S30">
-        <f>$B$37*$G$36*L30</f>
-        <v>1.5905882352941175E-7</v>
-      </c>
       <c r="T30">
-        <f>ROUND(Q30,6)</f>
-        <v>9.9999999999999995E-7</v>
+        <f>$B$37*$G$35*O30</f>
+        <v>1.0751491053677931E-8</v>
       </c>
       <c r="U30">
-        <f>ROUND(R30,7)</f>
-        <v>4.9999999999999998E-7</v>
+        <f>$B$37*$G$34*O30</f>
+        <v>6.4508946322067582E-9</v>
       </c>
       <c r="V30">
-        <f>ROUND(S30,7)</f>
-        <v>1.9999999999999999E-7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+        <f>$B$37*$G$36*O30</f>
+        <v>6.4508946322067582E-9</v>
+      </c>
+      <c r="W30" s="29"/>
+      <c r="X30" s="29"/>
+      <c r="Y30" s="29"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2019</v>
       </c>
-      <c r="L31" s="18">
-        <v>1.9138755980861245E-3</v>
-      </c>
-      <c r="M31" t="s">
+      <c r="O31" s="14">
+        <v>3.0434451799436964E-5</v>
+      </c>
+      <c r="P31" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>72</v>
+      </c>
+      <c r="R31" t="s">
         <v>73</v>
       </c>
-      <c r="N31" t="s">
-        <v>74</v>
-      </c>
-      <c r="O31" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q31">
-        <f t="shared" ref="Q31:Q40" si="0">$B$37*$G$35*L31</f>
-        <v>6.4688995215310997E-7</v>
-      </c>
-      <c r="R31">
-        <f t="shared" ref="R31:R40" si="1">$B$37*$G$34*L31</f>
-        <v>3.8813397129186598E-7</v>
-      </c>
-      <c r="S31">
-        <f t="shared" ref="S31:S40" si="2">$B$37*$G$36*L31</f>
-        <v>1.2937799043062199E-7</v>
-      </c>
       <c r="T31">
-        <f t="shared" ref="T31:T40" si="3">ROUND(Q31,6)</f>
-        <v>9.9999999999999995E-7</v>
+        <f t="shared" ref="T31:T40" si="0">$B$37*$G$35*O31</f>
+        <v>1.0286844708209693E-8</v>
       </c>
       <c r="U31">
-        <f>ROUND(R31,7)</f>
-        <v>3.9999999999999998E-7</v>
+        <f t="shared" ref="U31:U40" si="1">$B$37*$G$34*O31</f>
+        <v>6.1721068249258155E-9</v>
       </c>
       <c r="V31">
-        <f t="shared" ref="V31:V34" si="4">ROUND(S31,7)</f>
-        <v>9.9999999999999995E-8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+        <f t="shared" ref="V31:V40" si="2">$B$37*$G$36*O31</f>
+        <v>6.1721068249258155E-9</v>
+      </c>
+      <c r="W31" s="29"/>
+      <c r="X31" s="29"/>
+      <c r="Y31" s="29"/>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2020</v>
       </c>
-      <c r="L32" s="18">
-        <v>3.3018867924528299E-3</v>
-      </c>
-      <c r="M32" t="s">
+      <c r="O32" s="14">
+        <v>5.4192149880003095E-5</v>
+      </c>
+      <c r="P32" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>72</v>
+      </c>
+      <c r="R32" t="s">
         <v>73</v>
       </c>
-      <c r="N32" t="s">
-        <v>74</v>
-      </c>
-      <c r="O32" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q32">
+      <c r="T32">
         <f t="shared" si="0"/>
-        <v>1.1160377358490565E-6</v>
-      </c>
-      <c r="R32">
+        <v>1.8316946659441044E-8</v>
+      </c>
+      <c r="U32">
         <f t="shared" si="1"/>
-        <v>6.6962264150943376E-7</v>
-      </c>
-      <c r="S32">
+        <v>1.0990167995664626E-8</v>
+      </c>
+      <c r="V32">
         <f t="shared" si="2"/>
-        <v>2.2320754716981128E-7</v>
-      </c>
-      <c r="T32">
-        <f t="shared" si="3"/>
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="U32">
-        <f t="shared" ref="U31:U40" si="5">ROUND(R32,6)</f>
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="V32">
-        <f t="shared" si="4"/>
-        <v>1.9999999999999999E-7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
+        <v>1.0990167995664626E-8</v>
+      </c>
+      <c r="W32" s="29"/>
+      <c r="X32" s="29"/>
+      <c r="Y32" s="29"/>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2021</v>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="12">
         <v>0</v>
       </c>
-      <c r="H33" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="I33" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="L33" s="18">
-        <v>3.8194444444444448E-3</v>
-      </c>
-      <c r="M33" t="s">
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="K33" s="21"/>
+      <c r="L33" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="O33" s="14">
+        <v>8.058017727639001E-5</v>
+      </c>
+      <c r="P33" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>72</v>
+      </c>
+      <c r="R33" t="s">
         <v>73</v>
       </c>
-      <c r="N33" t="s">
-        <v>74</v>
-      </c>
-      <c r="O33" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q33">
+      <c r="T33">
         <f t="shared" si="0"/>
-        <v>1.2909722222222223E-6</v>
-      </c>
-      <c r="R33">
+        <v>2.7236099919419822E-8</v>
+      </c>
+      <c r="U33">
         <f t="shared" si="1"/>
-        <v>7.7458333333333326E-7</v>
-      </c>
-      <c r="S33">
+        <v>1.6341659951651891E-8</v>
+      </c>
+      <c r="V33">
         <f t="shared" si="2"/>
-        <v>2.5819444444444442E-7</v>
-      </c>
-      <c r="T33">
-        <f t="shared" si="3"/>
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="U33">
-        <f t="shared" si="5"/>
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="V33">
-        <f t="shared" si="4"/>
-        <v>2.9999999999999999E-7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
+        <v>1.6341659951651891E-8</v>
+      </c>
+      <c r="W33" s="29"/>
+      <c r="X33" s="29"/>
+      <c r="Y33" s="29"/>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2022</v>
       </c>
       <c r="G34">
         <v>6</v>
       </c>
-      <c r="H34" t="s">
-        <v>8</v>
+      <c r="H34">
+        <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>11</v>
-      </c>
-      <c r="L34" s="18">
-        <v>6.8459657701711489E-3</v>
-      </c>
-      <c r="M34" t="s">
+        <v>85</v>
+      </c>
+      <c r="J34" t="s">
+        <v>78</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="L34" t="s">
+        <v>9</v>
+      </c>
+      <c r="O34" s="14">
+        <v>1.9553072625698323E-4</v>
+      </c>
+      <c r="P34" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>72</v>
+      </c>
+      <c r="R34" t="s">
         <v>73</v>
       </c>
-      <c r="N34" t="s">
-        <v>74</v>
-      </c>
-      <c r="O34" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q34">
+      <c r="T34">
         <f t="shared" si="0"/>
-        <v>2.3139364303178481E-6</v>
-      </c>
-      <c r="R34">
+        <v>6.6089385474860326E-8</v>
+      </c>
+      <c r="U34">
         <f t="shared" si="1"/>
-        <v>1.3883618581907089E-6</v>
-      </c>
-      <c r="S34">
+        <v>3.9653631284916192E-8</v>
+      </c>
+      <c r="V34">
         <f t="shared" si="2"/>
-        <v>4.6278728606356959E-7</v>
-      </c>
-      <c r="T34">
-        <f t="shared" si="3"/>
-        <v>1.9999999999999999E-6</v>
-      </c>
-      <c r="U34">
-        <f t="shared" si="5"/>
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="V34">
-        <f t="shared" si="4"/>
-        <v>4.9999999999999998E-7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
+        <v>3.9653631284916192E-8</v>
+      </c>
+      <c r="W34" s="29"/>
+      <c r="X34" s="29"/>
+      <c r="Y34" s="29"/>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2023</v>
       </c>
       <c r="G35">
         <v>10</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
+        <v>89</v>
+      </c>
+      <c r="J35" t="s">
+        <v>7</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="L35" t="s">
         <v>9</v>
       </c>
-      <c r="I35" t="s">
-        <v>11</v>
-      </c>
-      <c r="L35" s="18">
-        <v>9.6078431372549032E-3</v>
-      </c>
-      <c r="M35" t="s">
+      <c r="O35" s="14">
+        <v>3.3690869086908695E-4</v>
+      </c>
+      <c r="P35" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>72</v>
+      </c>
+      <c r="R35" t="s">
         <v>73</v>
       </c>
-      <c r="N35" t="s">
-        <v>74</v>
-      </c>
-      <c r="O35" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q35">
+      <c r="T35">
         <f t="shared" si="0"/>
-        <v>3.2474509803921571E-6</v>
-      </c>
-      <c r="R35">
+        <v>1.1387513751375138E-7</v>
+      </c>
+      <c r="U35">
         <f t="shared" si="1"/>
-        <v>1.948470588235294E-6</v>
-      </c>
-      <c r="S35">
+        <v>6.8325082508250822E-8</v>
+      </c>
+      <c r="V35">
         <f t="shared" si="2"/>
-        <v>6.4949019607843133E-7</v>
-      </c>
-      <c r="T35">
-        <f t="shared" si="3"/>
-        <v>3.0000000000000001E-6</v>
-      </c>
-      <c r="U35">
-        <f t="shared" si="5"/>
-        <v>1.9999999999999999E-6</v>
-      </c>
-      <c r="V35">
-        <f t="shared" ref="V31:V40" si="6">ROUND(S35,6)</f>
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
+        <v>6.8325082508250822E-8</v>
+      </c>
+      <c r="W35" s="29"/>
+      <c r="X35" s="29"/>
+      <c r="Y35" s="29"/>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2024</v>
       </c>
@@ -1496,61 +1550,64 @@
         <v>3.3799999999999997E-2</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s">
         <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G36">
-        <v>2</v>
-      </c>
-      <c r="H36" t="s">
-        <v>10</v>
-      </c>
-      <c r="I36" t="s">
-        <v>11</v>
-      </c>
-      <c r="L36" s="18">
-        <v>1.2673611111111111E-2</v>
+        <v>6</v>
+      </c>
+      <c r="H36">
+        <v>3</v>
+      </c>
+      <c r="I36" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="J36" t="s">
+        <v>8</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="L36" t="s">
+        <v>9</v>
       </c>
       <c r="M36" t="s">
+        <v>77</v>
+      </c>
+      <c r="O36" s="14">
+        <v>4.8114948589506984E-4</v>
+      </c>
+      <c r="P36" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>72</v>
+      </c>
+      <c r="R36" t="s">
         <v>73</v>
       </c>
-      <c r="N36" t="s">
-        <v>74</v>
-      </c>
-      <c r="O36" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q36">
+      <c r="T36">
         <f t="shared" si="0"/>
-        <v>4.2836805555555554E-6</v>
-      </c>
-      <c r="R36">
+        <v>1.6262852623253359E-7</v>
+      </c>
+      <c r="U36">
         <f t="shared" si="1"/>
-        <v>2.5702083333333329E-6</v>
-      </c>
-      <c r="S36">
+        <v>9.7577115739520148E-8</v>
+      </c>
+      <c r="V36">
         <f t="shared" si="2"/>
-        <v>8.5673611111111104E-7</v>
-      </c>
-      <c r="T36">
-        <f t="shared" si="3"/>
-        <v>3.9999999999999998E-6</v>
-      </c>
-      <c r="U36">
-        <f t="shared" si="5"/>
-        <v>3.0000000000000001E-6</v>
-      </c>
-      <c r="V36">
-        <f t="shared" si="6"/>
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.35">
+        <v>9.7577115739520148E-8</v>
+      </c>
+      <c r="W36" s="29"/>
+      <c r="X36" s="29"/>
+      <c r="Y36" s="29"/>
+    </row>
+    <row r="37" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>2025</v>
       </c>
@@ -1559,204 +1616,181 @@
         <v>3.3799999999999995E-5</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L37" s="19">
-        <v>1.6773162939297124E-2</v>
-      </c>
-      <c r="M37" t="s">
+        <v>75</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K37" s="22"/>
+      <c r="M37" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="O37" s="15">
+        <v>6.5715358618099887E-4</v>
+      </c>
+      <c r="P37" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>72</v>
+      </c>
+      <c r="R37" t="s">
         <v>73</v>
       </c>
-      <c r="N37" t="s">
-        <v>74</v>
-      </c>
-      <c r="O37" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q37">
+      <c r="T37">
         <f t="shared" si="0"/>
-        <v>5.6693290734824276E-6</v>
-      </c>
-      <c r="R37">
+        <v>2.2211791212917761E-7</v>
+      </c>
+      <c r="U37">
         <f t="shared" si="1"/>
-        <v>3.4015974440894562E-6</v>
-      </c>
-      <c r="S37">
+        <v>1.3327074727750656E-7</v>
+      </c>
+      <c r="V37">
         <f t="shared" si="2"/>
-        <v>1.1338658146964855E-6</v>
-      </c>
-      <c r="T37">
-        <f t="shared" si="3"/>
-        <v>6.0000000000000002E-6</v>
-      </c>
-      <c r="U37">
-        <f t="shared" si="5"/>
-        <v>3.0000000000000001E-6</v>
-      </c>
-      <c r="V37">
-        <f t="shared" si="6"/>
-        <v>9.9999999999999995E-7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
+        <v>1.3327074727750656E-7</v>
+      </c>
+      <c r="W37" s="29"/>
+      <c r="X37" s="29"/>
+      <c r="Y37" s="29"/>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2026</v>
       </c>
-      <c r="L38" s="18">
-        <v>2.2962962962962963E-2</v>
-      </c>
-      <c r="M38" t="s">
+      <c r="O38" s="14">
+        <v>9.1846409101682864E-4</v>
+      </c>
+      <c r="P38" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>72</v>
+      </c>
+      <c r="R38" t="s">
         <v>73</v>
       </c>
-      <c r="N38" t="s">
-        <v>74</v>
-      </c>
-      <c r="O38" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q38">
+      <c r="T38">
         <f t="shared" si="0"/>
-        <v>7.7614814814814808E-6</v>
-      </c>
-      <c r="R38">
+        <v>3.1044086276368805E-7</v>
+      </c>
+      <c r="U38">
         <f t="shared" si="1"/>
-        <v>4.656888888888888E-6</v>
-      </c>
-      <c r="S38">
+        <v>1.8626451765821281E-7</v>
+      </c>
+      <c r="V38">
         <f t="shared" si="2"/>
-        <v>1.552296296296296E-6</v>
-      </c>
-      <c r="T38">
-        <f t="shared" si="3"/>
-        <v>7.9999999999999996E-6</v>
-      </c>
-      <c r="U38">
-        <f t="shared" si="5"/>
-        <v>5.0000000000000004E-6</v>
-      </c>
-      <c r="V38">
-        <f t="shared" si="6"/>
-        <v>1.9999999999999999E-6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
+        <v>1.8626451765821281E-7</v>
+      </c>
+      <c r="W38" s="29"/>
+      <c r="X38" s="29"/>
+      <c r="Y38" s="29"/>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2027</v>
       </c>
-      <c r="L39" s="18">
-        <v>2.524271844660194E-2</v>
-      </c>
-      <c r="M39" t="s">
+      <c r="O39" s="14">
+        <v>1.028306683993446E-3</v>
+      </c>
+      <c r="P39" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>72</v>
+      </c>
+      <c r="R39" t="s">
         <v>73</v>
       </c>
-      <c r="N39" t="s">
-        <v>74</v>
-      </c>
-      <c r="O39" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q39">
+      <c r="T39">
         <f t="shared" si="0"/>
-        <v>8.532038834951455E-6</v>
-      </c>
-      <c r="R39">
+        <v>3.4756765918978473E-7</v>
+      </c>
+      <c r="U39">
         <f t="shared" si="1"/>
-        <v>5.1192233009708728E-6</v>
-      </c>
-      <c r="S39">
+        <v>2.085405955138708E-7</v>
+      </c>
+      <c r="V39">
         <f t="shared" si="2"/>
-        <v>1.7064077669902909E-6</v>
-      </c>
-      <c r="T39">
-        <f t="shared" si="3"/>
-        <v>9.0000000000000002E-6</v>
-      </c>
-      <c r="U39">
-        <f t="shared" si="5"/>
-        <v>5.0000000000000004E-6</v>
-      </c>
-      <c r="V39">
-        <f t="shared" si="6"/>
-        <v>1.9999999999999999E-6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
+        <v>2.085405955138708E-7</v>
+      </c>
+      <c r="W39" s="29"/>
+      <c r="X39" s="29"/>
+      <c r="Y39" s="29"/>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2028</v>
       </c>
-      <c r="L40" s="20">
-        <v>2.8853754940711459E-2</v>
-      </c>
-      <c r="M40" t="s">
+      <c r="O40" s="16">
+        <v>1.1831442463533224E-3</v>
+      </c>
+      <c r="P40" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>72</v>
+      </c>
+      <c r="R40" t="s">
         <v>73</v>
       </c>
-      <c r="N40" t="s">
-        <v>74</v>
-      </c>
-      <c r="O40" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q40">
+      <c r="T40">
         <f t="shared" si="0"/>
-        <v>9.7525691699604717E-6</v>
-      </c>
-      <c r="R40">
+        <v>3.9990275526742293E-7</v>
+      </c>
+      <c r="U40">
         <f t="shared" si="1"/>
-        <v>5.8515415019762829E-6</v>
-      </c>
-      <c r="S40">
+        <v>2.3994165316045375E-7</v>
+      </c>
+      <c r="V40">
         <f t="shared" si="2"/>
-        <v>1.9505138339920944E-6</v>
-      </c>
-      <c r="T40">
-        <f t="shared" si="3"/>
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="U40">
-        <f t="shared" si="5"/>
-        <v>6.0000000000000002E-6</v>
-      </c>
-      <c r="V40">
-        <f t="shared" si="6"/>
-        <v>1.9999999999999999E-6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.35">
+        <v>2.3994165316045375E-7</v>
+      </c>
+      <c r="W40" s="29"/>
+      <c r="X40" s="29"/>
+      <c r="Y40" s="29"/>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2029</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2030</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2031</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2032</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2033</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2034</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2035</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2036</v>
       </c>
@@ -2084,9 +2118,10 @@
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="I33" r:id="rId1" display="https://doi.org/10.1016/j.resconrec.2023.107391" xr:uid="{C91B04C4-6F06-46FC-95C3-9BE3E8D63B79}"/>
+    <hyperlink ref="L33" r:id="rId1" display="https://doi.org/10.1016/j.resconrec.2023.107391" xr:uid="{C91B04C4-6F06-46FC-95C3-9BE3E8D63B79}"/>
     <hyperlink ref="D27" r:id="rId2" display="https://doi.org/10.1016/j.resconrec.2023.107391" xr:uid="{46E41433-83E9-41D0-81BF-194345B4E180}"/>
     <hyperlink ref="D28" r:id="rId3" display="https://doi.org/10.1016/j.resconrec.2023.107391" xr:uid="{834D0FB7-3EFD-43D3-9B68-EB35F321DE1A}"/>
+    <hyperlink ref="M37" r:id="rId4" xr:uid="{7B120840-CD9C-400D-9838-2232DE726815}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2094,58 +2129,61 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B730B5FD-02A7-4220-AE14-32AAECAEAC50}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="5.81640625" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="9.36328125" customWidth="1"/>
     <col min="5" max="5" width="14.7265625" customWidth="1"/>
     <col min="6" max="6" width="11.26953125" customWidth="1"/>
-    <col min="7" max="7" width="4.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.08984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B2" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B2" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" t="s">
         <v>56</v>
       </c>
-      <c r="C3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>58</v>
       </c>
-      <c r="E3" t="s">
-        <v>60</v>
-      </c>
       <c r="F3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" t="s">
         <v>56</v>
       </c>
-      <c r="G3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="J3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2018</v>
       </c>
@@ -2162,20 +2200,20 @@
         <f>SUM(B4:D4)</f>
         <v>16.099999999999998</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <f>B4/$E4</f>
         <v>2.4844720496894415E-2</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="25">
         <f t="shared" ref="G4:H4" si="0">C4/$E4</f>
         <v>0</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="6">
         <f t="shared" si="0"/>
         <v>0.97515527950310565</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2019</v>
       </c>
@@ -2189,23 +2227,23 @@
         <v>16.5</v>
       </c>
       <c r="E5">
-        <f t="shared" ref="E5:E15" si="1">SUM(B5:D5)</f>
+        <f t="shared" ref="E5:E14" si="1">SUM(B5:D5)</f>
         <v>17.11</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="7">
         <f t="shared" ref="F5:F14" si="2">B5/$E5</f>
         <v>3.5067212156633547E-2</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="26">
         <f t="shared" ref="G5:G14" si="3">C5/$E5</f>
         <v>5.8445353594389253E-4</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="8">
         <f t="shared" ref="H5:H14" si="4">D5/$E5</f>
         <v>0.96434833430742262</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2020</v>
       </c>
@@ -2222,20 +2260,20 @@
         <f t="shared" si="1"/>
         <v>17.22</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="7">
         <f t="shared" si="2"/>
         <v>4.065040650406504E-2</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="26">
         <f t="shared" si="3"/>
         <v>1.1614401858304297E-3</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="8">
         <f t="shared" si="4"/>
         <v>0.95818815331010454</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -2252,20 +2290,20 @@
         <f t="shared" si="1"/>
         <v>19.400000000000002</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="7">
         <f t="shared" si="2"/>
         <v>6.1855670103092772E-2</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="26">
         <f t="shared" si="3"/>
         <v>5.1546391752577319E-3</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="8">
         <f t="shared" si="4"/>
         <v>0.9329896907216495</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2022</v>
       </c>
@@ -2282,20 +2320,20 @@
         <f t="shared" si="1"/>
         <v>21.3</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="7">
         <f t="shared" si="2"/>
         <v>8.9201877934272297E-2</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="26">
         <f t="shared" si="3"/>
         <v>4.6948356807511738E-3</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="8">
         <f t="shared" si="4"/>
         <v>0.9061032863849765</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -2312,20 +2350,20 @@
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="7">
         <f t="shared" si="2"/>
         <v>0.12608695652173912</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="26">
         <f t="shared" si="3"/>
         <v>4.3478260869565218E-3</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="8">
         <f t="shared" si="4"/>
         <v>0.86956521739130432</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -2342,20 +2380,20 @@
         <f t="shared" si="1"/>
         <v>25.2</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="7">
         <f t="shared" si="2"/>
         <v>0.15873015873015872</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="26">
         <f t="shared" si="3"/>
         <v>7.9365079365079378E-3</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="8">
         <f t="shared" si="4"/>
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2025</v>
       </c>
@@ -2372,20 +2410,20 @@
         <f t="shared" si="1"/>
         <v>27.5</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="7">
         <f t="shared" si="2"/>
         <v>0.18909090909090909</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="26">
         <f t="shared" si="3"/>
         <v>1.0909090909090908E-2</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="8">
         <f t="shared" si="4"/>
         <v>0.8</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2026</v>
       </c>
@@ -2402,20 +2440,20 @@
         <f t="shared" si="1"/>
         <v>29.9</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="7">
         <f t="shared" si="2"/>
         <v>0.21404682274247494</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="26">
         <f t="shared" si="3"/>
         <v>1.6722408026755852E-2</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="8">
         <f t="shared" si="4"/>
         <v>0.76923076923076927</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2027</v>
       </c>
@@ -2432,20 +2470,20 @@
         <f t="shared" si="1"/>
         <v>32.200000000000003</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="7">
         <f t="shared" si="2"/>
         <v>0.24223602484472048</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="26">
         <f t="shared" si="3"/>
         <v>2.1739130434782605E-2</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="8">
         <f t="shared" si="4"/>
         <v>0.73602484472049678</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2028</v>
       </c>
@@ -2462,73 +2500,73 @@
         <f t="shared" si="1"/>
         <v>34.4</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="9">
         <f t="shared" si="2"/>
         <v>0.27325581395348841</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="27">
         <f t="shared" si="3"/>
         <v>2.9069767441860465E-2</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="10">
         <f t="shared" si="4"/>
         <v>0.69767441860465118</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="C15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" t="s">
         <v>64</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>66</v>
       </c>
       <c r="F19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2018</v>
       </c>
-      <c r="B20" s="5">
-        <f>C20/E20</f>
-        <v>2.3529411764705885E-3</v>
-      </c>
-      <c r="C20" s="15">
+      <c r="B20" s="28">
+        <f>C20/F20</f>
+        <v>3.1809145129224651E-5</v>
+      </c>
+      <c r="C20" s="11">
         <v>0.4</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="11">
         <v>170</v>
       </c>
       <c r="F20">
@@ -2539,17 +2577,17 @@
       <c r="A21">
         <v>2019</v>
       </c>
-      <c r="B21" s="5">
-        <f t="shared" ref="B21:B30" si="5">C21/E21</f>
-        <v>1.9138755980861245E-3</v>
-      </c>
-      <c r="C21" s="15">
+      <c r="B21" s="28">
+        <f t="shared" ref="B21:B30" si="5">C21/F21</f>
+        <v>3.0434451799436964E-5</v>
+      </c>
+      <c r="C21" s="11">
         <v>0.4</v>
       </c>
       <c r="D21">
         <v>9</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="11">
         <v>209</v>
       </c>
       <c r="F21">
@@ -2560,17 +2598,17 @@
       <c r="A22">
         <v>2020</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="28">
         <f t="shared" si="5"/>
-        <v>3.3018867924528299E-3</v>
-      </c>
-      <c r="C22" s="15">
+        <v>5.4192149880003095E-5</v>
+      </c>
+      <c r="C22" s="11">
         <v>0.7</v>
       </c>
       <c r="D22">
         <v>24</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="11">
         <v>212</v>
       </c>
       <c r="F22">
@@ -2581,17 +2619,17 @@
       <c r="A23">
         <v>2021</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="28">
         <f t="shared" si="5"/>
-        <v>3.8194444444444448E-3</v>
-      </c>
-      <c r="C23" s="15">
+        <v>8.058017727639001E-5</v>
+      </c>
+      <c r="C23" s="11">
         <v>1.1000000000000001</v>
       </c>
       <c r="D23">
         <v>66</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="11">
         <v>288</v>
       </c>
       <c r="F23">
@@ -2602,17 +2640,17 @@
       <c r="A24">
         <v>2022</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="28">
         <f t="shared" si="5"/>
-        <v>6.8459657701711489E-3</v>
-      </c>
-      <c r="C24" s="15">
+        <v>1.9553072625698323E-4</v>
+      </c>
+      <c r="C24" s="11">
         <v>2.8</v>
       </c>
       <c r="D24">
         <v>93</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="11">
         <v>409</v>
       </c>
       <c r="F24">
@@ -2623,17 +2661,17 @@
       <c r="A25">
         <v>2023</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="28">
         <f t="shared" si="5"/>
-        <v>9.6078431372549032E-3</v>
-      </c>
-      <c r="C25" s="15">
+        <v>3.3690869086908695E-4</v>
+      </c>
+      <c r="C25" s="11">
         <v>4.9000000000000004</v>
       </c>
       <c r="D25">
         <v>148</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="11">
         <v>510</v>
       </c>
       <c r="F25">
@@ -2644,17 +2682,17 @@
       <c r="A26">
         <v>2024</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="28">
         <f t="shared" si="5"/>
-        <v>1.2673611111111111E-2</v>
-      </c>
-      <c r="C26" s="15">
+        <v>4.8114948589506984E-4</v>
+      </c>
+      <c r="C26" s="11">
         <v>7.3</v>
       </c>
       <c r="D26">
         <v>183</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="11">
         <v>576</v>
       </c>
       <c r="F26">
@@ -2665,17 +2703,17 @@
       <c r="A27">
         <v>2025</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="28">
         <f t="shared" si="5"/>
-        <v>1.6773162939297124E-2</v>
-      </c>
-      <c r="C27" s="15">
+        <v>6.5715358618099887E-4</v>
+      </c>
+      <c r="C27" s="11">
         <v>10.5</v>
       </c>
       <c r="D27">
         <v>295</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="11">
         <v>626</v>
       </c>
       <c r="F27">
@@ -2686,17 +2724,17 @@
       <c r="A28">
         <v>2026</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="28">
         <f t="shared" si="5"/>
-        <v>2.2962962962962963E-2</v>
-      </c>
-      <c r="C28" s="15">
+        <v>9.1846409101682864E-4</v>
+      </c>
+      <c r="C28" s="11">
         <v>15.5</v>
       </c>
       <c r="D28">
         <v>482</v>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="11">
         <v>675</v>
       </c>
       <c r="F28">
@@ -2707,17 +2745,17 @@
       <c r="A29">
         <v>2027</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="28">
         <f t="shared" si="5"/>
-        <v>2.524271844660194E-2</v>
-      </c>
-      <c r="C29" s="15">
+        <v>1.028306683993446E-3</v>
+      </c>
+      <c r="C29" s="11">
         <v>18.2</v>
       </c>
       <c r="D29">
         <v>691</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="11">
         <v>721</v>
       </c>
       <c r="F29">
@@ -2728,17 +2766,17 @@
       <c r="A30">
         <v>2028</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="28">
         <f t="shared" si="5"/>
-        <v>2.8853754940711459E-2</v>
-      </c>
-      <c r="C30" s="15">
+        <v>1.1831442463533224E-3</v>
+      </c>
+      <c r="C30" s="11">
         <v>21.9</v>
       </c>
       <c r="D30">
         <v>991</v>
       </c>
-      <c r="E30" s="15">
+      <c r="E30" s="11">
         <v>759</v>
       </c>
       <c r="F30">
@@ -2761,78 +2799,78 @@
   <sheetData>
     <row r="1" spans="1:23" ht="17.5" x14ac:dyDescent="0.45">
       <c r="B1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="J1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N1" t="s">
+        <v>46</v>
+      </c>
+      <c r="R1" t="s">
         <v>48</v>
       </c>
-      <c r="R1" t="s">
-        <v>50</v>
-      </c>
       <c r="V1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
       <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
       <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>24</v>
-      </c>
       <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" t="s">
         <v>22</v>
       </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" t="s">
-        <v>24</v>
-      </c>
       <c r="Q2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" t="s">
         <v>22</v>
       </c>
-      <c r="R2" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2" t="s">
-        <v>24</v>
-      </c>
       <c r="U2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W2" t="s">
         <v>22</v>
-      </c>
-      <c r="V2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.35">
@@ -2840,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>0.30393992465576336</v>
@@ -2849,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G3">
         <v>0.90542979856308781</v>
@@ -2858,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K3">
         <v>0.56331411719800495</v>
@@ -2867,7 +2905,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O3">
         <v>0.31924702365464647</v>
@@ -2876,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="R3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="S3">
         <v>0.36234318344008598</v>
@@ -2885,7 +2923,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="W3">
         <v>0.91452134589285305</v>
@@ -2896,7 +2934,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4">
         <v>0.18852060065724716</v>
@@ -2905,7 +2943,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G4">
         <v>4.1520674290600239E-2</v>
@@ -2914,7 +2952,7 @@
         <v>2</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K4">
         <v>0.11678568072225042</v>
@@ -2923,7 +2961,7 @@
         <v>2</v>
       </c>
       <c r="N4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O4">
         <v>0.23689856627905867</v>
@@ -2932,7 +2970,7 @@
         <v>2</v>
       </c>
       <c r="R4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="S4">
         <v>0.24172749055100812</v>
@@ -2941,7 +2979,7 @@
         <v>2</v>
       </c>
       <c r="V4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="W4">
         <v>4.8863343914320068E-2</v>
@@ -2952,7 +2990,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5">
         <v>0.11614030403526776</v>
@@ -2961,7 +2999,7 @@
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G5">
         <v>3.0331786784455011E-2</v>
@@ -2970,7 +3008,7 @@
         <v>3</v>
       </c>
       <c r="J5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K5">
         <v>0.10788002212338918</v>
@@ -2979,7 +3017,7 @@
         <v>3</v>
       </c>
       <c r="N5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O5">
         <v>0.21584267751001046</v>
@@ -2988,7 +3026,7 @@
         <v>3</v>
       </c>
       <c r="R5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S5">
         <v>0.1489190260820292</v>
@@ -2997,7 +3035,7 @@
         <v>3</v>
       </c>
       <c r="V5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="W5">
         <v>2.0395134851194461E-2</v>
@@ -3008,7 +3046,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C6">
         <v>0.10523141119195512</v>
@@ -3017,7 +3055,7 @@
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G6">
         <v>2.2717740361856986E-2</v>
@@ -3026,7 +3064,7 @@
         <v>4</v>
       </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K6">
         <v>9.7508823924634447E-2</v>
@@ -3035,7 +3073,7 @@
         <v>4</v>
       </c>
       <c r="N6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O6">
         <v>0.10328875184219956</v>
@@ -3044,19 +3082,19 @@
         <v>4</v>
       </c>
       <c r="R6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="S6">
         <v>0.13493127470361002</v>
       </c>
       <c r="U6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="W6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
@@ -3064,25 +3102,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>7.2380296621979381E-2</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I7">
         <v>5</v>
       </c>
       <c r="J7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K7">
         <v>8.3074750800168254E-2</v>
@@ -3091,7 +3129,7 @@
         <v>5</v>
       </c>
       <c r="N7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O7">
         <v>5.0258088334766339E-2</v>
@@ -3100,19 +3138,19 @@
         <v>5</v>
       </c>
       <c r="R7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="S7">
         <v>6.1163171426547702E-2</v>
       </c>
       <c r="U7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="W7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.35">
@@ -3120,25 +3158,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>6.3315982871402013E-2</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I8">
         <v>6</v>
       </c>
       <c r="J8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K8">
         <v>3.1436605231552818E-2</v>
@@ -3147,7 +3185,7 @@
         <v>6</v>
       </c>
       <c r="N8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O8">
         <v>4.1308401327102409E-2</v>
@@ -3156,19 +3194,19 @@
         <v>6</v>
       </c>
       <c r="R8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S8">
         <v>2.5438294849965772E-2</v>
       </c>
       <c r="U8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="W8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.35">
@@ -3176,34 +3214,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C9">
         <v>5.3662117291731336E-2</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M9">
         <v>7</v>
       </c>
       <c r="N9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O9">
         <v>2.8239042857085037E-2</v>
@@ -3212,19 +3250,19 @@
         <v>7</v>
       </c>
       <c r="R9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S9">
         <v>2.5263049067487095E-2</v>
       </c>
       <c r="U9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="W9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
@@ -3232,55 +3270,55 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10">
         <v>3.1581866961590314E-2</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="W10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
@@ -3288,55 +3326,55 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>1.983904525662443E-2</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="W11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
@@ -3344,258 +3382,258 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12">
         <v>1.9702373005982925E-2</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="W12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="W13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="W14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="U15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="W15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C16">
         <v>2.5686077450456257E-2</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="S16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="V16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="W16">
         <v>1.6220175341632337E-2</v>
@@ -3603,37 +3641,37 @@
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C17">
         <v>48217.54210579193</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G17">
         <v>3371.8142200714274</v>
       </c>
       <c r="I17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K17">
         <v>470.9481475798874</v>
       </c>
       <c r="M17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O17">
         <v>4769.973992450834</v>
       </c>
       <c r="Q17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="S17">
         <v>37604.328656536789</v>
       </c>
       <c r="U17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W17">
         <v>2000.4770891529802</v>
@@ -3645,15 +3683,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E1D7978D1E43DE4EA43DBD7340A406DC" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d2a0579b8367a5d14f15657bceede69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d382aed9-cc96-421a-b6d1-bad087b40ea5" xmlns:ns3="3c3bb480-5c86-45a4-be90-daa3829a93c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6184784662eaf13c68ab2ee7ade41035" ns2:_="" ns3:_="">
     <xsd:import namespace="d382aed9-cc96-421a-b6d1-bad087b40ea5"/>
@@ -3896,6 +3925,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3909,14 +3947,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D15763B-BC3F-44A0-B84D-0D65F1925A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A8357D9-61C4-4864-BD66-2D2D973EC6D9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3931,6 +3961,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D15763B-BC3F-44A0-B84D-0D65F1925A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/PV_ICE/baselines/SupportingMaterial/Manual Files/Inverter_Gallium_Calcs.xlsx
+++ b/PV_ICE/baselines/SupportingMaterial/Manual Files/Inverter_Gallium_Calcs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmirletz\Documents\GitHub\PV_ICE\PV_ICE\baselines\SupportingMaterial\Manual Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898D25E6-5F9D-4382-A9CF-FCE690525C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E445B2F-4993-4A8B-AC54-1709977C92B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28590" yWindow="4395" windowWidth="24915" windowHeight="10680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="163">
   <si>
     <t>year</t>
   </si>
@@ -474,15 +474,213 @@
   <si>
     <t>600W solar power optimizer reference design based on GaN with wired and wireless communication</t>
   </si>
+  <si>
+    <t>TI reference design 010938</t>
+  </si>
+  <si>
+    <t>TI reference design 010933</t>
+  </si>
+  <si>
+    <t>US market shares by product type shipments full-year  2022</t>
+  </si>
+  <si>
+    <t>* Estimate</t>
+  </si>
+  <si>
+    <t>United States PV inverter market share by shipments (MWac)</t>
+  </si>
+  <si>
+    <t>US MLPE Market Share by shipments (MWac)</t>
+  </si>
+  <si>
+    <t>US Single-Phase String Market Share by shipments (MWac)</t>
+  </si>
+  <si>
+    <t>US Three-Phase String Market Share by shipments (MWac)</t>
+  </si>
+  <si>
+    <t>US Central inverter market share by shipments (MWac)</t>
+  </si>
+  <si>
+    <t>US Storage Hybrid Market Share by shipments (MWac)</t>
+  </si>
+  <si>
+    <t>Sungrow</t>
+  </si>
+  <si>
+    <t>Enphase Energy</t>
+  </si>
+  <si>
+    <t>SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t>Tigo</t>
+  </si>
+  <si>
+    <t>Ampt</t>
+  </si>
+  <si>
+    <t>General Electric</t>
+  </si>
+  <si>
+    <t>Fimer</t>
+  </si>
+  <si>
+    <t>2022 PV inverter shipments (MWac)</t>
+  </si>
+  <si>
+    <t>US market shares by product type shipments full-year  2021</t>
+  </si>
+  <si>
+    <t>SolarEdge Technologies*</t>
+  </si>
+  <si>
+    <t>Ginlong Solis*</t>
+  </si>
+  <si>
+    <t>2021 PV inverter shipments (MWac)</t>
+  </si>
+  <si>
+    <t>US market shares by product type shipments full-year  2020</t>
+  </si>
+  <si>
+    <t>Delta Energy Systems*</t>
+  </si>
+  <si>
+    <t>SMA*</t>
+  </si>
+  <si>
+    <t>APsystems</t>
+  </si>
+  <si>
+    <t>Yaskawa-Solectria Solar</t>
+  </si>
+  <si>
+    <t>Fronius*</t>
+  </si>
+  <si>
+    <t>Kaco New Energy</t>
+  </si>
+  <si>
+    <t>2020 PV inverter shipments (MWac)</t>
+  </si>
+  <si>
+    <t>US market shares by product type shipments full-year  2019</t>
+  </si>
+  <si>
+    <t>Delta*</t>
+  </si>
+  <si>
+    <t>Tabuchi*</t>
+  </si>
+  <si>
+    <t>KSTAR*</t>
+  </si>
+  <si>
+    <t>Schneider*</t>
+  </si>
+  <si>
+    <t>Huawei</t>
+  </si>
+  <si>
+    <t>2019 PV inverter shipments (MWac)</t>
+  </si>
+  <si>
+    <t>*Estimate</t>
+  </si>
+  <si>
+    <t>ABB*</t>
+  </si>
+  <si>
+    <t>KACO New Energy*</t>
+  </si>
+  <si>
+    <t>General Electric*</t>
+  </si>
+  <si>
+    <t>US market shares by product type shipments full-year  2018</t>
+  </si>
+  <si>
+    <t>Sunpower</t>
+  </si>
+  <si>
+    <t>APSystems</t>
+  </si>
+  <si>
+    <t>Schneider Electric*</t>
+  </si>
+  <si>
+    <t>2018 shipments (MWac)</t>
+  </si>
+  <si>
+    <t>SunPower</t>
+  </si>
+  <si>
+    <t>Ginlong-Solis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US market shares by product type shipments 2017 </t>
+  </si>
+  <si>
+    <t>2017 shipments (MWac)</t>
+  </si>
+  <si>
+    <t>Tigo Energy*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US market shares by product type shipments 2016 </t>
+  </si>
+  <si>
+    <t>ABB</t>
+  </si>
+  <si>
+    <t>Tigo Energy</t>
+  </si>
+  <si>
+    <t>2016 shipments (MWac)</t>
+  </si>
+  <si>
+    <t>US market shares by product type shipments 2015</t>
+  </si>
+  <si>
+    <t>2015 shipments (MWac)</t>
+  </si>
+  <si>
+    <t>Microinverter</t>
+  </si>
+  <si>
+    <t>Single-phase String</t>
+  </si>
+  <si>
+    <t>Three-phase String</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>Mwac</t>
+  </si>
+  <si>
+    <t>Total PV inverter shipments</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>TI reference design 010949</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0.000%"/>
-    <numFmt numFmtId="171" formatCode="0.000000000E+00"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.000%"/>
+    <numFmt numFmtId="166" formatCode="0.000000000E+00"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -677,7 +875,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -703,11 +901,8 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -717,14 +912,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1060,7 +1261,9 @@
     <col min="8" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.26953125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="36" customWidth="1"/>
-    <col min="11" max="11" width="17" style="4" customWidth="1"/>
+    <col min="11" max="11" width="16.453125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="20.36328125" customWidth="1"/>
+    <col min="13" max="13" width="14.36328125" customWidth="1"/>
     <col min="14" max="14" width="1.08984375" customWidth="1"/>
     <col min="15" max="15" width="12.08984375" customWidth="1"/>
     <col min="16" max="16" width="4.36328125" bestFit="1" customWidth="1"/>
@@ -1068,7 +1271,7 @@
     <col min="18" max="18" width="16.90625" customWidth="1"/>
     <col min="19" max="19" width="1.1796875" customWidth="1"/>
     <col min="20" max="22" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.90625" customWidth="1"/>
+    <col min="23" max="23" width="2.08984375" customWidth="1"/>
     <col min="24" max="25" width="15.453125" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="18.1796875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1101,7 +1304,7 @@
       <c r="J1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="K1" s="19" t="s">
         <v>80</v>
       </c>
       <c r="L1" s="3" t="s">
@@ -1256,11 +1459,11 @@
       <c r="A26">
         <v>2014</v>
       </c>
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27">
@@ -1333,9 +1536,9 @@
         <f>$B$37*$G$36*O30</f>
         <v>6.4508946322067582E-9</v>
       </c>
-      <c r="W30" s="29"/>
-      <c r="X30" s="29"/>
-      <c r="Y30" s="29"/>
+      <c r="W30" s="27"/>
+      <c r="X30" s="27"/>
+      <c r="Y30" s="27"/>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31">
@@ -1354,20 +1557,20 @@
         <v>73</v>
       </c>
       <c r="T31">
-        <f t="shared" ref="T31:T40" si="0">$B$37*$G$35*O31</f>
+        <f>$B$37*$G$35*O31</f>
         <v>1.0286844708209693E-8</v>
       </c>
       <c r="U31">
-        <f t="shared" ref="U31:U40" si="1">$B$37*$G$34*O31</f>
+        <f t="shared" ref="U31:U40" si="0">$B$37*$G$34*O31</f>
         <v>6.1721068249258155E-9</v>
       </c>
       <c r="V31">
-        <f t="shared" ref="V31:V40" si="2">$B$37*$G$36*O31</f>
+        <f t="shared" ref="V31:V40" si="1">$B$37*$G$36*O31</f>
         <v>6.1721068249258155E-9</v>
       </c>
-      <c r="W31" s="29"/>
-      <c r="X31" s="29"/>
-      <c r="Y31" s="29"/>
+      <c r="W31" s="27"/>
+      <c r="X31" s="27"/>
+      <c r="Y31" s="27"/>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32">
@@ -1386,20 +1589,20 @@
         <v>73</v>
       </c>
       <c r="T32">
+        <f t="shared" ref="T31:T40" si="2">$B$37*$G$35*O32</f>
+        <v>1.8316946659441044E-8</v>
+      </c>
+      <c r="U32">
         <f t="shared" si="0"/>
-        <v>1.8316946659441044E-8</v>
-      </c>
-      <c r="U32">
+        <v>1.0990167995664626E-8</v>
+      </c>
+      <c r="V32">
         <f t="shared" si="1"/>
         <v>1.0990167995664626E-8</v>
       </c>
-      <c r="V32">
-        <f t="shared" si="2"/>
-        <v>1.0990167995664626E-8</v>
-      </c>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29"/>
-      <c r="Y32" s="29"/>
+      <c r="W32" s="27"/>
+      <c r="X32" s="27"/>
+      <c r="Y32" s="27"/>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A33">
@@ -1413,7 +1616,7 @@
       <c r="J33" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="K33" s="21"/>
+      <c r="K33" s="20"/>
       <c r="L33" s="13" t="s">
         <v>10</v>
       </c>
@@ -1430,20 +1633,20 @@
         <v>73</v>
       </c>
       <c r="T33">
+        <f t="shared" si="2"/>
+        <v>2.7236099919419822E-8</v>
+      </c>
+      <c r="U33">
         <f t="shared" si="0"/>
-        <v>2.7236099919419822E-8</v>
-      </c>
-      <c r="U33">
+        <v>1.6341659951651891E-8</v>
+      </c>
+      <c r="V33">
         <f t="shared" si="1"/>
         <v>1.6341659951651891E-8</v>
       </c>
-      <c r="V33">
-        <f t="shared" si="2"/>
-        <v>1.6341659951651891E-8</v>
-      </c>
-      <c r="W33" s="29"/>
-      <c r="X33" s="29"/>
-      <c r="Y33" s="29"/>
+      <c r="W33" s="27"/>
+      <c r="X33" s="27"/>
+      <c r="Y33" s="27"/>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A34">
@@ -1465,7 +1668,7 @@
         <v>83</v>
       </c>
       <c r="L34" t="s">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="O34" s="14">
         <v>1.9553072625698323E-4</v>
@@ -1480,20 +1683,20 @@
         <v>73</v>
       </c>
       <c r="T34">
+        <f t="shared" si="2"/>
+        <v>6.6089385474860326E-8</v>
+      </c>
+      <c r="U34">
         <f t="shared" si="0"/>
-        <v>6.6089385474860326E-8</v>
-      </c>
-      <c r="U34">
+        <v>3.9653631284916192E-8</v>
+      </c>
+      <c r="V34">
         <f t="shared" si="1"/>
         <v>3.9653631284916192E-8</v>
       </c>
-      <c r="V34">
-        <f t="shared" si="2"/>
-        <v>3.9653631284916192E-8</v>
-      </c>
-      <c r="W34" s="29"/>
-      <c r="X34" s="29"/>
-      <c r="Y34" s="29"/>
+      <c r="W34" s="27"/>
+      <c r="X34" s="27"/>
+      <c r="Y34" s="27"/>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A35">
@@ -1502,6 +1705,9 @@
       <c r="G35">
         <v>10</v>
       </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
       <c r="I35" t="s">
         <v>89</v>
       </c>
@@ -1512,7 +1718,7 @@
         <v>81</v>
       </c>
       <c r="L35" t="s">
-        <v>9</v>
+        <v>98</v>
       </c>
       <c r="O35" s="14">
         <v>3.3690869086908695E-4</v>
@@ -1527,20 +1733,20 @@
         <v>73</v>
       </c>
       <c r="T35">
+        <f t="shared" si="2"/>
+        <v>1.1387513751375138E-7</v>
+      </c>
+      <c r="U35">
         <f t="shared" si="0"/>
-        <v>1.1387513751375138E-7</v>
-      </c>
-      <c r="U35">
+        <v>6.8325082508250822E-8</v>
+      </c>
+      <c r="V35">
         <f t="shared" si="1"/>
         <v>6.8325082508250822E-8</v>
       </c>
-      <c r="V35">
-        <f t="shared" si="2"/>
-        <v>6.8325082508250822E-8</v>
-      </c>
-      <c r="W35" s="29"/>
-      <c r="X35" s="29"/>
-      <c r="Y35" s="29"/>
+      <c r="W35" s="27"/>
+      <c r="X35" s="27"/>
+      <c r="Y35" s="27"/>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A36">
@@ -1564,7 +1770,7 @@
       <c r="H36">
         <v>3</v>
       </c>
-      <c r="I36" s="23" t="s">
+      <c r="I36" t="s">
         <v>86</v>
       </c>
       <c r="J36" t="s">
@@ -1592,20 +1798,20 @@
         <v>73</v>
       </c>
       <c r="T36">
+        <f t="shared" si="2"/>
+        <v>1.6262852623253359E-7</v>
+      </c>
+      <c r="U36">
         <f t="shared" si="0"/>
-        <v>1.6262852623253359E-7</v>
-      </c>
-      <c r="U36">
+        <v>9.7577115739520148E-8</v>
+      </c>
+      <c r="V36">
         <f t="shared" si="1"/>
         <v>9.7577115739520148E-8</v>
       </c>
-      <c r="V36">
-        <f t="shared" si="2"/>
-        <v>9.7577115739520148E-8</v>
-      </c>
-      <c r="W36" s="29"/>
-      <c r="X36" s="29"/>
-      <c r="Y36" s="29"/>
+      <c r="W36" s="27"/>
+      <c r="X36" s="27"/>
+      <c r="Y36" s="27"/>
     </row>
     <row r="37" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
@@ -1627,8 +1833,11 @@
       <c r="J37" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K37" s="22"/>
-      <c r="M37" s="30" t="s">
+      <c r="K37" s="21"/>
+      <c r="L37" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="M37" s="28" t="s">
         <v>94</v>
       </c>
       <c r="O37" s="15">
@@ -1644,20 +1853,20 @@
         <v>73</v>
       </c>
       <c r="T37">
+        <f t="shared" si="2"/>
+        <v>2.2211791212917761E-7</v>
+      </c>
+      <c r="U37">
         <f t="shared" si="0"/>
-        <v>2.2211791212917761E-7</v>
-      </c>
-      <c r="U37">
+        <v>1.3327074727750656E-7</v>
+      </c>
+      <c r="V37">
         <f t="shared" si="1"/>
         <v>1.3327074727750656E-7</v>
       </c>
-      <c r="V37">
-        <f t="shared" si="2"/>
-        <v>1.3327074727750656E-7</v>
-      </c>
-      <c r="W37" s="29"/>
-      <c r="X37" s="29"/>
-      <c r="Y37" s="29"/>
+      <c r="W37" s="27"/>
+      <c r="X37" s="27"/>
+      <c r="Y37" s="27"/>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A38">
@@ -1676,20 +1885,20 @@
         <v>73</v>
       </c>
       <c r="T38">
+        <f t="shared" si="2"/>
+        <v>3.1044086276368805E-7</v>
+      </c>
+      <c r="U38">
         <f t="shared" si="0"/>
-        <v>3.1044086276368805E-7</v>
-      </c>
-      <c r="U38">
+        <v>1.8626451765821281E-7</v>
+      </c>
+      <c r="V38">
         <f t="shared" si="1"/>
         <v>1.8626451765821281E-7</v>
       </c>
-      <c r="V38">
-        <f t="shared" si="2"/>
-        <v>1.8626451765821281E-7</v>
-      </c>
-      <c r="W38" s="29"/>
-      <c r="X38" s="29"/>
-      <c r="Y38" s="29"/>
+      <c r="W38" s="27"/>
+      <c r="X38" s="27"/>
+      <c r="Y38" s="27"/>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A39">
@@ -1708,20 +1917,20 @@
         <v>73</v>
       </c>
       <c r="T39">
+        <f t="shared" si="2"/>
+        <v>3.4756765918978473E-7</v>
+      </c>
+      <c r="U39">
         <f t="shared" si="0"/>
-        <v>3.4756765918978473E-7</v>
-      </c>
-      <c r="U39">
+        <v>2.085405955138708E-7</v>
+      </c>
+      <c r="V39">
         <f t="shared" si="1"/>
         <v>2.085405955138708E-7</v>
       </c>
-      <c r="V39">
-        <f t="shared" si="2"/>
-        <v>2.085405955138708E-7</v>
-      </c>
-      <c r="W39" s="29"/>
-      <c r="X39" s="29"/>
-      <c r="Y39" s="29"/>
+      <c r="W39" s="27"/>
+      <c r="X39" s="27"/>
+      <c r="Y39" s="27"/>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A40">
@@ -1740,20 +1949,20 @@
         <v>73</v>
       </c>
       <c r="T40">
+        <f t="shared" si="2"/>
+        <v>3.9990275526742293E-7</v>
+      </c>
+      <c r="U40">
         <f t="shared" si="0"/>
-        <v>3.9990275526742293E-7</v>
-      </c>
-      <c r="U40">
+        <v>2.3994165316045375E-7</v>
+      </c>
+      <c r="V40">
         <f t="shared" si="1"/>
         <v>2.3994165316045375E-7</v>
       </c>
-      <c r="V40">
-        <f t="shared" si="2"/>
-        <v>2.3994165316045375E-7</v>
-      </c>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
-      <c r="Y40" s="29"/>
+      <c r="W40" s="27"/>
+      <c r="X40" s="27"/>
+      <c r="Y40" s="27"/>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A41">
@@ -2150,12 +2359,12 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
@@ -2173,7 +2382,7 @@
       <c r="F3" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="22" t="s">
         <v>55</v>
       </c>
       <c r="H3" t="s">
@@ -2204,7 +2413,7 @@
         <f>B4/$E4</f>
         <v>2.4844720496894415E-2</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="23">
         <f t="shared" ref="G4:H4" si="0">C4/$E4</f>
         <v>0</v>
       </c>
@@ -2234,7 +2443,7 @@
         <f t="shared" ref="F5:F14" si="2">B5/$E5</f>
         <v>3.5067212156633547E-2</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="24">
         <f t="shared" ref="G5:G14" si="3">C5/$E5</f>
         <v>5.8445353594389253E-4</v>
       </c>
@@ -2264,7 +2473,7 @@
         <f t="shared" si="2"/>
         <v>4.065040650406504E-2</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="24">
         <f t="shared" si="3"/>
         <v>1.1614401858304297E-3</v>
       </c>
@@ -2294,7 +2503,7 @@
         <f t="shared" si="2"/>
         <v>6.1855670103092772E-2</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="24">
         <f t="shared" si="3"/>
         <v>5.1546391752577319E-3</v>
       </c>
@@ -2324,7 +2533,7 @@
         <f t="shared" si="2"/>
         <v>8.9201877934272297E-2</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="24">
         <f t="shared" si="3"/>
         <v>4.6948356807511738E-3</v>
       </c>
@@ -2354,7 +2563,7 @@
         <f t="shared" si="2"/>
         <v>0.12608695652173912</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="24">
         <f t="shared" si="3"/>
         <v>4.3478260869565218E-3</v>
       </c>
@@ -2384,7 +2593,7 @@
         <f t="shared" si="2"/>
         <v>0.15873015873015872</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="24">
         <f t="shared" si="3"/>
         <v>7.9365079365079378E-3</v>
       </c>
@@ -2414,7 +2623,7 @@
         <f t="shared" si="2"/>
         <v>0.18909090909090909</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="24">
         <f t="shared" si="3"/>
         <v>1.0909090909090908E-2</v>
       </c>
@@ -2444,7 +2653,7 @@
         <f t="shared" si="2"/>
         <v>0.21404682274247494</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="24">
         <f t="shared" si="3"/>
         <v>1.6722408026755852E-2</v>
       </c>
@@ -2474,7 +2683,7 @@
         <f t="shared" si="2"/>
         <v>0.24223602484472048</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="24">
         <f t="shared" si="3"/>
         <v>2.1739130434782605E-2</v>
       </c>
@@ -2504,7 +2713,7 @@
         <f t="shared" si="2"/>
         <v>0.27325581395348841</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="25">
         <f t="shared" si="3"/>
         <v>2.9069767441860465E-2</v>
       </c>
@@ -2527,10 +2736,10 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="17"/>
+      <c r="C18" s="29"/>
       <c r="D18" t="s">
         <v>64</v>
       </c>
@@ -2556,7 +2765,7 @@
       <c r="A20">
         <v>2018</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="26">
         <f>C20/F20</f>
         <v>3.1809145129224651E-5</v>
       </c>
@@ -2577,7 +2786,7 @@
       <c r="A21">
         <v>2019</v>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="26">
         <f t="shared" ref="B21:B30" si="5">C21/F21</f>
         <v>3.0434451799436964E-5</v>
       </c>
@@ -2598,7 +2807,7 @@
       <c r="A22">
         <v>2020</v>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="26">
         <f t="shared" si="5"/>
         <v>5.4192149880003095E-5</v>
       </c>
@@ -2619,7 +2828,7 @@
       <c r="A23">
         <v>2021</v>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="26">
         <f t="shared" si="5"/>
         <v>8.058017727639001E-5</v>
       </c>
@@ -2640,7 +2849,7 @@
       <c r="A24">
         <v>2022</v>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="26">
         <f t="shared" si="5"/>
         <v>1.9553072625698323E-4</v>
       </c>
@@ -2661,7 +2870,7 @@
       <c r="A25">
         <v>2023</v>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="26">
         <f t="shared" si="5"/>
         <v>3.3690869086908695E-4</v>
       </c>
@@ -2682,7 +2891,7 @@
       <c r="A26">
         <v>2024</v>
       </c>
-      <c r="B26" s="28">
+      <c r="B26" s="26">
         <f t="shared" si="5"/>
         <v>4.8114948589506984E-4</v>
       </c>
@@ -2703,7 +2912,7 @@
       <c r="A27">
         <v>2025</v>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="26">
         <f t="shared" si="5"/>
         <v>6.5715358618099887E-4</v>
       </c>
@@ -2724,7 +2933,7 @@
       <c r="A28">
         <v>2026</v>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="26">
         <f t="shared" si="5"/>
         <v>9.1846409101682864E-4</v>
       </c>
@@ -2745,7 +2954,7 @@
       <c r="A29">
         <v>2027</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="26">
         <f t="shared" si="5"/>
         <v>1.028306683993446E-3</v>
       </c>
@@ -2766,7 +2975,7 @@
       <c r="A30">
         <v>2028</v>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="26">
         <f t="shared" si="5"/>
         <v>1.1831442463533224E-3</v>
       </c>
@@ -2794,895 +3003,5137 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC8D308E-7B61-42DF-B4D3-D4FC1F1DABBA}">
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:Y180"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="14.90625" customWidth="1"/>
+    <col min="4" max="4" width="17.90625" customWidth="1"/>
+    <col min="5" max="5" width="17.6328125" customWidth="1"/>
+    <col min="9" max="9" width="13.26953125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="B1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B1" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="I1" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+    </row>
+    <row r="2" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="B2" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I2" t="s">
+        <v>154</v>
+      </c>
+      <c r="J2" t="s">
+        <v>161</v>
+      </c>
+      <c r="K2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2015</v>
+      </c>
+      <c r="B3">
+        <f>D180</f>
+        <v>9904</v>
+      </c>
+      <c r="C3">
+        <f>H180</f>
+        <v>1516</v>
+      </c>
+      <c r="D3">
+        <f>L180</f>
+        <v>2120</v>
+      </c>
+      <c r="E3">
+        <f>P180</f>
+        <v>1105</v>
+      </c>
+      <c r="F3">
+        <f>T180</f>
+        <v>6190</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="30">
+        <f>(C3+G3)/B3</f>
+        <v>0.15306946688206785</v>
+      </c>
+      <c r="J3" s="30">
+        <f>(D3+E3)/B3</f>
+        <v>0.32562600969305333</v>
+      </c>
+      <c r="K3" s="30">
+        <f>F3/B3</f>
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2016</v>
+      </c>
+      <c r="B4">
+        <f>D163</f>
+        <v>13817</v>
+      </c>
+      <c r="C4">
+        <f>H163</f>
+        <v>1923</v>
+      </c>
+      <c r="D4">
+        <f>L163</f>
+        <v>1829</v>
+      </c>
+      <c r="E4">
+        <f>P163</f>
+        <v>2025</v>
+      </c>
+      <c r="F4">
+        <f>T163</f>
+        <v>9194</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="30">
+        <f t="shared" ref="I4:I11" si="0">(C4+G4)/B4</f>
+        <v>0.13917637692697402</v>
+      </c>
+      <c r="J4" s="30">
+        <f t="shared" ref="J4:J11" si="1">(D4+E4)/B4</f>
+        <v>0.27893175074183979</v>
+      </c>
+      <c r="K4" s="30">
+        <f t="shared" ref="K4:K11" si="2">F4/B4</f>
+        <v>0.66541217340956793</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2017</v>
+      </c>
+      <c r="B5">
+        <f>D144</f>
+        <v>9600</v>
+      </c>
+      <c r="C5">
+        <f>H144</f>
+        <v>2064</v>
+      </c>
+      <c r="D5">
+        <f>L144</f>
+        <v>1664</v>
+      </c>
+      <c r="E5">
+        <f>P144</f>
+        <v>2283</v>
+      </c>
+      <c r="F5">
+        <f>T144</f>
+        <v>4851</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="30">
+        <f t="shared" si="0"/>
+        <v>0.215</v>
+      </c>
+      <c r="J5" s="30">
+        <f t="shared" si="1"/>
+        <v>0.41114583333333332</v>
+      </c>
+      <c r="K5" s="30">
+        <f t="shared" si="2"/>
+        <v>0.50531250000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>2018</v>
+      </c>
+      <c r="B6">
+        <f>D121</f>
+        <v>11583.952555</v>
+      </c>
+      <c r="C6">
+        <f>H121</f>
+        <v>2651.4248549999998</v>
+      </c>
+      <c r="D6">
+        <f>L121</f>
+        <v>1876.7811999999999</v>
+      </c>
+      <c r="E6">
+        <f>P121</f>
+        <v>2807.2974000000004</v>
+      </c>
+      <c r="F6">
+        <f>T121</f>
+        <v>5917.5950000000003</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="30">
+        <f t="shared" si="0"/>
+        <v>0.22888775160388247</v>
+      </c>
+      <c r="J6" s="30">
+        <f t="shared" si="1"/>
+        <v>0.4043592700988925</v>
+      </c>
+      <c r="K6" s="30">
+        <f t="shared" si="2"/>
+        <v>0.51084420208936188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>2019</v>
+      </c>
+      <c r="B7">
+        <f>D102</f>
+        <v>18470.21</v>
+      </c>
+      <c r="C7">
+        <f>H102</f>
+        <v>3821.49</v>
+      </c>
+      <c r="D7">
+        <f>L102</f>
+        <v>2277.16</v>
+      </c>
+      <c r="E7">
+        <f>P102</f>
+        <v>3260.96</v>
+      </c>
+      <c r="F7">
+        <f>T102</f>
+        <v>11319.04</v>
+      </c>
+      <c r="G7">
+        <f>Y102</f>
+        <v>124.04</v>
+      </c>
+      <c r="I7" s="30">
+        <f t="shared" si="0"/>
+        <v>0.21361587117850853</v>
+      </c>
+      <c r="J7" s="30">
+        <f t="shared" si="1"/>
+        <v>0.29984066234222567</v>
+      </c>
+      <c r="K7" s="30">
+        <f t="shared" si="2"/>
+        <v>0.61282681680392381</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>2020</v>
+      </c>
+      <c r="B8">
+        <f>D86</f>
+        <v>30854.86</v>
+      </c>
+      <c r="C8">
+        <f>H86</f>
+        <v>4039.47</v>
+      </c>
+      <c r="D8">
+        <f>L86</f>
+        <v>1912.89</v>
+      </c>
+      <c r="E8">
+        <f>P86</f>
+        <v>3935.58</v>
+      </c>
+      <c r="F8">
+        <f>T86</f>
+        <v>23221.3</v>
+      </c>
+      <c r="G8">
+        <f>Y86</f>
+        <v>194.08</v>
+      </c>
+      <c r="I8" s="30">
+        <f t="shared" si="0"/>
+        <v>0.13720853051998941</v>
+      </c>
+      <c r="J8" s="30">
+        <f t="shared" si="1"/>
+        <v>0.1895477730250599</v>
+      </c>
+      <c r="K8" s="30">
+        <f t="shared" si="2"/>
+        <v>0.75259780793041997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>2021</v>
+      </c>
+      <c r="B9">
+        <f>D69</f>
+        <v>30493.785181493997</v>
+      </c>
+      <c r="C9">
+        <f>H69</f>
+        <v>5522.4659814939978</v>
+      </c>
+      <c r="D9">
+        <f>L69</f>
+        <v>1915.4571562580002</v>
+      </c>
+      <c r="E9">
+        <f>P69</f>
+        <v>4564.4751303419989</v>
+      </c>
+      <c r="F9">
+        <f>T69</f>
+        <v>19707.379413400002</v>
+      </c>
+      <c r="G9">
+        <f>Y69</f>
+        <v>1691.6102000000001</v>
+      </c>
+      <c r="I9" s="30">
+        <f t="shared" si="0"/>
+        <v>0.23657529357398571</v>
+      </c>
+      <c r="J9" s="30">
+        <f t="shared" si="1"/>
+        <v>0.21250009626658375</v>
+      </c>
+      <c r="K9" s="30">
+        <f t="shared" si="2"/>
+        <v>0.64627527530953988</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>2022</v>
+      </c>
+      <c r="B10">
+        <f>D52</f>
+        <v>45536</v>
+      </c>
+      <c r="C10">
+        <f>H52</f>
+        <v>7538</v>
+      </c>
+      <c r="D10">
+        <f>L52</f>
+        <v>3790</v>
+      </c>
+      <c r="E10">
+        <f>P52</f>
+        <v>4978.22</v>
+      </c>
+      <c r="F10">
+        <f>T52</f>
+        <v>28623</v>
+      </c>
+      <c r="G10">
+        <f>Y52</f>
+        <v>4348</v>
+      </c>
+      <c r="I10" s="30">
+        <f t="shared" si="0"/>
+        <v>0.26102424455375967</v>
+      </c>
+      <c r="J10" s="30">
+        <f t="shared" si="1"/>
+        <v>0.19255578004216448</v>
+      </c>
+      <c r="K10" s="30">
+        <f t="shared" si="2"/>
+        <v>0.62857958538299363</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>2023</v>
+      </c>
+      <c r="B11">
+        <f>D36</f>
+        <v>48217.54210579193</v>
+      </c>
+      <c r="C11">
+        <f>H36</f>
+        <v>3371.8142200714274</v>
+      </c>
+      <c r="D11">
+        <f>L36</f>
+        <v>470.9481475798874</v>
+      </c>
+      <c r="E11">
+        <f>P36</f>
+        <v>4769.973992450834</v>
+      </c>
+      <c r="F11">
+        <f>T36</f>
+        <v>37604.328656536789</v>
+      </c>
+      <c r="G11">
+        <f>X36</f>
+        <v>2000.4770891529802</v>
+      </c>
+      <c r="I11" s="30">
+        <f t="shared" si="0"/>
+        <v>0.11141777607488382</v>
+      </c>
+      <c r="J11" s="30">
+        <f t="shared" si="1"/>
+        <v>0.10869326620863111</v>
+      </c>
+      <c r="K11" s="30">
+        <f t="shared" si="2"/>
+        <v>0.77988895771648481</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="23" spans="2:24" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
         <v>19</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G23" t="s">
         <v>36</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K23" t="s">
         <v>40</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O23" t="s">
         <v>46</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S23" t="s">
         <v>48</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="24" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C24" t="s">
         <v>21</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D24" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F24" t="s">
         <v>20</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G24" t="s">
         <v>21</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H24" t="s">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J24" t="s">
         <v>20</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K24" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L24" t="s">
         <v>22</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N24" t="s">
         <v>20</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O24" t="s">
         <v>21</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P24" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R24" t="s">
         <v>20</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S24" t="s">
         <v>21</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T24" t="s">
         <v>22</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V24" t="s">
         <v>20</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W24" t="s">
         <v>21</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A3">
+    <row r="25" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B25">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C25" t="s">
         <v>23</v>
       </c>
-      <c r="C3">
+      <c r="D25">
         <v>0.30393992465576336</v>
       </c>
-      <c r="E3">
+      <c r="F25">
         <v>1</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G25" t="s">
         <v>28</v>
       </c>
-      <c r="G3">
+      <c r="H25">
         <v>0.90542979856308781</v>
       </c>
-      <c r="I3">
+      <c r="J25">
         <v>1</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K25" t="s">
         <v>41</v>
       </c>
-      <c r="K3">
+      <c r="L25">
         <v>0.56331411719800495</v>
       </c>
-      <c r="M3">
+      <c r="N25">
         <v>1</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O25" t="s">
         <v>30</v>
       </c>
-      <c r="O3">
+      <c r="P25">
         <v>0.31924702365464647</v>
       </c>
-      <c r="Q3">
+      <c r="R25">
         <v>1</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S25" t="s">
         <v>23</v>
       </c>
-      <c r="S3">
+      <c r="T25">
         <v>0.36234318344008598</v>
       </c>
-      <c r="U3">
+      <c r="V25">
         <v>1</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W25" t="s">
         <v>41</v>
       </c>
-      <c r="W3">
+      <c r="X25">
         <v>0.91452134589285305</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="26" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B26">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C26" t="s">
         <v>24</v>
       </c>
-      <c r="C4">
+      <c r="D26">
         <v>0.18852060065724716</v>
       </c>
-      <c r="E4">
+      <c r="F26">
         <v>2</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G26" t="s">
         <v>37</v>
       </c>
-      <c r="G4">
+      <c r="H26">
         <v>4.1520674290600239E-2</v>
       </c>
-      <c r="I4">
+      <c r="J26">
         <v>2</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K26" t="s">
         <v>27</v>
       </c>
-      <c r="K4">
+      <c r="L26">
         <v>0.11678568072225042</v>
       </c>
-      <c r="M4">
+      <c r="N26">
         <v>2</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O26" t="s">
         <v>27</v>
       </c>
-      <c r="O4">
+      <c r="P26">
         <v>0.23689856627905867</v>
       </c>
-      <c r="Q4">
+      <c r="R26">
         <v>2</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S26" t="s">
         <v>24</v>
       </c>
-      <c r="S4">
+      <c r="T26">
         <v>0.24172749055100812</v>
       </c>
-      <c r="U4">
+      <c r="V26">
         <v>2</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W26" t="s">
         <v>43</v>
       </c>
-      <c r="W4">
+      <c r="X26">
         <v>4.8863343914320068E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A5">
+    <row r="27" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B27">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C27" t="s">
         <v>25</v>
       </c>
-      <c r="C5">
+      <c r="D27">
         <v>0.11614030403526776</v>
       </c>
-      <c r="E5">
+      <c r="F27">
         <v>3</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G27" t="s">
         <v>38</v>
       </c>
-      <c r="G5">
+      <c r="H27">
         <v>3.0331786784455011E-2</v>
       </c>
-      <c r="I5">
+      <c r="J27">
         <v>3</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K27" t="s">
         <v>42</v>
       </c>
-      <c r="K5">
+      <c r="L27">
         <v>0.10788002212338918</v>
       </c>
-      <c r="M5">
+      <c r="N27">
         <v>3</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O27" t="s">
         <v>23</v>
       </c>
-      <c r="O5">
+      <c r="P27">
         <v>0.21584267751001046</v>
       </c>
-      <c r="Q5">
+      <c r="R27">
         <v>3</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S27" t="s">
         <v>25</v>
       </c>
-      <c r="S5">
+      <c r="T27">
         <v>0.1489190260820292</v>
       </c>
-      <c r="U5">
+      <c r="V27">
         <v>3</v>
       </c>
-      <c r="V5" t="s">
+      <c r="W27" t="s">
         <v>50</v>
       </c>
-      <c r="W5">
+      <c r="X27">
         <v>2.0395134851194461E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A6">
+    <row r="28" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B28">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C28" t="s">
         <v>26</v>
       </c>
-      <c r="C6">
+      <c r="D28">
         <v>0.10523141119195512</v>
       </c>
-      <c r="E6">
+      <c r="F28">
         <v>4</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G28" t="s">
         <v>39</v>
       </c>
-      <c r="G6">
+      <c r="H28">
         <v>2.2717740361856986E-2</v>
       </c>
-      <c r="I6">
+      <c r="J28">
         <v>4</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K28" t="s">
         <v>43</v>
       </c>
-      <c r="K6">
+      <c r="L28">
         <v>9.7508823924634447E-2</v>
       </c>
-      <c r="M6">
+      <c r="N28">
         <v>4</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O28" t="s">
         <v>41</v>
       </c>
-      <c r="O6">
+      <c r="P28">
         <v>0.10328875184219956</v>
       </c>
-      <c r="Q6">
+      <c r="R28">
         <v>4</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S28" t="s">
         <v>26</v>
       </c>
-      <c r="S6">
+      <c r="T28">
         <v>0.13493127470361002</v>
       </c>
-      <c r="U6" t="s">
+      <c r="V28" t="s">
         <v>33</v>
       </c>
-      <c r="V6" t="s">
+      <c r="W28" t="s">
         <v>33</v>
       </c>
-      <c r="W6" t="s">
+      <c r="X28" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A7">
+    <row r="29" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B29">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C29" t="s">
         <v>27</v>
       </c>
-      <c r="C7">
+      <c r="D29">
         <v>7.2380296621979381E-2</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F29" t="s">
         <v>33</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G29" t="s">
         <v>33</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H29" t="s">
         <v>33</v>
       </c>
-      <c r="I7">
+      <c r="J29">
         <v>5</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K29" t="s">
         <v>44</v>
       </c>
-      <c r="K7">
+      <c r="L29">
         <v>8.3074750800168254E-2</v>
       </c>
-      <c r="M7">
+      <c r="N29">
         <v>5</v>
       </c>
-      <c r="N7" t="s">
+      <c r="O29" t="s">
         <v>42</v>
       </c>
-      <c r="O7">
+      <c r="P29">
         <v>5.0258088334766339E-2</v>
       </c>
-      <c r="Q7">
+      <c r="R29">
         <v>5</v>
       </c>
-      <c r="R7" t="s">
+      <c r="S29" t="s">
         <v>27</v>
       </c>
-      <c r="S7">
+      <c r="T29">
         <v>6.1163171426547702E-2</v>
       </c>
-      <c r="U7" t="s">
+      <c r="V29" t="s">
         <v>33</v>
       </c>
-      <c r="V7" t="s">
+      <c r="W29" t="s">
         <v>33</v>
       </c>
-      <c r="W7" t="s">
+      <c r="X29" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A8">
+    <row r="30" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B30">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C30" t="s">
         <v>28</v>
       </c>
-      <c r="C8">
+      <c r="D30">
         <v>6.3315982871402013E-2</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F30" t="s">
         <v>33</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G30" t="s">
         <v>33</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H30" t="s">
         <v>33</v>
       </c>
-      <c r="I8">
+      <c r="J30">
         <v>6</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K30" t="s">
         <v>45</v>
       </c>
-      <c r="K8">
+      <c r="L30">
         <v>3.1436605231552818E-2</v>
       </c>
-      <c r="M8">
+      <c r="N30">
         <v>6</v>
       </c>
-      <c r="N8" t="s">
+      <c r="O30" t="s">
         <v>47</v>
       </c>
-      <c r="O8">
+      <c r="P30">
         <v>4.1308401327102409E-2</v>
       </c>
-      <c r="Q8">
+      <c r="R30">
         <v>6</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S30" t="s">
         <v>31</v>
       </c>
-      <c r="S8">
+      <c r="T30">
         <v>2.5438294849965772E-2</v>
       </c>
-      <c r="U8" t="s">
+      <c r="V30" t="s">
         <v>33</v>
       </c>
-      <c r="V8" t="s">
+      <c r="W30" t="s">
         <v>33</v>
       </c>
-      <c r="W8" t="s">
+      <c r="X30" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A9">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B31">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C31" t="s">
         <v>29</v>
       </c>
-      <c r="C9">
+      <c r="D31">
         <v>5.3662117291731336E-2</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F31" t="s">
         <v>33</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G31" t="s">
         <v>33</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H31" t="s">
         <v>33</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J31" t="s">
         <v>33</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K31" t="s">
         <v>33</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L31" t="s">
         <v>33</v>
       </c>
-      <c r="M9">
+      <c r="N31">
         <v>7</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O31" t="s">
         <v>45</v>
       </c>
-      <c r="O9">
+      <c r="P31">
         <v>2.8239042857085037E-2</v>
       </c>
-      <c r="Q9">
+      <c r="R31">
         <v>7</v>
       </c>
-      <c r="R9" t="s">
+      <c r="S31" t="s">
         <v>32</v>
       </c>
-      <c r="S9">
+      <c r="T31">
         <v>2.5263049067487095E-2</v>
       </c>
-      <c r="U9" t="s">
+      <c r="V31" t="s">
         <v>33</v>
       </c>
-      <c r="V9" t="s">
+      <c r="W31" t="s">
         <v>33</v>
       </c>
-      <c r="W9" t="s">
+      <c r="X31" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A10">
+    <row r="32" spans="2:24" x14ac:dyDescent="0.35">
+      <c r="B32">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C32" t="s">
         <v>30</v>
       </c>
-      <c r="C10">
+      <c r="D32">
         <v>3.1581866961590314E-2</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F32" t="s">
         <v>33</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G32" t="s">
         <v>33</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H32" t="s">
         <v>33</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J32" t="s">
         <v>33</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K32" t="s">
         <v>33</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L32" t="s">
         <v>33</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N32" t="s">
         <v>33</v>
       </c>
-      <c r="N10" t="s">
+      <c r="O32" t="s">
         <v>33</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P32" t="s">
         <v>33</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R32" t="s">
         <v>33</v>
       </c>
-      <c r="R10" t="s">
+      <c r="S32" t="s">
         <v>33</v>
       </c>
-      <c r="S10" t="s">
+      <c r="T32" t="s">
         <v>33</v>
       </c>
-      <c r="U10" t="s">
+      <c r="V32" t="s">
         <v>33</v>
       </c>
-      <c r="V10" t="s">
+      <c r="W32" t="s">
         <v>33</v>
       </c>
-      <c r="W10" t="s">
+      <c r="X32" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A11">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B33">
         <v>9</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C33" t="s">
         <v>31</v>
       </c>
-      <c r="C11">
+      <c r="D33">
         <v>1.983904525662443E-2</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F33" t="s">
         <v>33</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G33" t="s">
         <v>33</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H33" t="s">
         <v>33</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J33" t="s">
         <v>33</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K33" t="s">
         <v>33</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L33" t="s">
         <v>33</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N33" t="s">
         <v>33</v>
       </c>
-      <c r="N11" t="s">
+      <c r="O33" t="s">
         <v>33</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P33" t="s">
         <v>33</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R33" t="s">
         <v>33</v>
       </c>
-      <c r="R11" t="s">
+      <c r="S33" t="s">
         <v>33</v>
       </c>
-      <c r="S11" t="s">
+      <c r="T33" t="s">
         <v>33</v>
       </c>
-      <c r="U11" t="s">
+      <c r="V33" t="s">
         <v>33</v>
       </c>
-      <c r="V11" t="s">
+      <c r="W33" t="s">
         <v>33</v>
       </c>
-      <c r="W11" t="s">
+      <c r="X33" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A12">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B34">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C34" t="s">
         <v>32</v>
       </c>
-      <c r="C12">
+      <c r="D34">
         <v>1.9702373005982925E-2</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F34" t="s">
         <v>33</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G34" t="s">
         <v>33</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H34" t="s">
         <v>33</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J34" t="s">
         <v>33</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K34" t="s">
         <v>33</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L34" t="s">
         <v>33</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N34" t="s">
         <v>33</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O34" t="s">
         <v>33</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P34" t="s">
         <v>33</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R34" t="s">
         <v>33</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S34" t="s">
         <v>33</v>
       </c>
-      <c r="S12" t="s">
+      <c r="T34" t="s">
         <v>33</v>
       </c>
-      <c r="U12" t="s">
+      <c r="V34" t="s">
         <v>33</v>
       </c>
-      <c r="V12" t="s">
+      <c r="W34" t="s">
         <v>33</v>
       </c>
-      <c r="W12" t="s">
+      <c r="X34" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="35" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="C35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35">
+        <v>2.5686077450456299E-2</v>
+      </c>
+      <c r="G35" t="s">
         <v>33</v>
       </c>
-      <c r="B13" t="s">
+      <c r="H35" t="s">
         <v>33</v>
       </c>
-      <c r="C13" t="s">
+      <c r="K35" t="s">
         <v>33</v>
       </c>
-      <c r="E13" t="s">
+      <c r="L35" t="s">
         <v>33</v>
       </c>
-      <c r="F13" t="s">
+      <c r="O35" t="s">
         <v>33</v>
       </c>
-      <c r="G13" t="s">
+      <c r="P35" t="s">
         <v>33</v>
       </c>
-      <c r="I13" t="s">
+      <c r="S35" t="s">
         <v>33</v>
       </c>
-      <c r="J13" t="s">
+      <c r="T35" t="s">
         <v>33</v>
       </c>
-      <c r="K13" t="s">
-        <v>33</v>
-      </c>
-      <c r="M13" t="s">
-        <v>33</v>
-      </c>
-      <c r="N13" t="s">
-        <v>33</v>
-      </c>
-      <c r="O13" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>33</v>
-      </c>
-      <c r="R13" t="s">
-        <v>33</v>
-      </c>
-      <c r="S13" t="s">
-        <v>33</v>
-      </c>
-      <c r="U13" t="s">
-        <v>33</v>
-      </c>
-      <c r="V13" t="s">
-        <v>33</v>
-      </c>
-      <c r="W13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J14" t="s">
-        <v>33</v>
-      </c>
-      <c r="K14" t="s">
-        <v>33</v>
-      </c>
-      <c r="M14" t="s">
-        <v>33</v>
-      </c>
-      <c r="N14" t="s">
-        <v>33</v>
-      </c>
-      <c r="O14" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>33</v>
-      </c>
-      <c r="R14" t="s">
-        <v>33</v>
-      </c>
-      <c r="S14" t="s">
-        <v>33</v>
-      </c>
-      <c r="U14" t="s">
-        <v>33</v>
-      </c>
-      <c r="V14" t="s">
-        <v>33</v>
-      </c>
-      <c r="W14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" t="s">
-        <v>33</v>
-      </c>
-      <c r="I15" t="s">
-        <v>33</v>
-      </c>
-      <c r="J15" t="s">
-        <v>33</v>
-      </c>
-      <c r="K15" t="s">
-        <v>33</v>
-      </c>
-      <c r="M15" t="s">
-        <v>33</v>
-      </c>
-      <c r="N15" t="s">
-        <v>33</v>
-      </c>
-      <c r="O15" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>33</v>
-      </c>
-      <c r="R15" t="s">
-        <v>33</v>
-      </c>
-      <c r="S15" t="s">
-        <v>33</v>
-      </c>
-      <c r="U15" t="s">
-        <v>33</v>
-      </c>
-      <c r="V15" t="s">
-        <v>33</v>
-      </c>
-      <c r="W15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="B16" t="s">
+      <c r="W35" t="s">
         <v>34</v>
       </c>
-      <c r="C16">
-        <v>2.5686077450456257E-2</v>
-      </c>
-      <c r="F16" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" t="s">
-        <v>33</v>
-      </c>
-      <c r="J16" t="s">
-        <v>33</v>
-      </c>
-      <c r="K16" t="s">
-        <v>33</v>
-      </c>
-      <c r="N16" t="s">
-        <v>33</v>
-      </c>
-      <c r="O16" t="s">
-        <v>33</v>
-      </c>
-      <c r="R16" t="s">
-        <v>33</v>
-      </c>
-      <c r="S16" t="s">
-        <v>33</v>
-      </c>
-      <c r="V16" t="s">
+      <c r="X35">
+        <v>1.6220175341632337E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36">
+        <v>48217.54210579193</v>
+      </c>
+      <c r="F36" t="s">
+        <v>35</v>
+      </c>
+      <c r="H36">
+        <v>3371.8142200714274</v>
+      </c>
+      <c r="J36" t="s">
+        <v>35</v>
+      </c>
+      <c r="L36">
+        <v>470.9481475798874</v>
+      </c>
+      <c r="N36" t="s">
+        <v>35</v>
+      </c>
+      <c r="P36">
+        <v>4769.973992450834</v>
+      </c>
+      <c r="R36" t="s">
+        <v>35</v>
+      </c>
+      <c r="T36">
+        <v>37604.328656536789</v>
+      </c>
+      <c r="V36" t="s">
+        <v>35</v>
+      </c>
+      <c r="X36">
+        <v>2000.4770891529802</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+    </row>
+    <row r="38" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>99</v>
+      </c>
+      <c r="J38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" t="s">
+        <v>102</v>
+      </c>
+      <c r="J40" t="s">
+        <v>103</v>
+      </c>
+      <c r="N40" t="s">
+        <v>104</v>
+      </c>
+      <c r="R40" t="s">
+        <v>105</v>
+      </c>
+      <c r="V40" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" t="s">
+        <v>21</v>
+      </c>
+      <c r="H41" t="s">
+        <v>22</v>
+      </c>
+      <c r="J41" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" t="s">
+        <v>22</v>
+      </c>
+      <c r="N41" t="s">
+        <v>20</v>
+      </c>
+      <c r="O41" t="s">
+        <v>21</v>
+      </c>
+      <c r="P41" t="s">
+        <v>22</v>
+      </c>
+      <c r="R41" t="s">
+        <v>20</v>
+      </c>
+      <c r="S41" t="s">
+        <v>21</v>
+      </c>
+      <c r="T41" t="s">
+        <v>22</v>
+      </c>
+      <c r="V41" t="s">
+        <v>20</v>
+      </c>
+      <c r="W41" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42">
+        <v>0.20218960760167404</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
+        <v>108</v>
+      </c>
+      <c r="H42">
+        <v>0.46120001773141939</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42" t="s">
+        <v>29</v>
+      </c>
+      <c r="L42">
+        <v>0.88311345646438</v>
+      </c>
+      <c r="N42">
+        <v>1</v>
+      </c>
+      <c r="O42" t="s">
+        <v>30</v>
+      </c>
+      <c r="P42">
+        <v>0.48445140315181606</v>
+      </c>
+      <c r="R42">
+        <v>1</v>
+      </c>
+      <c r="S42" t="s">
+        <v>24</v>
+      </c>
+      <c r="T42">
+        <v>0.38058078868163553</v>
+      </c>
+      <c r="V42">
+        <v>1</v>
+      </c>
+      <c r="W42" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y42">
+        <v>0.56113668355557955</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43">
+        <v>0.17788139169135367</v>
+      </c>
+      <c r="F43">
+        <v>2</v>
+      </c>
+      <c r="G43" t="s">
+        <v>109</v>
+      </c>
+      <c r="H43">
+        <v>0.4439956784944421</v>
+      </c>
+      <c r="J43">
+        <v>2</v>
+      </c>
+      <c r="K43" t="s">
+        <v>107</v>
+      </c>
+      <c r="L43">
+        <v>6.5768307415860414E-2</v>
+      </c>
+      <c r="N43">
+        <v>2</v>
+      </c>
+      <c r="O43" t="s">
+        <v>107</v>
+      </c>
+      <c r="P43">
+        <v>0.33391236493915555</v>
+      </c>
+      <c r="R43">
+        <v>2</v>
+      </c>
+      <c r="S43" t="s">
+        <v>26</v>
+      </c>
+      <c r="T43">
+        <v>0.25699761024320827</v>
+      </c>
+      <c r="V43">
+        <v>2</v>
+      </c>
+      <c r="W43" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y43">
+        <v>0.31760092918155203</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B44">
+        <v>3</v>
+      </c>
+      <c r="C44" t="s">
+        <v>26</v>
+      </c>
+      <c r="D44">
+        <v>0.14043669992035457</v>
+      </c>
+      <c r="F44">
+        <v>3</v>
+      </c>
+      <c r="G44" t="s">
+        <v>110</v>
+      </c>
+      <c r="H44">
+        <v>5.9700192552175568E-2</v>
+      </c>
+      <c r="J44">
+        <v>3</v>
+      </c>
+      <c r="K44" t="s">
+        <v>27</v>
+      </c>
+      <c r="L44">
+        <v>2.9486344058504272E-2</v>
+      </c>
+      <c r="N44">
+        <v>3</v>
+      </c>
+      <c r="O44" t="s">
+        <v>27</v>
+      </c>
+      <c r="P44">
+        <v>0.122622322430992</v>
+      </c>
+      <c r="R44">
+        <v>3</v>
+      </c>
+      <c r="S44" t="s">
+        <v>107</v>
+      </c>
+      <c r="T44">
+        <v>0.14720374227064759</v>
+      </c>
+      <c r="V44">
+        <v>3</v>
+      </c>
+      <c r="W44" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y44">
+        <v>5.2388810154910891E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B45">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>109</v>
+      </c>
+      <c r="D45">
+        <v>0.12708626141953619</v>
+      </c>
+      <c r="F45">
+        <v>4</v>
+      </c>
+      <c r="G45" t="s">
+        <v>111</v>
+      </c>
+      <c r="H45">
+        <v>1.8002924731844942E-2</v>
+      </c>
+      <c r="J45">
+        <v>4</v>
+      </c>
+      <c r="K45" t="s">
+        <v>44</v>
+      </c>
+      <c r="L45">
+        <v>1.0170498283310847E-2</v>
+      </c>
+      <c r="N45">
+        <v>4</v>
+      </c>
+      <c r="O45" t="s">
+        <v>42</v>
+      </c>
+      <c r="P45">
+        <v>3.3604182667906518E-2</v>
+      </c>
+      <c r="R45">
+        <v>4</v>
+      </c>
+      <c r="S45" t="s">
+        <v>112</v>
+      </c>
+      <c r="T45">
+        <v>0.10209779584554453</v>
+      </c>
+      <c r="V45">
+        <v>4</v>
+      </c>
+      <c r="W45" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y45">
+        <v>4.0839354290206659E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B46">
+        <v>5</v>
+      </c>
+      <c r="C46" t="s">
+        <v>112</v>
+      </c>
+      <c r="D46">
+        <v>9.8822995384085385E-2</v>
+      </c>
+      <c r="J46">
+        <v>5</v>
+      </c>
+      <c r="K46" t="s">
+        <v>42</v>
+      </c>
+      <c r="L46">
+        <v>7.6227285685894815E-3</v>
+      </c>
+      <c r="N46">
+        <v>5</v>
+      </c>
+      <c r="O46" t="s">
+        <v>113</v>
+      </c>
+      <c r="P46">
+        <v>2.071596156031805E-2</v>
+      </c>
+      <c r="R46">
+        <v>5</v>
+      </c>
+      <c r="S46" t="s">
+        <v>27</v>
+      </c>
+      <c r="T46">
+        <v>7.1039379241263925E-2</v>
+      </c>
+      <c r="V46">
+        <v>5</v>
+      </c>
+      <c r="W46" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y46">
+        <v>2.5297493929061447E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B47">
+        <v>6</v>
+      </c>
+      <c r="C47" t="s">
+        <v>108</v>
+      </c>
+      <c r="D47">
+        <v>7.634341745812552E-2</v>
+      </c>
+      <c r="R47">
+        <v>6</v>
+      </c>
+      <c r="S47" t="s">
+        <v>31</v>
+      </c>
+      <c r="T47">
+        <v>4.1710264097370671E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B48">
+        <v>7</v>
+      </c>
+      <c r="C48" t="s">
+        <v>27</v>
+      </c>
+      <c r="D48">
+        <v>7.1982358270824026E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B49">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49">
+        <v>5.3212449701171026E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B50">
+        <v>9</v>
+      </c>
+      <c r="C50" t="s">
+        <v>31</v>
+      </c>
+      <c r="D50">
+        <v>2.5522685607863117E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="C51" t="s">
         <v>34</v>
       </c>
-      <c r="W16">
-        <v>1.6220175341632337E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17">
-        <v>48217.54210579193</v>
-      </c>
-      <c r="E17" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17">
-        <v>3371.8142200714274</v>
-      </c>
-      <c r="I17" t="s">
-        <v>35</v>
-      </c>
-      <c r="K17">
-        <v>470.9481475798874</v>
-      </c>
-      <c r="M17" t="s">
-        <v>35</v>
-      </c>
-      <c r="O17">
-        <v>4769.973992450834</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>35</v>
-      </c>
-      <c r="S17">
-        <v>37604.328656536789</v>
-      </c>
-      <c r="U17" t="s">
-        <v>35</v>
-      </c>
-      <c r="W17">
-        <v>2000.4770891529802</v>
+      <c r="D51">
+        <v>2.65221329450126E-2</v>
+      </c>
+      <c r="G51" t="s">
+        <v>34</v>
+      </c>
+      <c r="H51">
+        <v>0.02</v>
+      </c>
+      <c r="K51" t="s">
+        <v>34</v>
+      </c>
+      <c r="L51">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="52" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
+        <v>114</v>
+      </c>
+      <c r="D52">
+        <v>45536</v>
+      </c>
+      <c r="F52" t="s">
+        <v>114</v>
+      </c>
+      <c r="H52">
+        <v>7538</v>
+      </c>
+      <c r="J52" t="s">
+        <v>114</v>
+      </c>
+      <c r="L52">
+        <v>3790</v>
+      </c>
+      <c r="N52" t="s">
+        <v>114</v>
+      </c>
+      <c r="P52">
+        <v>4978.22</v>
+      </c>
+      <c r="R52" t="s">
+        <v>114</v>
+      </c>
+      <c r="T52">
+        <v>28623</v>
+      </c>
+      <c r="V52" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y52">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="54" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B54" t="s">
+        <v>115</v>
+      </c>
+      <c r="J54" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
+        <v>101</v>
+      </c>
+      <c r="F56" t="s">
+        <v>102</v>
+      </c>
+      <c r="J56" t="s">
+        <v>103</v>
+      </c>
+      <c r="N56" t="s">
+        <v>104</v>
+      </c>
+      <c r="R56" t="s">
+        <v>105</v>
+      </c>
+      <c r="V56" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" t="s">
+        <v>21</v>
+      </c>
+      <c r="D57" t="s">
+        <v>22</v>
+      </c>
+      <c r="F57" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" t="s">
+        <v>21</v>
+      </c>
+      <c r="H57" t="s">
+        <v>22</v>
+      </c>
+      <c r="J57" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" t="s">
+        <v>21</v>
+      </c>
+      <c r="L57" t="s">
+        <v>22</v>
+      </c>
+      <c r="N57" t="s">
+        <v>20</v>
+      </c>
+      <c r="O57" t="s">
+        <v>21</v>
+      </c>
+      <c r="P57" t="s">
+        <v>22</v>
+      </c>
+      <c r="R57" t="s">
+        <v>20</v>
+      </c>
+      <c r="S57" t="s">
+        <v>21</v>
+      </c>
+      <c r="T57" t="s">
+        <v>22</v>
+      </c>
+      <c r="V57" t="s">
+        <v>20</v>
+      </c>
+      <c r="W57" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B58" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" t="s">
+        <v>22</v>
+      </c>
+      <c r="F58" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" t="s">
+        <v>21</v>
+      </c>
+      <c r="H58" t="s">
+        <v>22</v>
+      </c>
+      <c r="J58" t="s">
+        <v>20</v>
+      </c>
+      <c r="K58" t="s">
+        <v>21</v>
+      </c>
+      <c r="L58" t="s">
+        <v>22</v>
+      </c>
+      <c r="N58" t="s">
+        <v>20</v>
+      </c>
+      <c r="O58" t="s">
+        <v>21</v>
+      </c>
+      <c r="P58" t="s">
+        <v>22</v>
+      </c>
+      <c r="R58" t="s">
+        <v>20</v>
+      </c>
+      <c r="S58" t="s">
+        <v>21</v>
+      </c>
+      <c r="T58" t="s">
+        <v>22</v>
+      </c>
+      <c r="V58" t="s">
+        <v>20</v>
+      </c>
+      <c r="W58" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59">
+        <v>0.29108390274182161</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
+      </c>
+      <c r="G59" t="s">
+        <v>116</v>
+      </c>
+      <c r="H59">
+        <v>0.47655571058638319</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="K59" t="s">
+        <v>116</v>
+      </c>
+      <c r="L59">
+        <v>0.86453993219827907</v>
+      </c>
+      <c r="N59">
+        <v>1</v>
+      </c>
+      <c r="O59" t="s">
+        <v>107</v>
+      </c>
+      <c r="P59">
+        <v>0.31342977877826828</v>
+      </c>
+      <c r="R59">
+        <v>1</v>
+      </c>
+      <c r="S59" t="s">
+        <v>24</v>
+      </c>
+      <c r="T59">
+        <v>0.38058078868163553</v>
+      </c>
+      <c r="V59">
+        <v>1</v>
+      </c>
+      <c r="W59" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y59">
+        <v>0.81342616638277543</v>
+      </c>
+    </row>
+    <row r="60" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B60">
+        <v>2</v>
+      </c>
+      <c r="C60" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60">
+        <v>0.22001748750009706</v>
+      </c>
+      <c r="F60">
+        <v>2</v>
+      </c>
+      <c r="G60" t="s">
+        <v>108</v>
+      </c>
+      <c r="H60">
+        <v>0.43441884287442489</v>
+      </c>
+      <c r="J60">
+        <v>2</v>
+      </c>
+      <c r="K60" t="s">
+        <v>107</v>
+      </c>
+      <c r="L60">
+        <v>0.11160477046410426</v>
+      </c>
+      <c r="N60">
+        <v>2</v>
+      </c>
+      <c r="O60" t="s">
+        <v>30</v>
+      </c>
+      <c r="P60">
+        <v>0.28600721062581097</v>
+      </c>
+      <c r="R60">
+        <v>2</v>
+      </c>
+      <c r="S60" t="s">
+        <v>107</v>
+      </c>
+      <c r="T60">
+        <v>0.25699761024320827</v>
+      </c>
+      <c r="V60">
+        <v>2</v>
+      </c>
+      <c r="W60" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y60">
+        <v>0.12848716566026855</v>
+      </c>
+    </row>
+    <row r="61" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B61">
+        <v>3</v>
+      </c>
+      <c r="C61" t="s">
+        <v>27</v>
+      </c>
+      <c r="D61">
+        <v>0.12215603861014342</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="G61" t="s">
+        <v>110</v>
+      </c>
+      <c r="H61">
+        <v>7.2945673427402324E-2</v>
+      </c>
+      <c r="K61" t="s">
+        <v>34</v>
+      </c>
+      <c r="L61">
+        <v>2.3855297337616526E-2</v>
+      </c>
+      <c r="N61">
+        <v>3</v>
+      </c>
+      <c r="O61" t="s">
+        <v>116</v>
+      </c>
+      <c r="P61">
+        <v>0.16615783377993215</v>
+      </c>
+      <c r="R61">
+        <v>3</v>
+      </c>
+      <c r="S61" t="s">
+        <v>27</v>
+      </c>
+      <c r="T61">
+        <v>0.14720374227064759</v>
+      </c>
+      <c r="V61">
+        <v>3</v>
+      </c>
+      <c r="W61" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y61">
+        <v>3.7538198811995813E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B62">
+        <v>4</v>
+      </c>
+      <c r="C62" t="s">
+        <v>116</v>
+      </c>
+      <c r="D62">
+        <v>8.6304887515150419E-2</v>
+      </c>
+      <c r="G62" t="s">
+        <v>34</v>
+      </c>
+      <c r="H62">
+        <v>1.6079773111789607E-2</v>
+      </c>
+      <c r="N62">
+        <v>4</v>
+      </c>
+      <c r="O62" t="s">
+        <v>27</v>
+      </c>
+      <c r="P62">
+        <v>0.15270101821055959</v>
+      </c>
+      <c r="R62">
+        <v>4</v>
+      </c>
+      <c r="S62" t="s">
+        <v>26</v>
+      </c>
+      <c r="T62">
+        <v>0.10209779584554453</v>
+      </c>
+      <c r="V62">
+        <v>4</v>
+      </c>
+      <c r="W62" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y62">
+        <v>1.259155330229151E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B63">
+        <v>5</v>
+      </c>
+      <c r="C63" t="s">
+        <v>108</v>
+      </c>
+      <c r="D63">
+        <v>7.8673843447612926E-2</v>
+      </c>
+      <c r="N63">
+        <v>5</v>
+      </c>
+      <c r="O63" t="s">
+        <v>117</v>
+      </c>
+      <c r="P63">
+        <v>3.8602466870445634E-2</v>
+      </c>
+      <c r="R63">
+        <v>5</v>
+      </c>
+      <c r="S63" t="s">
+        <v>112</v>
+      </c>
+      <c r="T63">
+        <v>7.1039379241263925E-2</v>
+      </c>
+      <c r="W63" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y63">
+        <v>7.9569158426687197E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B64">
+        <v>6</v>
+      </c>
+      <c r="C64" t="s">
+        <v>26</v>
+      </c>
+      <c r="D64">
+        <v>6.5983281118576487E-2</v>
+      </c>
+      <c r="N64">
+        <v>6</v>
+      </c>
+      <c r="O64" t="s">
+        <v>113</v>
+      </c>
+      <c r="P64">
+        <v>2.6706246943855424E-2</v>
+      </c>
+      <c r="R64">
+        <v>6</v>
+      </c>
+      <c r="S64" t="s">
+        <v>31</v>
+      </c>
+      <c r="T64">
+        <v>4.1710264097370671E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B65">
+        <v>7</v>
+      </c>
+      <c r="C65" t="s">
+        <v>112</v>
+      </c>
+      <c r="D65">
+        <v>4.5910994376966656E-2</v>
+      </c>
+      <c r="O65" t="s">
+        <v>34</v>
+      </c>
+      <c r="P65">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="S65" t="s">
+        <v>34</v>
+      </c>
+      <c r="T65">
+        <v>4.0000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B66">
+        <v>8</v>
+      </c>
+      <c r="C66" t="s">
+        <v>30</v>
+      </c>
+      <c r="D66">
+        <v>4.2817918216082558E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B67">
+        <v>9</v>
+      </c>
+      <c r="C67" t="s">
+        <v>31</v>
+      </c>
+      <c r="D67">
+        <v>2.6956312412761849E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="C68" t="s">
+        <v>34</v>
+      </c>
+      <c r="D68">
+        <v>2.0095334060787059E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
+        <v>118</v>
+      </c>
+      <c r="D69">
+        <v>30493.785181493997</v>
+      </c>
+      <c r="F69" t="s">
+        <v>118</v>
+      </c>
+      <c r="H69">
+        <v>5522.4659814939978</v>
+      </c>
+      <c r="J69" t="s">
+        <v>118</v>
+      </c>
+      <c r="L69">
+        <v>1915.4571562580002</v>
+      </c>
+      <c r="N69" t="s">
+        <v>118</v>
+      </c>
+      <c r="P69">
+        <v>4564.4751303419989</v>
+      </c>
+      <c r="R69" t="s">
+        <v>118</v>
+      </c>
+      <c r="T69">
+        <v>19707.379413400002</v>
+      </c>
+      <c r="V69" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y69">
+        <v>1691.6102000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B71" t="s">
+        <v>119</v>
+      </c>
+      <c r="J71" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
+        <v>101</v>
+      </c>
+      <c r="F73" t="s">
+        <v>102</v>
+      </c>
+      <c r="J73" t="s">
+        <v>103</v>
+      </c>
+      <c r="N73" t="s">
+        <v>104</v>
+      </c>
+      <c r="R73" t="s">
+        <v>105</v>
+      </c>
+      <c r="V73" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
+        <v>20</v>
+      </c>
+      <c r="C74" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" t="s">
+        <v>22</v>
+      </c>
+      <c r="F74" t="s">
+        <v>20</v>
+      </c>
+      <c r="G74" t="s">
+        <v>21</v>
+      </c>
+      <c r="H74" t="s">
+        <v>22</v>
+      </c>
+      <c r="J74" t="s">
+        <v>20</v>
+      </c>
+      <c r="K74" t="s">
+        <v>21</v>
+      </c>
+      <c r="L74" t="s">
+        <v>22</v>
+      </c>
+      <c r="N74" t="s">
+        <v>20</v>
+      </c>
+      <c r="O74" t="s">
+        <v>21</v>
+      </c>
+      <c r="P74" t="s">
+        <v>22</v>
+      </c>
+      <c r="R74" t="s">
+        <v>20</v>
+      </c>
+      <c r="S74" t="s">
+        <v>21</v>
+      </c>
+      <c r="T74" t="s">
+        <v>22</v>
+      </c>
+      <c r="V74" t="s">
+        <v>20</v>
+      </c>
+      <c r="W74" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75" t="s">
+        <v>24</v>
+      </c>
+      <c r="D75">
+        <v>0.25940000000000002</v>
+      </c>
+      <c r="F75">
+        <v>1</v>
+      </c>
+      <c r="G75" t="s">
+        <v>109</v>
+      </c>
+      <c r="H75">
+        <v>0.55589999999999995</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="K75" t="s">
+        <v>109</v>
+      </c>
+      <c r="L75">
+        <v>0.74070000000000003</v>
+      </c>
+      <c r="N75">
+        <v>1</v>
+      </c>
+      <c r="O75" t="s">
+        <v>30</v>
+      </c>
+      <c r="P75">
+        <v>0.26679999999999998</v>
+      </c>
+      <c r="R75">
+        <v>1</v>
+      </c>
+      <c r="S75" t="s">
+        <v>24</v>
+      </c>
+      <c r="T75">
+        <v>0.34470000000000001</v>
+      </c>
+      <c r="V75">
+        <v>1</v>
+      </c>
+      <c r="W75" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y75">
+        <v>0.94769999999999999</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B76">
+        <v>2</v>
+      </c>
+      <c r="C76" t="s">
+        <v>26</v>
+      </c>
+      <c r="D76">
+        <v>0.2009</v>
+      </c>
+      <c r="F76">
+        <v>2</v>
+      </c>
+      <c r="G76" t="s">
+        <v>28</v>
+      </c>
+      <c r="H76">
+        <v>0.37869999999999998</v>
+      </c>
+      <c r="J76">
+        <v>2</v>
+      </c>
+      <c r="K76" t="s">
+        <v>120</v>
+      </c>
+      <c r="L76">
+        <v>7.9100000000000004E-2</v>
+      </c>
+      <c r="N76">
+        <v>2</v>
+      </c>
+      <c r="O76" t="s">
+        <v>23</v>
+      </c>
+      <c r="P76">
+        <v>0.1653</v>
+      </c>
+      <c r="R76">
+        <v>2</v>
+      </c>
+      <c r="S76" t="s">
+        <v>26</v>
+      </c>
+      <c r="T76">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="V76">
+        <v>2</v>
+      </c>
+      <c r="W76" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y76">
+        <v>3.8100000000000002E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B77">
+        <v>3</v>
+      </c>
+      <c r="C77" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77">
+        <v>0.13469999999999999</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+      <c r="G77" t="s">
+        <v>110</v>
+      </c>
+      <c r="H77">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="J77">
+        <v>3</v>
+      </c>
+      <c r="K77" t="s">
+        <v>27</v>
+      </c>
+      <c r="L77">
+        <v>5.2299999999999999E-2</v>
+      </c>
+      <c r="N77">
+        <v>3</v>
+      </c>
+      <c r="O77" t="s">
+        <v>109</v>
+      </c>
+      <c r="P77">
+        <v>0.16389999999999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77" t="s">
+        <v>107</v>
+      </c>
+      <c r="T77">
+        <v>0.1467</v>
+      </c>
+      <c r="V77">
+        <v>3</v>
+      </c>
+      <c r="W77" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y77">
+        <v>1.24E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B78">
+        <v>4</v>
+      </c>
+      <c r="C78" t="s">
+        <v>121</v>
+      </c>
+      <c r="D78">
+        <v>0.1231</v>
+      </c>
+      <c r="F78">
+        <v>4</v>
+      </c>
+      <c r="G78" t="s">
+        <v>122</v>
+      </c>
+      <c r="H78">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="J78">
+        <v>4</v>
+      </c>
+      <c r="K78" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78">
+        <v>5.0799999999999998E-2</v>
+      </c>
+      <c r="N78">
+        <v>4</v>
+      </c>
+      <c r="O78" t="s">
+        <v>27</v>
+      </c>
+      <c r="P78">
+        <v>0.14410000000000001</v>
+      </c>
+      <c r="R78">
+        <v>4</v>
+      </c>
+      <c r="S78" t="s">
+        <v>27</v>
+      </c>
+      <c r="T78">
+        <v>0.1348</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B79">
+        <v>5</v>
+      </c>
+      <c r="C79" t="s">
+        <v>109</v>
+      </c>
+      <c r="D79">
+        <v>7.2800000000000004E-2</v>
+      </c>
+      <c r="G79" t="s">
+        <v>34</v>
+      </c>
+      <c r="H79">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="J79">
+        <v>5</v>
+      </c>
+      <c r="K79" t="s">
+        <v>44</v>
+      </c>
+      <c r="L79">
+        <v>4.2200000000000001E-2</v>
+      </c>
+      <c r="N79">
+        <v>5</v>
+      </c>
+      <c r="O79" t="s">
+        <v>123</v>
+      </c>
+      <c r="P79">
+        <v>7.6799999999999993E-2</v>
+      </c>
+      <c r="R79">
+        <v>5</v>
+      </c>
+      <c r="S79" t="s">
+        <v>112</v>
+      </c>
+      <c r="T79">
+        <v>5.6500000000000002E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B80">
+        <v>6</v>
+      </c>
+      <c r="C80" t="s">
+        <v>108</v>
+      </c>
+      <c r="D80">
+        <v>4.9599999999999998E-2</v>
+      </c>
+      <c r="J80">
+        <v>6</v>
+      </c>
+      <c r="K80" t="s">
+        <v>113</v>
+      </c>
+      <c r="L80">
+        <v>2.4799999999999999E-2</v>
+      </c>
+      <c r="N80">
+        <v>6</v>
+      </c>
+      <c r="O80" t="s">
+        <v>124</v>
+      </c>
+      <c r="P80">
+        <v>5.2200000000000003E-2</v>
+      </c>
+      <c r="R80">
+        <v>6</v>
+      </c>
+      <c r="S80" t="s">
+        <v>113</v>
+      </c>
+      <c r="T80">
+        <v>2.9499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B81">
+        <v>7</v>
+      </c>
+      <c r="C81" t="s">
+        <v>112</v>
+      </c>
+      <c r="D81">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="K81" t="s">
+        <v>34</v>
+      </c>
+      <c r="L81">
+        <v>1.01E-2</v>
+      </c>
+      <c r="N81">
+        <v>7</v>
+      </c>
+      <c r="O81" t="s">
+        <v>120</v>
+      </c>
+      <c r="P81">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="R81">
+        <v>7</v>
+      </c>
+      <c r="S81" t="s">
+        <v>31</v>
+      </c>
+      <c r="T81">
+        <v>2.0500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B82">
+        <v>8</v>
+      </c>
+      <c r="C82" t="s">
+        <v>30</v>
+      </c>
+      <c r="D82">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="N82">
+        <v>8</v>
+      </c>
+      <c r="O82" t="s">
+        <v>42</v>
+      </c>
+      <c r="P82">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B83">
+        <v>9</v>
+      </c>
+      <c r="C83" t="s">
+        <v>113</v>
+      </c>
+      <c r="D83">
+        <v>2.6800000000000001E-2</v>
+      </c>
+      <c r="N83">
+        <v>9</v>
+      </c>
+      <c r="O83" t="s">
+        <v>113</v>
+      </c>
+      <c r="P83">
+        <v>2.35E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B84">
+        <v>10</v>
+      </c>
+      <c r="C84" t="s">
+        <v>31</v>
+      </c>
+      <c r="D84">
+        <v>1.54E-2</v>
+      </c>
+      <c r="N84">
+        <v>10</v>
+      </c>
+      <c r="O84" t="s">
+        <v>125</v>
+      </c>
+      <c r="P84">
+        <v>2.2599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="C85" t="s">
+        <v>34</v>
+      </c>
+      <c r="D85">
+        <v>4.0899999999999999E-2</v>
+      </c>
+      <c r="O85" t="s">
+        <v>34</v>
+      </c>
+      <c r="P85">
+        <v>7.7000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B86" t="s">
+        <v>126</v>
+      </c>
+      <c r="D86">
+        <v>30854.86</v>
+      </c>
+      <c r="F86" t="s">
+        <v>126</v>
+      </c>
+      <c r="H86">
+        <v>4039.47</v>
+      </c>
+      <c r="J86" t="s">
+        <v>126</v>
+      </c>
+      <c r="L86">
+        <v>1912.89</v>
+      </c>
+      <c r="N86" t="s">
+        <v>126</v>
+      </c>
+      <c r="P86">
+        <v>3935.58</v>
+      </c>
+      <c r="R86" t="s">
+        <v>126</v>
+      </c>
+      <c r="T86">
+        <v>23221.3</v>
+      </c>
+      <c r="V86" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y86">
+        <v>194.08</v>
+      </c>
+    </row>
+    <row r="88" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B88" t="s">
+        <v>127</v>
+      </c>
+      <c r="J88" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B90" t="s">
+        <v>101</v>
+      </c>
+      <c r="F90" t="s">
+        <v>102</v>
+      </c>
+      <c r="J90" t="s">
+        <v>103</v>
+      </c>
+      <c r="N90" t="s">
+        <v>104</v>
+      </c>
+      <c r="R90" t="s">
+        <v>105</v>
+      </c>
+      <c r="V90" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="91" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B91" t="s">
+        <v>20</v>
+      </c>
+      <c r="C91" t="s">
+        <v>21</v>
+      </c>
+      <c r="D91" t="s">
+        <v>22</v>
+      </c>
+      <c r="F91" t="s">
+        <v>20</v>
+      </c>
+      <c r="G91" t="s">
+        <v>21</v>
+      </c>
+      <c r="H91" t="s">
+        <v>22</v>
+      </c>
+      <c r="J91" t="s">
+        <v>20</v>
+      </c>
+      <c r="K91" t="s">
+        <v>21</v>
+      </c>
+      <c r="L91" t="s">
+        <v>22</v>
+      </c>
+      <c r="N91" t="s">
+        <v>20</v>
+      </c>
+      <c r="O91" t="s">
+        <v>21</v>
+      </c>
+      <c r="P91" t="s">
+        <v>22</v>
+      </c>
+      <c r="R91" t="s">
+        <v>20</v>
+      </c>
+      <c r="S91" t="s">
+        <v>21</v>
+      </c>
+      <c r="T91" t="s">
+        <v>22</v>
+      </c>
+      <c r="V91" t="s">
+        <v>20</v>
+      </c>
+      <c r="W91" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92" t="s">
+        <v>24</v>
+      </c>
+      <c r="D92">
+        <v>0.24460000000000001</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92" t="s">
+        <v>109</v>
+      </c>
+      <c r="H92">
+        <v>0.58260000000000001</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92" t="s">
+        <v>109</v>
+      </c>
+      <c r="L92">
+        <v>0.79710000000000003</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="O92" t="s">
+        <v>30</v>
+      </c>
+      <c r="P92">
+        <v>0.29559999999999997</v>
+      </c>
+      <c r="R92">
+        <v>1</v>
+      </c>
+      <c r="S92" t="s">
+        <v>24</v>
+      </c>
+      <c r="T92">
+        <v>0.3992</v>
+      </c>
+      <c r="V92">
+        <v>1</v>
+      </c>
+      <c r="W92" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y92">
+        <v>0.50009999999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B93">
+        <v>2</v>
+      </c>
+      <c r="C93" t="s">
+        <v>121</v>
+      </c>
+      <c r="D93">
+        <v>0.1246</v>
+      </c>
+      <c r="F93">
+        <v>2</v>
+      </c>
+      <c r="G93" t="s">
+        <v>28</v>
+      </c>
+      <c r="H93">
+        <v>0.36980000000000002</v>
+      </c>
+      <c r="J93">
+        <v>2</v>
+      </c>
+      <c r="K93" t="s">
+        <v>121</v>
+      </c>
+      <c r="L93">
+        <v>7.0099999999999996E-2</v>
+      </c>
+      <c r="N93">
+        <v>2</v>
+      </c>
+      <c r="O93" t="s">
+        <v>23</v>
+      </c>
+      <c r="P93">
+        <v>0.1822</v>
+      </c>
+      <c r="R93">
+        <v>2</v>
+      </c>
+      <c r="S93" t="s">
+        <v>26</v>
+      </c>
+      <c r="T93">
+        <v>0.1673</v>
+      </c>
+      <c r="V93">
+        <v>2</v>
+      </c>
+      <c r="W93" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y93">
+        <v>0.2581</v>
+      </c>
+    </row>
+    <row r="94" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B94">
+        <v>3</v>
+      </c>
+      <c r="C94" t="s">
+        <v>23</v>
+      </c>
+      <c r="D94">
+        <v>0.121</v>
+      </c>
+      <c r="F94">
+        <v>3</v>
+      </c>
+      <c r="G94" t="s">
+        <v>110</v>
+      </c>
+      <c r="H94">
+        <v>2.4500000000000001E-2</v>
+      </c>
+      <c r="J94">
+        <v>3</v>
+      </c>
+      <c r="K94" t="s">
+        <v>128</v>
+      </c>
+      <c r="L94">
+        <v>6.1499999999999999E-2</v>
+      </c>
+      <c r="N94">
+        <v>3</v>
+      </c>
+      <c r="O94" t="s">
+        <v>121</v>
+      </c>
+      <c r="P94">
+        <v>0.1671</v>
+      </c>
+      <c r="R94">
+        <v>3</v>
+      </c>
+      <c r="S94" t="s">
+        <v>23</v>
+      </c>
+      <c r="T94">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="V94">
+        <v>3</v>
+      </c>
+      <c r="W94" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y94">
+        <v>8.0600000000000005E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B95">
+        <v>4</v>
+      </c>
+      <c r="C95" t="s">
+        <v>109</v>
+      </c>
+      <c r="D95">
+        <v>0.1205</v>
+      </c>
+      <c r="F95">
+        <v>4</v>
+      </c>
+      <c r="G95" t="s">
+        <v>122</v>
+      </c>
+      <c r="H95">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="J95">
+        <v>4</v>
+      </c>
+      <c r="K95" t="s">
+        <v>124</v>
+      </c>
+      <c r="L95">
+        <v>3.2800000000000003E-2</v>
+      </c>
+      <c r="N95">
+        <v>4</v>
+      </c>
+      <c r="O95" t="s">
+        <v>109</v>
+      </c>
+      <c r="P95">
+        <v>0.107</v>
+      </c>
+      <c r="R95">
+        <v>4</v>
+      </c>
+      <c r="S95" t="s">
+        <v>121</v>
+      </c>
+      <c r="T95">
+        <v>0.14099999999999999</v>
+      </c>
+      <c r="W95" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y95">
+        <v>0.16120000000000001</v>
+      </c>
+    </row>
+    <row r="96" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B96">
+        <v>5</v>
+      </c>
+      <c r="C96" t="s">
+        <v>26</v>
+      </c>
+      <c r="D96">
+        <v>0.10249999999999999</v>
+      </c>
+      <c r="G96" t="s">
+        <v>34</v>
+      </c>
+      <c r="H96">
+        <v>6.1000000000000004E-3</v>
+      </c>
+      <c r="J96">
+        <v>5</v>
+      </c>
+      <c r="K96" t="s">
+        <v>117</v>
+      </c>
+      <c r="L96">
+        <v>2.58E-2</v>
+      </c>
+      <c r="N96">
+        <v>5</v>
+      </c>
+      <c r="O96" t="s">
+        <v>47</v>
+      </c>
+      <c r="P96">
+        <v>9.0300000000000005E-2</v>
+      </c>
+      <c r="R96">
+        <v>5</v>
+      </c>
+      <c r="S96" t="s">
+        <v>113</v>
+      </c>
+      <c r="T96">
+        <v>9.1700000000000004E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B97">
+        <v>6</v>
+      </c>
+      <c r="C97" t="s">
+        <v>28</v>
+      </c>
+      <c r="D97">
+        <v>7.6499999999999999E-2</v>
+      </c>
+      <c r="K97" t="s">
+        <v>34</v>
+      </c>
+      <c r="L97">
+        <v>1.2702545354840276E-2</v>
+      </c>
+      <c r="N97">
+        <v>6</v>
+      </c>
+      <c r="O97" t="s">
+        <v>124</v>
+      </c>
+      <c r="P97">
+        <v>4.41E-2</v>
+      </c>
+      <c r="R97">
+        <v>6</v>
+      </c>
+      <c r="S97" t="s">
+        <v>130</v>
+      </c>
+      <c r="T97">
+        <v>1.9300000000000001E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B98">
+        <v>7</v>
+      </c>
+      <c r="C98" t="s">
+        <v>113</v>
+      </c>
+      <c r="D98">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="N98">
+        <v>7</v>
+      </c>
+      <c r="O98" t="s">
+        <v>128</v>
+      </c>
+      <c r="P98">
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="R98">
+        <v>7</v>
+      </c>
+      <c r="S98" t="s">
+        <v>112</v>
+      </c>
+      <c r="T98">
+        <v>1.8599999999999998E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B99">
+        <v>8</v>
+      </c>
+      <c r="C99" t="s">
+        <v>30</v>
+      </c>
+      <c r="D99">
+        <v>5.2200000000000003E-2</v>
+      </c>
+      <c r="N99">
+        <v>8</v>
+      </c>
+      <c r="O99" t="s">
+        <v>131</v>
+      </c>
+      <c r="P99">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="S99" t="s">
+        <v>34</v>
+      </c>
+      <c r="T99">
+        <v>1.7987389915422605E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B100">
+        <v>9</v>
+      </c>
+      <c r="C100" t="s">
+        <v>47</v>
+      </c>
+      <c r="D100">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="N100">
+        <v>9</v>
+      </c>
+      <c r="O100" t="s">
+        <v>132</v>
+      </c>
+      <c r="P100">
+        <v>1.89E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="C101" t="s">
+        <v>34</v>
+      </c>
+      <c r="D101">
+        <v>8.1100000000000005E-2</v>
+      </c>
+      <c r="O101" t="s">
+        <v>34</v>
+      </c>
+      <c r="P101">
+        <v>3.3092595388729253E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B102" t="s">
+        <v>133</v>
+      </c>
+      <c r="D102">
+        <v>18470.21</v>
+      </c>
+      <c r="F102" t="s">
+        <v>133</v>
+      </c>
+      <c r="H102">
+        <v>3821.49</v>
+      </c>
+      <c r="J102" t="s">
+        <v>133</v>
+      </c>
+      <c r="L102">
+        <v>2277.16</v>
+      </c>
+      <c r="N102" t="s">
+        <v>133</v>
+      </c>
+      <c r="P102">
+        <v>3260.96</v>
+      </c>
+      <c r="R102" t="s">
+        <v>133</v>
+      </c>
+      <c r="T102">
+        <v>11319.04</v>
+      </c>
+      <c r="V102" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y102">
+        <v>124.04</v>
+      </c>
+    </row>
+    <row r="104" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B104" t="s">
+        <v>138</v>
+      </c>
+      <c r="F104" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="106" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B106" t="s">
+        <v>101</v>
+      </c>
+      <c r="F106" t="s">
+        <v>102</v>
+      </c>
+      <c r="J106" t="s">
+        <v>103</v>
+      </c>
+      <c r="N106" t="s">
+        <v>104</v>
+      </c>
+      <c r="R106" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B107" t="s">
+        <v>20</v>
+      </c>
+      <c r="C107" t="s">
+        <v>21</v>
+      </c>
+      <c r="D107" t="s">
+        <v>22</v>
+      </c>
+      <c r="F107" t="s">
+        <v>20</v>
+      </c>
+      <c r="G107" t="s">
+        <v>21</v>
+      </c>
+      <c r="H107" t="s">
+        <v>22</v>
+      </c>
+      <c r="J107" t="s">
+        <v>20</v>
+      </c>
+      <c r="K107" t="s">
+        <v>21</v>
+      </c>
+      <c r="L107" t="s">
+        <v>22</v>
+      </c>
+      <c r="N107" t="s">
+        <v>20</v>
+      </c>
+      <c r="O107" t="s">
+        <v>21</v>
+      </c>
+      <c r="P107" t="s">
+        <v>22</v>
+      </c>
+      <c r="R107" t="s">
+        <v>20</v>
+      </c>
+      <c r="S107" t="s">
+        <v>21</v>
+      </c>
+      <c r="T107" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="108" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B108">
+        <v>1</v>
+      </c>
+      <c r="C108" t="s">
+        <v>24</v>
+      </c>
+      <c r="D108">
+        <v>0.31230000000000002</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="G108" t="s">
+        <v>109</v>
+      </c>
+      <c r="H108">
+        <v>0.6956</v>
+      </c>
+      <c r="J108">
+        <v>1</v>
+      </c>
+      <c r="K108" t="s">
+        <v>109</v>
+      </c>
+      <c r="L108">
+        <v>0.71789999999999998</v>
+      </c>
+      <c r="N108">
+        <v>1</v>
+      </c>
+      <c r="O108" t="s">
+        <v>30</v>
+      </c>
+      <c r="P108">
+        <v>0.2641</v>
+      </c>
+      <c r="R108">
+        <v>1</v>
+      </c>
+      <c r="S108" t="s">
+        <v>24</v>
+      </c>
+      <c r="T108">
+        <v>0.61140000000000005</v>
+      </c>
+    </row>
+    <row r="109" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B109">
+        <v>2</v>
+      </c>
+      <c r="C109" t="s">
+        <v>109</v>
+      </c>
+      <c r="D109">
+        <v>0.15920000000000001</v>
+      </c>
+      <c r="F109">
+        <v>2</v>
+      </c>
+      <c r="G109" t="s">
+        <v>108</v>
+      </c>
+      <c r="H109">
+        <v>0.1862</v>
+      </c>
+      <c r="J109">
+        <v>2</v>
+      </c>
+      <c r="K109" t="s">
+        <v>42</v>
+      </c>
+      <c r="L109">
+        <v>0.10730000000000001</v>
+      </c>
+      <c r="N109">
+        <v>2</v>
+      </c>
+      <c r="O109" t="s">
+        <v>121</v>
+      </c>
+      <c r="P109">
+        <v>0.1852</v>
+      </c>
+      <c r="R109">
+        <v>2</v>
+      </c>
+      <c r="S109" t="s">
+        <v>121</v>
+      </c>
+      <c r="T109">
+        <v>0.1825</v>
+      </c>
+    </row>
+    <row r="110" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B110">
+        <v>3</v>
+      </c>
+      <c r="C110" t="s">
+        <v>121</v>
+      </c>
+      <c r="D110">
+        <v>0.1515</v>
+      </c>
+      <c r="F110">
+        <v>3</v>
+      </c>
+      <c r="G110" t="s">
+        <v>139</v>
+      </c>
+      <c r="H110">
+        <v>8.0500000000000002E-2</v>
+      </c>
+      <c r="J110">
+        <v>3</v>
+      </c>
+      <c r="K110" t="s">
+        <v>120</v>
+      </c>
+      <c r="L110">
+        <v>6.3899999999999998E-2</v>
+      </c>
+      <c r="N110">
+        <v>3</v>
+      </c>
+      <c r="O110" t="s">
+        <v>132</v>
+      </c>
+      <c r="P110">
+        <v>0.161</v>
+      </c>
+      <c r="R110">
+        <v>3</v>
+      </c>
+      <c r="S110" t="s">
+        <v>26</v>
+      </c>
+      <c r="T110">
+        <v>0.1033</v>
+      </c>
+    </row>
+    <row r="111" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B111">
+        <v>4</v>
+      </c>
+      <c r="C111" t="s">
+        <v>30</v>
+      </c>
+      <c r="D111">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="F111">
+        <v>4</v>
+      </c>
+      <c r="G111" t="s">
+        <v>140</v>
+      </c>
+      <c r="H111">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="J111">
+        <v>4</v>
+      </c>
+      <c r="K111" t="s">
+        <v>121</v>
+      </c>
+      <c r="L111">
+        <v>5.33E-2</v>
+      </c>
+      <c r="N111">
+        <v>4</v>
+      </c>
+      <c r="O111" t="s">
+        <v>109</v>
+      </c>
+      <c r="P111">
+        <v>0.13780000000000001</v>
+      </c>
+      <c r="R111">
+        <v>4</v>
+      </c>
+      <c r="S111" t="s">
+        <v>23</v>
+      </c>
+      <c r="T111">
+        <v>3.7199999999999997E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="2:25" x14ac:dyDescent="0.35">
+      <c r="B112">
+        <v>5</v>
+      </c>
+      <c r="C112" t="s">
+        <v>26</v>
+      </c>
+      <c r="D112">
+        <v>5.2699999999999997E-2</v>
+      </c>
+      <c r="G112" t="s">
+        <v>34</v>
+      </c>
+      <c r="H112">
+        <v>2.2599999999999999E-2</v>
+      </c>
+      <c r="J112">
+        <v>5</v>
+      </c>
+      <c r="K112" t="s">
+        <v>44</v>
+      </c>
+      <c r="L112">
+        <v>3.9199999999999999E-2</v>
+      </c>
+      <c r="N112">
+        <v>5</v>
+      </c>
+      <c r="O112" t="s">
+        <v>123</v>
+      </c>
+      <c r="P112">
+        <v>0.1026</v>
+      </c>
+      <c r="R112">
+        <v>5</v>
+      </c>
+      <c r="S112" t="s">
+        <v>141</v>
+      </c>
+      <c r="T112">
+        <v>3.3000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B113">
+        <v>6</v>
+      </c>
+      <c r="C113" t="s">
+        <v>108</v>
+      </c>
+      <c r="D113">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="K113" t="s">
+        <v>34</v>
+      </c>
+      <c r="L113">
+        <v>1.83E-2</v>
+      </c>
+      <c r="N113">
+        <v>6</v>
+      </c>
+      <c r="O113" t="s">
+        <v>141</v>
+      </c>
+      <c r="P113">
+        <v>6.2300000000000001E-2</v>
+      </c>
+      <c r="S113" t="s">
+        <v>34</v>
+      </c>
+      <c r="T113">
+        <v>3.27E-2</v>
+      </c>
+    </row>
+    <row r="114" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B114">
+        <v>7</v>
+      </c>
+      <c r="C114" t="s">
+        <v>132</v>
+      </c>
+      <c r="D114">
+        <v>3.9600000000000003E-2</v>
+      </c>
+      <c r="N114">
+        <v>7</v>
+      </c>
+      <c r="O114" t="s">
+        <v>23</v>
+      </c>
+      <c r="P114">
+        <v>4.8099999999999997E-2</v>
+      </c>
+    </row>
+    <row r="115" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B115">
+        <v>8</v>
+      </c>
+      <c r="C115" t="s">
+        <v>141</v>
+      </c>
+      <c r="D115">
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="N115">
+        <v>8</v>
+      </c>
+      <c r="O115" t="s">
+        <v>44</v>
+      </c>
+      <c r="P115">
+        <v>1.89E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B116">
+        <v>9</v>
+      </c>
+      <c r="C116" t="s">
+        <v>23</v>
+      </c>
+      <c r="D116">
+        <v>3.0599999999999999E-2</v>
+      </c>
+      <c r="O116" t="s">
+        <v>34</v>
+      </c>
+      <c r="P116">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="117" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B117">
+        <v>10</v>
+      </c>
+      <c r="C117" t="s">
+        <v>123</v>
+      </c>
+      <c r="D117">
+        <v>2.9600000000000001E-2</v>
+      </c>
+    </row>
+    <row r="118" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B118">
+        <v>11</v>
+      </c>
+      <c r="C118" t="s">
+        <v>139</v>
+      </c>
+      <c r="D118">
+        <v>1.84E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B119">
+        <v>12</v>
+      </c>
+      <c r="C119" t="s">
+        <v>42</v>
+      </c>
+      <c r="D119">
+        <v>1.7399999999999999E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="C120" t="s">
+        <v>34</v>
+      </c>
+      <c r="D120">
+        <v>4.65E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B121" t="s">
+        <v>142</v>
+      </c>
+      <c r="D121">
+        <v>11583.952555</v>
+      </c>
+      <c r="F121" t="s">
+        <v>142</v>
+      </c>
+      <c r="H121">
+        <v>2651.4248549999998</v>
+      </c>
+      <c r="J121" t="s">
+        <v>142</v>
+      </c>
+      <c r="L121">
+        <v>1876.7811999999999</v>
+      </c>
+      <c r="N121" t="s">
+        <v>142</v>
+      </c>
+      <c r="P121">
+        <v>2807.2974000000004</v>
+      </c>
+      <c r="R121" t="s">
+        <v>142</v>
+      </c>
+      <c r="T121">
+        <v>5917.5950000000003</v>
+      </c>
+    </row>
+    <row r="123" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B123" t="s">
+        <v>145</v>
+      </c>
+      <c r="K123" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="125" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B125" t="s">
+        <v>101</v>
+      </c>
+      <c r="F125" t="s">
+        <v>102</v>
+      </c>
+      <c r="J125" t="s">
+        <v>103</v>
+      </c>
+      <c r="N125" t="s">
+        <v>104</v>
+      </c>
+      <c r="R125" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="126" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B126" t="s">
+        <v>20</v>
+      </c>
+      <c r="C126" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126" t="s">
+        <v>22</v>
+      </c>
+      <c r="F126" t="s">
+        <v>20</v>
+      </c>
+      <c r="G126" t="s">
+        <v>21</v>
+      </c>
+      <c r="H126" t="s">
+        <v>22</v>
+      </c>
+      <c r="J126" t="s">
+        <v>20</v>
+      </c>
+      <c r="K126" t="s">
+        <v>21</v>
+      </c>
+      <c r="L126" t="s">
+        <v>22</v>
+      </c>
+      <c r="N126" t="s">
+        <v>20</v>
+      </c>
+      <c r="O126" t="s">
+        <v>21</v>
+      </c>
+      <c r="P126" t="s">
+        <v>22</v>
+      </c>
+      <c r="R126" t="s">
+        <v>20</v>
+      </c>
+      <c r="S126" t="s">
+        <v>21</v>
+      </c>
+      <c r="T126" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="127" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B127">
+        <v>1</v>
+      </c>
+      <c r="C127" t="s">
+        <v>121</v>
+      </c>
+      <c r="D127">
+        <v>0.19</v>
+      </c>
+      <c r="F127">
+        <v>1</v>
+      </c>
+      <c r="G127" t="s">
+        <v>109</v>
+      </c>
+      <c r="H127">
+        <v>0.62</v>
+      </c>
+      <c r="J127">
+        <v>1</v>
+      </c>
+      <c r="K127" t="s">
+        <v>109</v>
+      </c>
+      <c r="L127">
+        <v>0.63</v>
+      </c>
+      <c r="N127">
+        <v>1</v>
+      </c>
+      <c r="O127" t="s">
+        <v>121</v>
+      </c>
+      <c r="P127">
+        <v>0.22</v>
+      </c>
+      <c r="R127">
+        <v>1</v>
+      </c>
+      <c r="S127" t="s">
+        <v>24</v>
+      </c>
+      <c r="T127">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="128" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B128">
+        <v>2</v>
+      </c>
+      <c r="C128" t="s">
+        <v>24</v>
+      </c>
+      <c r="D128">
+        <v>0.18</v>
+      </c>
+      <c r="F128">
+        <v>2</v>
+      </c>
+      <c r="G128" t="s">
+        <v>108</v>
+      </c>
+      <c r="H128">
+        <v>0.25</v>
+      </c>
+      <c r="J128">
+        <v>2</v>
+      </c>
+      <c r="K128" t="s">
+        <v>128</v>
+      </c>
+      <c r="L128">
+        <v>0.11</v>
+      </c>
+      <c r="N128">
+        <v>2</v>
+      </c>
+      <c r="O128" t="s">
+        <v>132</v>
+      </c>
+      <c r="P128">
+        <v>0.18</v>
+      </c>
+      <c r="R128">
+        <v>2</v>
+      </c>
+      <c r="S128" t="s">
+        <v>121</v>
+      </c>
+      <c r="T128">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="129" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B129">
+        <v>3</v>
+      </c>
+      <c r="C129" t="s">
+        <v>109</v>
+      </c>
+      <c r="D129">
+        <v>0.13</v>
+      </c>
+      <c r="F129">
+        <v>3</v>
+      </c>
+      <c r="G129" t="s">
+        <v>143</v>
+      </c>
+      <c r="H129">
+        <v>0.09</v>
+      </c>
+      <c r="J129">
+        <v>3</v>
+      </c>
+      <c r="K129" t="s">
+        <v>121</v>
+      </c>
+      <c r="L129">
+        <v>0.09</v>
+      </c>
+      <c r="N129">
+        <v>3</v>
+      </c>
+      <c r="O129" t="s">
+        <v>30</v>
+      </c>
+      <c r="P129">
+        <v>0.16</v>
+      </c>
+      <c r="R129">
+        <v>3</v>
+      </c>
+      <c r="S129" t="s">
+        <v>141</v>
+      </c>
+      <c r="T129">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="130" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B130">
+        <v>4</v>
+      </c>
+      <c r="C130" t="s">
+        <v>141</v>
+      </c>
+      <c r="D130">
+        <v>0.06</v>
+      </c>
+      <c r="G130" t="s">
+        <v>34</v>
+      </c>
+      <c r="H130">
+        <v>0.03</v>
+      </c>
+      <c r="J130">
+        <v>4</v>
+      </c>
+      <c r="K130" t="s">
+        <v>135</v>
+      </c>
+      <c r="L130">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="N130">
+        <v>4</v>
+      </c>
+      <c r="O130" t="s">
+        <v>123</v>
+      </c>
+      <c r="P130">
+        <v>0.12</v>
+      </c>
+      <c r="R130">
+        <v>4</v>
+      </c>
+      <c r="S130" t="s">
+        <v>136</v>
+      </c>
+      <c r="T130">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="131" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B131">
+        <v>5</v>
+      </c>
+      <c r="C131" t="s">
+        <v>108</v>
+      </c>
+      <c r="D131">
+        <v>0.05</v>
+      </c>
+      <c r="J131">
+        <v>5</v>
+      </c>
+      <c r="K131" t="s">
+        <v>44</v>
+      </c>
+      <c r="L131">
+        <v>0.03</v>
+      </c>
+      <c r="N131">
+        <v>5</v>
+      </c>
+      <c r="O131" t="s">
+        <v>109</v>
+      </c>
+      <c r="P131">
+        <v>0.1</v>
+      </c>
+      <c r="R131">
+        <v>5</v>
+      </c>
+      <c r="S131" t="s">
+        <v>26</v>
+      </c>
+      <c r="T131">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="132" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B132">
+        <v>6</v>
+      </c>
+      <c r="C132" t="s">
+        <v>136</v>
+      </c>
+      <c r="D132">
+        <v>0.05</v>
+      </c>
+      <c r="J132">
+        <v>6</v>
+      </c>
+      <c r="K132" t="s">
+        <v>144</v>
+      </c>
+      <c r="L132">
+        <v>0.03</v>
+      </c>
+      <c r="N132">
+        <v>6</v>
+      </c>
+      <c r="O132" t="s">
+        <v>144</v>
+      </c>
+      <c r="P132">
+        <v>0.05</v>
+      </c>
+      <c r="R132">
+        <v>6</v>
+      </c>
+      <c r="S132" t="s">
+        <v>137</v>
+      </c>
+      <c r="T132">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="133" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B133">
+        <v>7</v>
+      </c>
+      <c r="C133" t="s">
+        <v>132</v>
+      </c>
+      <c r="D133">
+        <v>0.04</v>
+      </c>
+      <c r="K133" t="s">
+        <v>34</v>
+      </c>
+      <c r="L133">
+        <v>0.04</v>
+      </c>
+      <c r="N133">
+        <v>7</v>
+      </c>
+      <c r="O133" t="s">
+        <v>23</v>
+      </c>
+      <c r="P133">
+        <v>0.04</v>
+      </c>
+      <c r="R133">
+        <v>7</v>
+      </c>
+      <c r="S133" t="s">
+        <v>23</v>
+      </c>
+      <c r="T133">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="134" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B134">
+        <v>8</v>
+      </c>
+      <c r="C134" t="s">
+        <v>123</v>
+      </c>
+      <c r="D134">
+        <v>0.04</v>
+      </c>
+      <c r="N134">
+        <v>8</v>
+      </c>
+      <c r="O134" t="s">
+        <v>44</v>
+      </c>
+      <c r="P134">
+        <v>0.04</v>
+      </c>
+      <c r="R134">
+        <v>8</v>
+      </c>
+      <c r="S134" t="s">
+        <v>123</v>
+      </c>
+      <c r="T134">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="135" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B135">
+        <v>9</v>
+      </c>
+      <c r="C135" t="s">
+        <v>26</v>
+      </c>
+      <c r="D135">
+        <v>0.04</v>
+      </c>
+      <c r="N135">
+        <v>9</v>
+      </c>
+      <c r="O135" t="s">
+        <v>135</v>
+      </c>
+      <c r="P135">
+        <v>0.02</v>
+      </c>
+      <c r="S135" t="s">
+        <v>34</v>
+      </c>
+      <c r="T135">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="136" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B136">
+        <v>10</v>
+      </c>
+      <c r="C136" t="s">
+        <v>30</v>
+      </c>
+      <c r="D136">
+        <v>0.04</v>
+      </c>
+      <c r="O136" t="s">
+        <v>34</v>
+      </c>
+      <c r="P136">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="137" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B137">
+        <v>11</v>
+      </c>
+      <c r="C137" t="s">
+        <v>144</v>
+      </c>
+      <c r="D137">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="138" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B138">
+        <v>12</v>
+      </c>
+      <c r="C138" t="s">
+        <v>23</v>
+      </c>
+      <c r="D138">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="139" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B139">
+        <v>13</v>
+      </c>
+      <c r="C139" t="s">
+        <v>137</v>
+      </c>
+      <c r="D139">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="140" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B140">
+        <v>14</v>
+      </c>
+      <c r="C140" t="s">
+        <v>143</v>
+      </c>
+      <c r="D140">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="141" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B141">
+        <v>15</v>
+      </c>
+      <c r="C141" t="s">
+        <v>128</v>
+      </c>
+      <c r="D141">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="142" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B142">
+        <v>16</v>
+      </c>
+      <c r="C142" t="s">
+        <v>135</v>
+      </c>
+      <c r="D142">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="143" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="C143" t="s">
+        <v>34</v>
+      </c>
+      <c r="D143">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="144" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B144" t="s">
+        <v>146</v>
+      </c>
+      <c r="D144">
+        <v>9600</v>
+      </c>
+      <c r="F144" t="s">
+        <v>146</v>
+      </c>
+      <c r="H144">
+        <v>2064</v>
+      </c>
+      <c r="J144" t="s">
+        <v>146</v>
+      </c>
+      <c r="L144">
+        <v>1664</v>
+      </c>
+      <c r="N144" t="s">
+        <v>146</v>
+      </c>
+      <c r="P144">
+        <v>2283</v>
+      </c>
+      <c r="R144" t="s">
+        <v>146</v>
+      </c>
+      <c r="T144">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="147" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B147" t="s">
+        <v>148</v>
+      </c>
+      <c r="G147" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="149" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B149" t="s">
+        <v>101</v>
+      </c>
+      <c r="F149" t="s">
+        <v>102</v>
+      </c>
+      <c r="J149" t="s">
+        <v>103</v>
+      </c>
+      <c r="N149" t="s">
+        <v>104</v>
+      </c>
+      <c r="R149" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="150" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B150" t="s">
+        <v>20</v>
+      </c>
+      <c r="C150" t="s">
+        <v>21</v>
+      </c>
+      <c r="D150" t="s">
+        <v>22</v>
+      </c>
+      <c r="F150" t="s">
+        <v>20</v>
+      </c>
+      <c r="G150" t="s">
+        <v>21</v>
+      </c>
+      <c r="H150" t="s">
+        <v>22</v>
+      </c>
+      <c r="J150" t="s">
+        <v>20</v>
+      </c>
+      <c r="K150" t="s">
+        <v>21</v>
+      </c>
+      <c r="L150" t="s">
+        <v>22</v>
+      </c>
+      <c r="N150" t="s">
+        <v>20</v>
+      </c>
+      <c r="O150" t="s">
+        <v>21</v>
+      </c>
+      <c r="P150" t="s">
+        <v>22</v>
+      </c>
+      <c r="R150" t="s">
+        <v>20</v>
+      </c>
+      <c r="S150" t="s">
+        <v>21</v>
+      </c>
+      <c r="T150" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="151" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B151">
+        <v>1</v>
+      </c>
+      <c r="C151" t="s">
+        <v>121</v>
+      </c>
+      <c r="D151">
+        <v>0.26</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="G151" t="s">
+        <v>109</v>
+      </c>
+      <c r="H151">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J151">
+        <v>1</v>
+      </c>
+      <c r="K151" t="s">
+        <v>109</v>
+      </c>
+      <c r="L151">
+        <v>0.48</v>
+      </c>
+      <c r="N151">
+        <v>1</v>
+      </c>
+      <c r="O151" t="s">
+        <v>121</v>
+      </c>
+      <c r="P151">
+        <v>0.32</v>
+      </c>
+      <c r="R151">
+        <v>1</v>
+      </c>
+      <c r="S151" t="s">
+        <v>121</v>
+      </c>
+      <c r="T151">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="152" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B152">
+        <v>2</v>
+      </c>
+      <c r="C152" t="s">
+        <v>24</v>
+      </c>
+      <c r="D152">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F152">
+        <v>2</v>
+      </c>
+      <c r="G152" t="s">
+        <v>108</v>
+      </c>
+      <c r="H152">
+        <v>0.32</v>
+      </c>
+      <c r="J152">
+        <v>2</v>
+      </c>
+      <c r="K152" t="s">
+        <v>135</v>
+      </c>
+      <c r="L152">
+        <v>0.23</v>
+      </c>
+      <c r="N152">
+        <v>2</v>
+      </c>
+      <c r="O152" t="s">
+        <v>123</v>
+      </c>
+      <c r="P152">
+        <v>0.17</v>
+      </c>
+      <c r="R152">
+        <v>2</v>
+      </c>
+      <c r="S152" t="s">
+        <v>24</v>
+      </c>
+      <c r="T152">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="153" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B153">
+        <v>3</v>
+      </c>
+      <c r="C153" t="s">
+        <v>26</v>
+      </c>
+      <c r="D153">
+        <v>0.12</v>
+      </c>
+      <c r="F153">
+        <v>3</v>
+      </c>
+      <c r="G153" t="s">
+        <v>143</v>
+      </c>
+      <c r="H153">
+        <v>0.06</v>
+      </c>
+      <c r="J153">
+        <v>3</v>
+      </c>
+      <c r="K153" t="s">
+        <v>121</v>
+      </c>
+      <c r="L153">
+        <v>0.12</v>
+      </c>
+      <c r="N153">
+        <v>3</v>
+      </c>
+      <c r="O153" t="s">
+        <v>109</v>
+      </c>
+      <c r="P153">
+        <v>0.1</v>
+      </c>
+      <c r="R153">
+        <v>3</v>
+      </c>
+      <c r="S153" t="s">
+        <v>26</v>
+      </c>
+      <c r="T153">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="154" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B154">
+        <v>4</v>
+      </c>
+      <c r="C154" t="s">
+        <v>112</v>
+      </c>
+      <c r="D154">
+        <v>0.11</v>
+      </c>
+      <c r="F154">
+        <v>4</v>
+      </c>
+      <c r="G154" t="s">
+        <v>122</v>
+      </c>
+      <c r="H154">
+        <v>0.02</v>
+      </c>
+      <c r="J154">
+        <v>4</v>
+      </c>
+      <c r="K154" t="s">
+        <v>44</v>
+      </c>
+      <c r="L154">
+        <v>0.09</v>
+      </c>
+      <c r="N154">
+        <v>4</v>
+      </c>
+      <c r="O154" t="s">
+        <v>132</v>
+      </c>
+      <c r="P154">
+        <v>0.09</v>
+      </c>
+      <c r="R154">
+        <v>4</v>
+      </c>
+      <c r="S154" t="s">
+        <v>112</v>
+      </c>
+      <c r="T154">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="155" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B155">
+        <v>5</v>
+      </c>
+      <c r="C155" t="s">
+        <v>109</v>
+      </c>
+      <c r="D155">
+        <v>0.08</v>
+      </c>
+      <c r="F155">
+        <v>5</v>
+      </c>
+      <c r="G155" t="s">
+        <v>150</v>
+      </c>
+      <c r="H155">
+        <v>0.02</v>
+      </c>
+      <c r="J155">
+        <v>5</v>
+      </c>
+      <c r="K155" t="s">
+        <v>144</v>
+      </c>
+      <c r="L155">
+        <v>0.03</v>
+      </c>
+      <c r="N155">
+        <v>5</v>
+      </c>
+      <c r="O155" t="s">
+        <v>30</v>
+      </c>
+      <c r="P155">
+        <v>0.08</v>
+      </c>
+      <c r="R155">
+        <v>5</v>
+      </c>
+      <c r="S155" t="s">
+        <v>136</v>
+      </c>
+      <c r="T155">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="156" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B156">
+        <v>6</v>
+      </c>
+      <c r="C156" t="s">
+        <v>136</v>
+      </c>
+      <c r="D156">
+        <v>0.04</v>
+      </c>
+      <c r="G156" t="s">
+        <v>34</v>
+      </c>
+      <c r="H156">
+        <v>0.01</v>
+      </c>
+      <c r="K156" t="s">
+        <v>34</v>
+      </c>
+      <c r="L156">
+        <v>0.05</v>
+      </c>
+      <c r="N156">
+        <v>6</v>
+      </c>
+      <c r="O156" t="s">
+        <v>44</v>
+      </c>
+      <c r="P156">
+        <v>0.06</v>
+      </c>
+      <c r="R156">
+        <v>6</v>
+      </c>
+      <c r="S156" t="s">
+        <v>141</v>
+      </c>
+      <c r="T156">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="157" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B157">
+        <v>7</v>
+      </c>
+      <c r="C157" t="s">
+        <v>108</v>
+      </c>
+      <c r="D157">
+        <v>0.04</v>
+      </c>
+      <c r="N157">
+        <v>7</v>
+      </c>
+      <c r="O157" t="s">
+        <v>23</v>
+      </c>
+      <c r="P157">
+        <v>0.06</v>
+      </c>
+      <c r="R157">
+        <v>7</v>
+      </c>
+      <c r="S157" t="s">
+        <v>123</v>
+      </c>
+      <c r="T157">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="158" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B158">
+        <v>8</v>
+      </c>
+      <c r="C158" t="s">
+        <v>123</v>
+      </c>
+      <c r="D158">
+        <v>0.04</v>
+      </c>
+      <c r="N158">
+        <v>8</v>
+      </c>
+      <c r="O158" t="s">
+        <v>144</v>
+      </c>
+      <c r="P158">
+        <v>0.02</v>
+      </c>
+      <c r="S158" t="s">
+        <v>34</v>
+      </c>
+      <c r="T158">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="159" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B159">
+        <v>9</v>
+      </c>
+      <c r="C159" t="s">
+        <v>149</v>
+      </c>
+      <c r="D159">
+        <v>0.04</v>
+      </c>
+      <c r="O159" t="s">
+        <v>34</v>
+      </c>
+      <c r="P159">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="160" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B160">
+        <v>10</v>
+      </c>
+      <c r="C160" t="s">
+        <v>141</v>
+      </c>
+      <c r="D160">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="161" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B161">
+        <v>11</v>
+      </c>
+      <c r="C161" t="s">
+        <v>44</v>
+      </c>
+      <c r="D161">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="162" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="C162" t="s">
+        <v>34</v>
+      </c>
+      <c r="D162">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="163" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B163" t="s">
+        <v>151</v>
+      </c>
+      <c r="D163">
+        <v>13817</v>
+      </c>
+      <c r="F163" t="s">
+        <v>151</v>
+      </c>
+      <c r="H163">
+        <v>1923</v>
+      </c>
+      <c r="J163" t="s">
+        <v>151</v>
+      </c>
+      <c r="L163">
+        <v>1829</v>
+      </c>
+      <c r="N163" t="s">
+        <v>151</v>
+      </c>
+      <c r="P163">
+        <v>2025</v>
+      </c>
+      <c r="R163" t="s">
+        <v>151</v>
+      </c>
+      <c r="T163">
+        <v>9194</v>
+      </c>
+    </row>
+    <row r="165" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B165" t="s">
+        <v>152</v>
+      </c>
+      <c r="G165" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="167" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B167" t="s">
+        <v>101</v>
+      </c>
+      <c r="F167" t="s">
+        <v>102</v>
+      </c>
+      <c r="J167" t="s">
+        <v>103</v>
+      </c>
+      <c r="N167" t="s">
+        <v>104</v>
+      </c>
+      <c r="R167" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="168" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B168" t="s">
+        <v>20</v>
+      </c>
+      <c r="C168" t="s">
+        <v>21</v>
+      </c>
+      <c r="D168" t="s">
+        <v>22</v>
+      </c>
+      <c r="F168" t="s">
+        <v>20</v>
+      </c>
+      <c r="G168" t="s">
+        <v>21</v>
+      </c>
+      <c r="H168" t="s">
+        <v>22</v>
+      </c>
+      <c r="J168" t="s">
+        <v>20</v>
+      </c>
+      <c r="K168" t="s">
+        <v>21</v>
+      </c>
+      <c r="L168" t="s">
+        <v>22</v>
+      </c>
+      <c r="N168" t="s">
+        <v>20</v>
+      </c>
+      <c r="O168" t="s">
+        <v>21</v>
+      </c>
+      <c r="P168" t="s">
+        <v>22</v>
+      </c>
+      <c r="R168" t="s">
+        <v>20</v>
+      </c>
+      <c r="S168" t="s">
+        <v>21</v>
+      </c>
+      <c r="T168" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="169" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B169">
+        <v>1</v>
+      </c>
+      <c r="C169" t="s">
+        <v>121</v>
+      </c>
+      <c r="D169">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F169">
+        <v>1</v>
+      </c>
+      <c r="G169" t="s">
+        <v>109</v>
+      </c>
+      <c r="H169">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J169">
+        <v>1</v>
+      </c>
+      <c r="K169" t="s">
+        <v>109</v>
+      </c>
+      <c r="L169">
+        <v>0.38</v>
+      </c>
+      <c r="N169">
+        <v>1</v>
+      </c>
+      <c r="O169" t="s">
+        <v>123</v>
+      </c>
+      <c r="P169">
+        <v>0.36</v>
+      </c>
+      <c r="R169">
+        <v>1</v>
+      </c>
+      <c r="S169" t="s">
+        <v>121</v>
+      </c>
+      <c r="T169">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="170" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B170">
+        <v>2</v>
+      </c>
+      <c r="C170" t="s">
+        <v>26</v>
+      </c>
+      <c r="D170">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F170">
+        <v>2</v>
+      </c>
+      <c r="G170" t="s">
+        <v>108</v>
+      </c>
+      <c r="H170">
+        <v>0.39</v>
+      </c>
+      <c r="J170">
+        <v>2</v>
+      </c>
+      <c r="K170" t="s">
+        <v>149</v>
+      </c>
+      <c r="L170">
+        <v>0.26</v>
+      </c>
+      <c r="N170">
+        <v>2</v>
+      </c>
+      <c r="O170" t="s">
+        <v>121</v>
+      </c>
+      <c r="P170">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="R170">
+        <v>2</v>
+      </c>
+      <c r="S170" t="s">
+        <v>26</v>
+      </c>
+      <c r="T170">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="171" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B171">
+        <v>3</v>
+      </c>
+      <c r="C171" t="s">
+        <v>112</v>
+      </c>
+      <c r="D171">
+        <v>0.12</v>
+      </c>
+      <c r="F171">
+        <v>3</v>
+      </c>
+      <c r="G171" t="s">
+        <v>122</v>
+      </c>
+      <c r="H171">
+        <v>0.02</v>
+      </c>
+      <c r="J171">
+        <v>3</v>
+      </c>
+      <c r="K171" t="s">
+        <v>121</v>
+      </c>
+      <c r="L171">
+        <v>0.2</v>
+      </c>
+      <c r="N171">
+        <v>3</v>
+      </c>
+      <c r="O171" t="s">
+        <v>30</v>
+      </c>
+      <c r="P171">
+        <v>0.12</v>
+      </c>
+      <c r="R171">
+        <v>3</v>
+      </c>
+      <c r="S171" t="s">
+        <v>24</v>
+      </c>
+      <c r="T171">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="172" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B172">
+        <v>4</v>
+      </c>
+      <c r="C172" t="s">
+        <v>149</v>
+      </c>
+      <c r="D172">
+        <v>0.09</v>
+      </c>
+      <c r="F172">
+        <v>4</v>
+      </c>
+      <c r="G172" t="s">
+        <v>147</v>
+      </c>
+      <c r="H172">
+        <v>0.01</v>
+      </c>
+      <c r="J172">
+        <v>4</v>
+      </c>
+      <c r="K172" t="s">
+        <v>44</v>
+      </c>
+      <c r="L172">
+        <v>0.13</v>
+      </c>
+      <c r="N172">
+        <v>4</v>
+      </c>
+      <c r="O172" t="s">
+        <v>44</v>
+      </c>
+      <c r="P172">
+        <v>0.09</v>
+      </c>
+      <c r="R172">
+        <v>4</v>
+      </c>
+      <c r="S172" t="s">
+        <v>141</v>
+      </c>
+      <c r="T172">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="173" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B173">
+        <v>5</v>
+      </c>
+      <c r="C173" t="s">
+        <v>109</v>
+      </c>
+      <c r="D173">
+        <v>0.09</v>
+      </c>
+      <c r="G173" t="s">
+        <v>34</v>
+      </c>
+      <c r="H173">
+        <v>0.02</v>
+      </c>
+      <c r="J173">
+        <v>5</v>
+      </c>
+      <c r="K173" t="s">
+        <v>42</v>
+      </c>
+      <c r="L173">
+        <v>0.02</v>
+      </c>
+      <c r="N173">
+        <v>5</v>
+      </c>
+      <c r="O173" t="s">
+        <v>109</v>
+      </c>
+      <c r="P173">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="R173">
+        <v>5</v>
+      </c>
+      <c r="S173" t="s">
+        <v>112</v>
+      </c>
+      <c r="T173">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="174" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B174">
+        <v>6</v>
+      </c>
+      <c r="C174" t="s">
+        <v>24</v>
+      </c>
+      <c r="D174">
+        <v>0.06</v>
+      </c>
+      <c r="J174">
+        <v>6</v>
+      </c>
+      <c r="K174" t="s">
+        <v>123</v>
+      </c>
+      <c r="L174">
+        <v>0.01</v>
+      </c>
+      <c r="N174">
+        <v>6</v>
+      </c>
+      <c r="O174" t="s">
+        <v>149</v>
+      </c>
+      <c r="P174">
+        <v>0.04</v>
+      </c>
+      <c r="R174">
+        <v>6</v>
+      </c>
+      <c r="S174" t="s">
+        <v>149</v>
+      </c>
+      <c r="T174">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="175" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B175">
+        <v>7</v>
+      </c>
+      <c r="C175" t="s">
+        <v>108</v>
+      </c>
+      <c r="D175">
+        <v>0.06</v>
+      </c>
+      <c r="K175" t="s">
+        <v>34</v>
+      </c>
+      <c r="L175">
+        <v>0.02</v>
+      </c>
+      <c r="O175" t="s">
+        <v>34</v>
+      </c>
+      <c r="P175">
+        <v>0.05</v>
+      </c>
+      <c r="R175">
+        <v>7</v>
+      </c>
+      <c r="S175" t="s">
+        <v>123</v>
+      </c>
+      <c r="T175">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="176" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B176">
+        <v>8</v>
+      </c>
+      <c r="C176" t="s">
+        <v>123</v>
+      </c>
+      <c r="D176">
+        <v>0.05</v>
+      </c>
+      <c r="S176" t="s">
+        <v>34</v>
+      </c>
+      <c r="T176">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="177" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B177">
+        <v>9</v>
+      </c>
+      <c r="C177" t="s">
+        <v>141</v>
+      </c>
+      <c r="D177">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="178" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B178">
+        <v>10</v>
+      </c>
+      <c r="C178" t="s">
+        <v>44</v>
+      </c>
+      <c r="D178">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="179" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="C179" t="s">
+        <v>34</v>
+      </c>
+      <c r="D179">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="180" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B180" t="s">
+        <v>153</v>
+      </c>
+      <c r="D180">
+        <v>9904</v>
+      </c>
+      <c r="F180" t="s">
+        <v>153</v>
+      </c>
+      <c r="H180">
+        <v>1516</v>
+      </c>
+      <c r="J180" t="s">
+        <v>153</v>
+      </c>
+      <c r="L180">
+        <v>2120</v>
+      </c>
+      <c r="N180" t="s">
+        <v>153</v>
+      </c>
+      <c r="P180">
+        <v>1105</v>
+      </c>
+      <c r="R180" t="s">
+        <v>153</v>
+      </c>
+      <c r="T180">
+        <v>6190</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="I1:K1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ProcessName xmlns="d382aed9-cc96-421a-b6d1-bad087b40ea5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d382aed9-cc96-421a-b6d1-bad087b40ea5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3c3bb480-5c86-45a4-be90-daa3829a93c5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E1D7978D1E43DE4EA43DBD7340A406DC" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d2a0579b8367a5d14f15657bceede69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d382aed9-cc96-421a-b6d1-bad087b40ea5" xmlns:ns3="3c3bb480-5c86-45a4-be90-daa3829a93c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6184784662eaf13c68ab2ee7ade41035" ns2:_="" ns3:_="">
     <xsd:import namespace="d382aed9-cc96-421a-b6d1-bad087b40ea5"/>
@@ -3925,28 +8376,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2355CD45-2F25-4965-9590-C756C8D0B153}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3c3bb480-5c86-45a4-be90-daa3829a93c5"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="d382aed9-cc96-421a-b6d1-bad087b40ea5"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ProcessName xmlns="d382aed9-cc96-421a-b6d1-bad087b40ea5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d382aed9-cc96-421a-b6d1-bad087b40ea5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3c3bb480-5c86-45a4-be90-daa3829a93c5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D15763B-BC3F-44A0-B84D-0D65F1925A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A8357D9-61C4-4864-BD66-2D2D973EC6D9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3965,31 +8420,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D15763B-BC3F-44A0-B84D-0D65F1925A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2355CD45-2F25-4965-9590-C756C8D0B153}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3c3bb480-5c86-45a4-be90-daa3829a93c5"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="d382aed9-cc96-421a-b6d1-bad087b40ea5"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{95965d95-ecc0-4720-b759-1f33c42ed7da}" enabled="1" method="Standard" siteId="{a0f29d7e-28cd-4f54-8442-7885aee7c080}" removed="0"/>

--- a/PV_ICE/baselines/SupportingMaterial/Manual Files/Inverter_Gallium_Calcs.xlsx
+++ b/PV_ICE/baselines/SupportingMaterial/Manual Files/Inverter_Gallium_Calcs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmirletz\Documents\GitHub\PV_ICE\PV_ICE\baselines\SupportingMaterial\Manual Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88992C6D-401F-44DD-826C-B4DE42E15A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9BC423E-1638-441F-9E90-A5B8A3074F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -949,7 +949,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -1001,9 +1001,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1011,7 +1008,6 @@
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1019,6 +1015,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1046,10 +1045,1290 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1320" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Gallium Use in PV Inverters</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1320" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.26129702537182853"/>
+          <c:y val="0.18814900449272512"/>
+          <c:w val="0.71019400699912516"/>
+          <c:h val="0.62334153143547666"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Maths!$Y$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Micro [kg/MWac]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Maths!$A$32:$A$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2028</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Maths!$Y$32:$Y$42</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>6.719681908548706E-9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.4292779426310583E-9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.1448091662150651E-8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.7022562449637387E-8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.13058659217877E-8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.1171960946094613E-8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.016428288953335E-7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.3882369508073601E-7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.9402553922730501E-7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.1722978699361545E-7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.4993922204213932E-7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7C6F-4036-B9B4-EEAA82DBCA58}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Maths!$Z$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>String [kg/MWac]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Maths!$A$32:$A$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2028</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Maths!$Z$32:$Z$42</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>6.4508946322067576E-10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.1721068249258161E-10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0990167995664627E-9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.6341659951651892E-9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.9653631284916193E-9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.8325082508250815E-9</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.7577115739520142E-9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.3327074727750655E-8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.862645176582128E-8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.085405955138708E-8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.3994165316045373E-8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7C6F-4036-B9B4-EEAA82DBCA58}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Maths!$AA$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Utility [kg/MWac]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Maths!$A$32:$A$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2019</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2024</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2025</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2026</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2027</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2028</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Maths!$AA$32:$AA$42</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1.9352683896620274E-11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.8516320474777447E-11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.2970503986993881E-11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.9024979854955678E-11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1896089385474859E-10</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.0497524752475247E-10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.9273134721856047E-10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.9981224183251968E-10</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.5879355297463856E-10</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6.2562178654161252E-10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.1982495948136124E-10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7C6F-4036-B9B4-EEAA82DBCA58}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="779298280"/>
+        <c:axId val="779289640"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="779298280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="779289640"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="779289640"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Gallium Intensity in PV Inverters [kg/MWac]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="779298280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.26651063836197397"/>
+          <c:y val="0.18642460169838107"/>
+          <c:w val="0.40348070995054536"/>
+          <c:h val="0.31007225632072066"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1100">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="11">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent5"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>220662</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>104782</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>57151</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B57A1215-BD0D-BE0B-7ECF-FE9684AA4CA1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Custom 2">
+    <a:clrScheme name="NREL2">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1057,34 +2336,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="007BBD"/>
+        <a:srgbClr val="5E6A71"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="00A4E4"/>
+        <a:srgbClr val="D1D5D8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="F6A01A"/>
+        <a:srgbClr val="0079C2"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="FFC425"/>
+        <a:srgbClr val="00A4E4"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="5E9732"/>
+        <a:srgbClr val="F7A11A"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8DC63F"/>
+        <a:srgbClr val="FFC423"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="933C06"/>
+        <a:srgbClr val="5D9732"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="D9531E"/>
+        <a:srgbClr val="8CC63F"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="933C06"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="D9531E"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
@@ -1379,7 +2658,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="X1" s="44" t="s">
+      <c r="X1" s="42" t="s">
         <v>173</v>
       </c>
       <c r="Y1">
@@ -1396,16 +2675,16 @@
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="X2" s="45" t="s">
+      <c r="X2" s="43" t="s">
         <v>172</v>
       </c>
-      <c r="Y2" s="46">
+      <c r="Y2" s="44">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Z2" s="46">
+      <c r="Z2" s="44">
         <v>1.2</v>
       </c>
-      <c r="AA2" s="46">
+      <c r="AA2" s="44">
         <v>1.3</v>
       </c>
     </row>
@@ -1521,13 +2800,13 @@
       <c r="A9">
         <v>1995</v>
       </c>
-      <c r="AC9" s="40">
+      <c r="AC9" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD9" s="40">
+      <c r="AD9" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE9" s="42">
+      <c r="AE9" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1535,13 +2814,13 @@
       <c r="A10">
         <v>1996</v>
       </c>
-      <c r="AC10" s="40">
+      <c r="AC10" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD10" s="40">
+      <c r="AD10" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE10" s="42">
+      <c r="AE10" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1549,13 +2828,13 @@
       <c r="A11">
         <v>1997</v>
       </c>
-      <c r="AC11" s="40">
+      <c r="AC11" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD11" s="40">
+      <c r="AD11" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE11" s="42">
+      <c r="AE11" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1563,13 +2842,13 @@
       <c r="A12">
         <v>1998</v>
       </c>
-      <c r="AC12" s="40">
+      <c r="AC12" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD12" s="40">
+      <c r="AD12" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE12" s="42">
+      <c r="AE12" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1577,13 +2856,13 @@
       <c r="A13">
         <v>1999</v>
       </c>
-      <c r="AC13" s="40">
+      <c r="AC13" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD13" s="40">
+      <c r="AD13" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE13" s="42">
+      <c r="AE13" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1591,13 +2870,13 @@
       <c r="A14">
         <v>2000</v>
       </c>
-      <c r="AC14" s="40">
+      <c r="AC14" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD14" s="40">
+      <c r="AD14" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE14" s="42">
+      <c r="AE14" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1605,13 +2884,13 @@
       <c r="A15">
         <v>2001</v>
       </c>
-      <c r="AC15" s="40">
+      <c r="AC15" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD15" s="40">
+      <c r="AD15" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE15" s="42">
+      <c r="AE15" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1619,13 +2898,13 @@
       <c r="A16">
         <v>2002</v>
       </c>
-      <c r="AC16" s="40">
+      <c r="AC16" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD16" s="40">
+      <c r="AD16" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE16" s="42">
+      <c r="AE16" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1633,13 +2912,13 @@
       <c r="A17">
         <v>2003</v>
       </c>
-      <c r="AC17" s="40">
+      <c r="AC17" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD17" s="40">
+      <c r="AD17" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE17" s="42">
+      <c r="AE17" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1647,13 +2926,13 @@
       <c r="A18">
         <v>2004</v>
       </c>
-      <c r="AC18" s="40">
+      <c r="AC18" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD18" s="40">
+      <c r="AD18" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE18" s="42">
+      <c r="AE18" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1661,13 +2940,13 @@
       <c r="A19">
         <v>2005</v>
       </c>
-      <c r="AC19" s="40">
+      <c r="AC19" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD19" s="40">
+      <c r="AD19" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE19" s="42">
+      <c r="AE19" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1675,13 +2954,13 @@
       <c r="A20">
         <v>2006</v>
       </c>
-      <c r="AC20" s="40">
+      <c r="AC20" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD20" s="40">
+      <c r="AD20" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE20" s="42">
+      <c r="AE20" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1689,13 +2968,13 @@
       <c r="A21">
         <v>2007</v>
       </c>
-      <c r="AC21" s="40">
+      <c r="AC21" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD21" s="40">
+      <c r="AD21" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE21" s="42">
+      <c r="AE21" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1703,13 +2982,13 @@
       <c r="A22">
         <v>2008</v>
       </c>
-      <c r="AC22" s="40">
+      <c r="AC22" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD22" s="40">
+      <c r="AD22" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE22" s="42">
+      <c r="AE22" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1717,13 +2996,13 @@
       <c r="A23">
         <v>2009</v>
       </c>
-      <c r="AC23" s="40">
+      <c r="AC23" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD23" s="40">
+      <c r="AD23" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE23" s="42">
+      <c r="AE23" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1731,13 +3010,13 @@
       <c r="A24">
         <v>2010</v>
       </c>
-      <c r="AC24" s="40">
+      <c r="AC24" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD24" s="40">
+      <c r="AD24" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE24" s="42">
+      <c r="AE24" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1745,13 +3024,13 @@
       <c r="A25">
         <v>2011</v>
       </c>
-      <c r="AC25" s="40">
+      <c r="AC25" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD25" s="40">
+      <c r="AD25" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE25" s="42">
+      <c r="AE25" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1759,13 +3038,13 @@
       <c r="A26">
         <v>2012</v>
       </c>
-      <c r="AC26" s="40">
+      <c r="AC26" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD26" s="40">
+      <c r="AD26" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE26" s="42">
+      <c r="AE26" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1773,13 +3052,13 @@
       <c r="A27">
         <v>2013</v>
       </c>
-      <c r="AC27" s="40">
+      <c r="AC27" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD27" s="40">
+      <c r="AD27" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE27" s="42">
+      <c r="AE27" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1793,13 +3072,13 @@
       <c r="H28" s="18"/>
       <c r="I28" s="18"/>
       <c r="J28" s="18"/>
-      <c r="AC28" s="40">
+      <c r="AC28" s="39">
         <v>0.74244430688220409</v>
       </c>
-      <c r="AD28" s="40">
+      <c r="AD28" s="39">
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE28" s="42">
+      <c r="AE28" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
@@ -1827,7 +3106,7 @@
         <f>WoodMacInverterCompany!U4</f>
         <v>0.25270531817362618</v>
       </c>
-      <c r="AE29" s="39">
+      <c r="AE29" s="38">
         <f>WoodMacInverterCompany!V4</f>
         <v>4.8503749441697556E-3</v>
       </c>
@@ -1857,7 +3136,7 @@
         <f>WoodMacInverterCompany!U5</f>
         <v>0.24140775674316256</v>
       </c>
-      <c r="AE30" s="39">
+      <c r="AE30" s="38">
         <f>WoodMacInverterCompany!V5</f>
         <v>5.7589593033124976E-3</v>
       </c>
@@ -1877,7 +3156,7 @@
         <f>WoodMacInverterCompany!U6</f>
         <v>0.23361236210093689</v>
       </c>
-      <c r="AE31" s="39">
+      <c r="AE31" s="38">
         <f>WoodMacInverterCompany!V6</f>
         <v>2.8711770168524066E-3</v>
       </c>
@@ -1898,28 +3177,28 @@
       <c r="S32" t="s">
         <v>73</v>
       </c>
-      <c r="U32" s="37">
+      <c r="U32" s="36">
         <f>$B$39*$G$37*P32</f>
         <v>1.0751491053677931E-8</v>
       </c>
-      <c r="V32" s="37">
+      <c r="V32" s="36">
         <f>$B$39*$G$36*P32</f>
         <v>6.4508946322067582E-9</v>
       </c>
-      <c r="W32" s="37">
+      <c r="W32" s="36">
         <f t="shared" ref="W32:W37" si="0">$B$39*$G$38*$H$38*P32</f>
         <v>1.9352683896620274E-8</v>
       </c>
       <c r="X32" s="27"/>
-      <c r="Y32" s="37">
+      <c r="Y32" s="36">
         <f>U32/1000/$Y$1</f>
         <v>6.719681908548706E-9</v>
       </c>
-      <c r="Z32" s="37">
+      <c r="Z32" s="36">
         <f>V32/1000/$Z$1</f>
         <v>6.4508946322067576E-10</v>
       </c>
-      <c r="AA32" s="37">
+      <c r="AA32" s="36">
         <f>W32/1000/$AA$1</f>
         <v>1.9352683896620274E-11</v>
       </c>
@@ -1932,11 +3211,11 @@
         <f>WoodMacInverterCompany!U7</f>
         <v>0.21975854286905561</v>
       </c>
-      <c r="AE32" s="39">
+      <c r="AE32" s="38">
         <f>WoodMacInverterCompany!V7</f>
         <v>2.776302802624211E-3</v>
       </c>
-      <c r="AG32" s="37">
+      <c r="AG32" s="36">
         <f>(Y32*AC32)+(Z32*AD32)+(AA32*AE32)</f>
         <v>5.3661361814351366E-9</v>
       </c>
@@ -1957,28 +3236,28 @@
       <c r="S33" t="s">
         <v>73</v>
       </c>
-      <c r="U33" s="37">
+      <c r="U33" s="36">
         <f>$B$39*$G$37*P33</f>
         <v>1.0286844708209693E-8</v>
       </c>
-      <c r="V33" s="37">
+      <c r="V33" s="36">
         <f t="shared" ref="V33:V42" si="1">$B$39*$G$36*P33</f>
         <v>6.1721068249258155E-9</v>
       </c>
-      <c r="W33" s="37">
+      <c r="W33" s="36">
         <f t="shared" si="0"/>
         <v>1.8516320474777446E-8</v>
       </c>
       <c r="X33" s="27"/>
-      <c r="Y33" s="37">
+      <c r="Y33" s="36">
         <f>U33/1000/$Y$1</f>
         <v>6.4292779426310583E-9</v>
       </c>
-      <c r="Z33" s="37">
+      <c r="Z33" s="36">
         <f t="shared" ref="Z33:Z42" si="2">V33/1000/$Z$1</f>
         <v>6.1721068249258161E-10</v>
       </c>
-      <c r="AA33" s="37">
+      <c r="AA33" s="36">
         <f t="shared" ref="AA33:AA42" si="3">W33/1000/$AA$1</f>
         <v>1.8516320474777447E-11</v>
       </c>
@@ -1991,11 +3270,11 @@
         <f>WoodMacInverterCompany!U8</f>
         <v>0.18271067343626388</v>
       </c>
-      <c r="AE33" s="39">
+      <c r="AE33" s="38">
         <f>WoodMacInverterCompany!V8</f>
         <v>3.7343167375427193E-3</v>
       </c>
-      <c r="AG33" s="37">
+      <c r="AG33" s="36">
         <f t="shared" ref="AG33:AG42" si="4">(Y33*AC33)+(Z33*AD33)+(AA33*AE33)</f>
         <v>5.3434114050482815E-9</v>
       </c>
@@ -2016,28 +3295,28 @@
       <c r="S34" t="s">
         <v>73</v>
       </c>
-      <c r="U34" s="37">
+      <c r="U34" s="36">
         <f t="shared" ref="U34:U42" si="5">$B$39*$G$37*P34</f>
         <v>1.8316946659441044E-8</v>
       </c>
-      <c r="V34" s="37">
+      <c r="V34" s="36">
         <f t="shared" si="1"/>
         <v>1.0990167995664626E-8</v>
       </c>
-      <c r="W34" s="37">
+      <c r="W34" s="36">
         <f t="shared" si="0"/>
         <v>3.2970503986993881E-8</v>
       </c>
       <c r="X34" s="27"/>
-      <c r="Y34" s="37">
-        <f t="shared" ref="Y33:Y42" si="6">U34/1000/$Y$1</f>
+      <c r="Y34" s="36">
+        <f t="shared" ref="Y34:Y42" si="6">U34/1000/$Y$1</f>
         <v>1.1448091662150651E-8</v>
       </c>
-      <c r="Z34" s="37">
+      <c r="Z34" s="36">
         <f t="shared" si="2"/>
         <v>1.0990167995664627E-9</v>
       </c>
-      <c r="AA34" s="37">
+      <c r="AA34" s="36">
         <f t="shared" si="3"/>
         <v>3.2970503986993881E-11</v>
       </c>
@@ -2050,11 +3329,11 @@
         <f>WoodMacInverterCompany!U9</f>
         <v>0.17972966841296417</v>
       </c>
-      <c r="AE34" s="39">
+      <c r="AE34" s="38">
         <f>WoodMacInverterCompany!V9</f>
         <v>7.1361510773210171E-3</v>
       </c>
-      <c r="AG34" s="37">
+      <c r="AG34" s="36">
         <f t="shared" si="4"/>
         <v>9.5065958395668732E-9</v>
       </c>
@@ -2088,28 +3367,28 @@
       <c r="S35" t="s">
         <v>73</v>
       </c>
-      <c r="U35" s="37">
+      <c r="U35" s="36">
         <f t="shared" si="5"/>
         <v>2.7236099919419822E-8</v>
       </c>
-      <c r="V35" s="37">
+      <c r="V35" s="36">
         <f t="shared" si="1"/>
         <v>1.6341659951651891E-8</v>
       </c>
-      <c r="W35" s="37">
+      <c r="W35" s="36">
         <f t="shared" si="0"/>
         <v>4.9024979854955677E-8</v>
       </c>
       <c r="X35" s="27"/>
-      <c r="Y35" s="37">
+      <c r="Y35" s="36">
         <f t="shared" si="6"/>
         <v>1.7022562449637387E-8</v>
       </c>
-      <c r="Z35" s="37">
+      <c r="Z35" s="36">
         <f t="shared" si="2"/>
         <v>1.6341659951651892E-9</v>
       </c>
-      <c r="AA35" s="37">
+      <c r="AA35" s="36">
         <f t="shared" si="3"/>
         <v>4.9024979854955678E-11</v>
       </c>
@@ -2122,11 +3401,11 @@
         <f>WoodMacInverterCompany!U10</f>
         <v>0.1251798418412931</v>
       </c>
-      <c r="AE35" s="39">
+      <c r="AE35" s="38">
         <f>WoodMacInverterCompany!V10</f>
         <v>3.8070870635134027E-3</v>
       </c>
-      <c r="AG35" s="37">
+      <c r="AG35" s="36">
         <f t="shared" si="4"/>
         <v>1.5031625680352174E-8</v>
       </c>
@@ -2169,28 +3448,28 @@
       <c r="S36" t="s">
         <v>73</v>
       </c>
-      <c r="U36" s="37">
+      <c r="U36" s="36">
         <f t="shared" si="5"/>
         <v>6.6089385474860326E-8</v>
       </c>
-      <c r="V36" s="37">
+      <c r="V36" s="36">
         <f t="shared" si="1"/>
         <v>3.9653631284916192E-8</v>
       </c>
-      <c r="W36" s="37">
+      <c r="W36" s="36">
         <f t="shared" si="0"/>
         <v>1.1896089385474858E-7</v>
       </c>
       <c r="X36" s="27"/>
-      <c r="Y36" s="37">
+      <c r="Y36" s="36">
         <f t="shared" si="6"/>
         <v>4.13058659217877E-8</v>
       </c>
-      <c r="Z36" s="37">
+      <c r="Z36" s="36">
         <f t="shared" si="2"/>
         <v>3.9653631284916193E-9</v>
       </c>
-      <c r="AA36" s="37">
+      <c r="AA36" s="36">
         <f t="shared" si="3"/>
         <v>1.1896089385474859E-10</v>
       </c>
@@ -2203,11 +3482,11 @@
         <f>WoodMacInverterCompany!U11</f>
         <v>0.1052077615174591</v>
       </c>
-      <c r="AE36" s="39">
+      <c r="AE36" s="38">
         <f>WoodMacInverterCompany!V11</f>
         <v>3.4344048825351459E-3</v>
       </c>
-      <c r="AG36" s="37">
+      <c r="AG36" s="36">
         <f t="shared" si="4"/>
         <v>3.723590270124415E-8</v>
       </c>
@@ -2250,28 +3529,28 @@
       <c r="S37" t="s">
         <v>73</v>
       </c>
-      <c r="U37" s="37">
+      <c r="U37" s="36">
         <f t="shared" si="5"/>
         <v>1.1387513751375138E-7</v>
       </c>
-      <c r="V37" s="37">
+      <c r="V37" s="36">
         <f t="shared" si="1"/>
         <v>6.8325082508250822E-8</v>
       </c>
-      <c r="W37" s="37">
+      <c r="W37" s="36">
         <f t="shared" si="0"/>
         <v>2.0497524752475247E-7</v>
       </c>
       <c r="X37" s="27"/>
-      <c r="Y37" s="37">
+      <c r="Y37" s="36">
         <f t="shared" si="6"/>
         <v>7.1171960946094613E-8</v>
       </c>
-      <c r="Z37" s="37">
+      <c r="Z37" s="36">
         <f t="shared" si="2"/>
         <v>6.8325082508250815E-9</v>
       </c>
-      <c r="AA37" s="37">
+      <c r="AA37" s="36">
         <f t="shared" si="3"/>
         <v>2.0497524752475247E-10</v>
       </c>
@@ -2284,11 +3563,11 @@
         <f>WoodMacInverterCompany!U12</f>
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE37" s="39">
+      <c r="AE37" s="38">
         <f>WoodMacInverterCompany!V12</f>
         <v>9.5944618750836153E-3</v>
       </c>
-      <c r="AG37" s="37">
+      <c r="AG37" s="36">
         <f t="shared" si="4"/>
         <v>6.1887715743716504E-8</v>
       </c>
@@ -2346,42 +3625,42 @@
       <c r="S38" t="s">
         <v>73</v>
       </c>
-      <c r="U38" s="37">
+      <c r="U38" s="36">
         <f t="shared" si="5"/>
         <v>1.6262852623253359E-7</v>
       </c>
-      <c r="V38" s="37">
+      <c r="V38" s="36">
         <f t="shared" si="1"/>
         <v>9.7577115739520148E-8</v>
       </c>
-      <c r="W38" s="37">
+      <c r="W38" s="36">
         <f>$B$39*$G$38*$H$38*P38</f>
         <v>2.9273134721856046E-7</v>
       </c>
       <c r="X38" s="27"/>
-      <c r="Y38" s="37">
+      <c r="Y38" s="36">
         <f t="shared" si="6"/>
         <v>1.016428288953335E-7</v>
       </c>
-      <c r="Z38" s="37">
+      <c r="Z38" s="36">
         <f t="shared" si="2"/>
         <v>9.7577115739520142E-9</v>
       </c>
-      <c r="AA38" s="37">
+      <c r="AA38" s="36">
         <f t="shared" si="3"/>
         <v>2.9273134721856047E-10</v>
       </c>
       <c r="AB38" s="27"/>
-      <c r="AC38" s="41">
+      <c r="AC38" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD38" s="41">
+      <c r="AD38" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE38" s="41">
+      <c r="AE38" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
-      <c r="AG38" s="37">
+      <c r="AG38" s="36">
         <f t="shared" si="4"/>
         <v>8.8383717666933081E-8</v>
       </c>
@@ -2429,42 +3708,42 @@
       <c r="S39" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="U39" s="38">
+      <c r="U39" s="37">
         <f t="shared" si="5"/>
         <v>2.2211791212917761E-7</v>
       </c>
-      <c r="V39" s="38">
+      <c r="V39" s="37">
         <f t="shared" si="1"/>
         <v>1.3327074727750656E-7</v>
       </c>
-      <c r="W39" s="37">
+      <c r="W39" s="36">
         <f t="shared" ref="W39:W42" si="7">$B$39*$G$38*$H$38*P39</f>
         <v>3.9981224183251968E-7</v>
       </c>
-      <c r="X39" s="36"/>
-      <c r="Y39" s="37">
+      <c r="X39" s="35"/>
+      <c r="Y39" s="36">
         <f t="shared" si="6"/>
         <v>1.3882369508073601E-7</v>
       </c>
-      <c r="Z39" s="37">
+      <c r="Z39" s="36">
         <f t="shared" si="2"/>
         <v>1.3327074727750655E-8</v>
       </c>
-      <c r="AA39" s="37">
+      <c r="AA39" s="36">
         <f t="shared" si="3"/>
         <v>3.9981224183251968E-10</v>
       </c>
-      <c r="AB39" s="43"/>
-      <c r="AC39" s="41">
+      <c r="AB39" s="27"/>
+      <c r="AC39" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD39" s="41">
+      <c r="AD39" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE39" s="41">
+      <c r="AE39" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
-      <c r="AG39" s="37">
+      <c r="AG39" s="36">
         <f t="shared" si="4"/>
         <v>1.207144114822988E-7</v>
       </c>
@@ -2485,42 +3764,42 @@
       <c r="S40" t="s">
         <v>73</v>
       </c>
-      <c r="U40" s="37">
+      <c r="U40" s="36">
         <f t="shared" si="5"/>
         <v>3.1044086276368805E-7</v>
       </c>
-      <c r="V40" s="37">
+      <c r="V40" s="36">
         <f t="shared" si="1"/>
         <v>1.8626451765821281E-7</v>
       </c>
-      <c r="W40" s="37">
+      <c r="W40" s="36">
         <f t="shared" si="7"/>
         <v>5.5879355297463852E-7</v>
       </c>
       <c r="X40" s="27"/>
-      <c r="Y40" s="37">
+      <c r="Y40" s="36">
         <f t="shared" si="6"/>
         <v>1.9402553922730501E-7</v>
       </c>
-      <c r="Z40" s="37">
+      <c r="Z40" s="36">
         <f t="shared" si="2"/>
         <v>1.862645176582128E-8</v>
       </c>
-      <c r="AA40" s="37">
+      <c r="AA40" s="36">
         <f t="shared" si="3"/>
         <v>5.5879355297463856E-10</v>
       </c>
       <c r="AB40" s="27"/>
-      <c r="AC40" s="41">
+      <c r="AC40" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD40" s="41">
+      <c r="AD40" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE40" s="41">
+      <c r="AE40" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
-      <c r="AG40" s="37">
+      <c r="AG40" s="36">
         <f t="shared" si="4"/>
         <v>1.6871528139874396E-7</v>
       </c>
@@ -2541,42 +3820,42 @@
       <c r="S41" t="s">
         <v>73</v>
       </c>
-      <c r="U41" s="37">
+      <c r="U41" s="36">
         <f t="shared" si="5"/>
         <v>3.4756765918978473E-7</v>
       </c>
-      <c r="V41" s="37">
+      <c r="V41" s="36">
         <f t="shared" si="1"/>
         <v>2.085405955138708E-7</v>
       </c>
-      <c r="W41" s="37">
+      <c r="W41" s="36">
         <f t="shared" si="7"/>
         <v>6.2562178654161249E-7</v>
       </c>
       <c r="X41" s="27"/>
-      <c r="Y41" s="37">
+      <c r="Y41" s="36">
         <f t="shared" si="6"/>
         <v>2.1722978699361545E-7</v>
       </c>
-      <c r="Z41" s="37">
+      <c r="Z41" s="36">
         <f t="shared" si="2"/>
         <v>2.085405955138708E-8</v>
       </c>
-      <c r="AA41" s="37">
+      <c r="AA41" s="36">
         <f t="shared" si="3"/>
         <v>6.2562178654161252E-10</v>
       </c>
       <c r="AB41" s="27"/>
-      <c r="AC41" s="41">
+      <c r="AC41" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD41" s="41">
+      <c r="AD41" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE41" s="41">
+      <c r="AE41" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
-      <c r="AG41" s="37">
+      <c r="AG41" s="36">
         <f t="shared" si="4"/>
         <v>1.8889257974374607E-7</v>
       </c>
@@ -2597,42 +3876,42 @@
       <c r="S42" t="s">
         <v>73</v>
       </c>
-      <c r="U42" s="37">
+      <c r="U42" s="36">
         <f t="shared" si="5"/>
         <v>3.9990275526742293E-7</v>
       </c>
-      <c r="V42" s="37">
+      <c r="V42" s="36">
         <f t="shared" si="1"/>
         <v>2.3994165316045375E-7</v>
       </c>
-      <c r="W42" s="37">
+      <c r="W42" s="36">
         <f t="shared" si="7"/>
         <v>7.1982495948136129E-7</v>
       </c>
       <c r="X42" s="27"/>
-      <c r="Y42" s="37">
+      <c r="Y42" s="36">
         <f t="shared" si="6"/>
         <v>2.4993922204213932E-7</v>
       </c>
-      <c r="Z42" s="37">
+      <c r="Z42" s="36">
         <f t="shared" si="2"/>
         <v>2.3994165316045373E-8</v>
       </c>
-      <c r="AA42" s="37">
+      <c r="AA42" s="36">
         <f t="shared" si="3"/>
         <v>7.1982495948136124E-10</v>
       </c>
       <c r="AB42" s="27"/>
-      <c r="AC42" s="41">
+      <c r="AC42" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD42" s="41">
+      <c r="AD42" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE42" s="41">
+      <c r="AE42" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
-      <c r="AG42" s="37">
+      <c r="AG42" s="36">
         <f t="shared" si="4"/>
         <v>2.1733513200043898E-7</v>
       </c>
@@ -2641,13 +3920,13 @@
       <c r="A43">
         <v>2029</v>
       </c>
-      <c r="AC43" s="41">
+      <c r="AC43" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD43" s="41">
+      <c r="AD43" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE43" s="41">
+      <c r="AE43" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2655,13 +3934,13 @@
       <c r="A44">
         <v>2030</v>
       </c>
-      <c r="AC44" s="41">
+      <c r="AC44" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD44" s="41">
+      <c r="AD44" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE44" s="41">
+      <c r="AE44" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2669,13 +3948,13 @@
       <c r="A45">
         <v>2031</v>
       </c>
-      <c r="AC45" s="41">
+      <c r="AC45" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD45" s="41">
+      <c r="AD45" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE45" s="41">
+      <c r="AE45" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2683,13 +3962,13 @@
       <c r="A46">
         <v>2032</v>
       </c>
-      <c r="AC46" s="41">
+      <c r="AC46" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD46" s="41">
+      <c r="AD46" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE46" s="41">
+      <c r="AE46" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2697,13 +3976,13 @@
       <c r="A47">
         <v>2033</v>
       </c>
-      <c r="AC47" s="41">
+      <c r="AC47" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD47" s="41">
+      <c r="AD47" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE47" s="41">
+      <c r="AE47" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2711,13 +3990,13 @@
       <c r="A48">
         <v>2034</v>
       </c>
-      <c r="AC48" s="41">
+      <c r="AC48" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD48" s="41">
+      <c r="AD48" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE48" s="41">
+      <c r="AE48" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2725,13 +4004,13 @@
       <c r="A49">
         <v>2035</v>
       </c>
-      <c r="AC49" s="41">
+      <c r="AC49" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD49" s="41">
+      <c r="AD49" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE49" s="41">
+      <c r="AE49" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2739,13 +4018,13 @@
       <c r="A50">
         <v>2036</v>
       </c>
-      <c r="AC50" s="41">
+      <c r="AC50" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD50" s="41">
+      <c r="AD50" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE50" s="41">
+      <c r="AE50" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2753,13 +4032,13 @@
       <c r="A51">
         <v>2037</v>
       </c>
-      <c r="AC51" s="41">
+      <c r="AC51" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD51" s="41">
+      <c r="AD51" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE51" s="41">
+      <c r="AE51" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2767,13 +4046,13 @@
       <c r="A52">
         <v>2038</v>
       </c>
-      <c r="AC52" s="41">
+      <c r="AC52" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD52" s="41">
+      <c r="AD52" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE52" s="41">
+      <c r="AE52" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2781,13 +4060,13 @@
       <c r="A53">
         <v>2039</v>
       </c>
-      <c r="AC53" s="41">
+      <c r="AC53" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD53" s="41">
+      <c r="AD53" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE53" s="41">
+      <c r="AE53" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2795,13 +4074,13 @@
       <c r="A54">
         <v>2040</v>
       </c>
-      <c r="AC54" s="41">
+      <c r="AC54" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD54" s="41">
+      <c r="AD54" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE54" s="41">
+      <c r="AE54" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2809,13 +4088,13 @@
       <c r="A55">
         <v>2041</v>
       </c>
-      <c r="AC55" s="41">
+      <c r="AC55" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD55" s="41">
+      <c r="AD55" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE55" s="41">
+      <c r="AE55" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2823,13 +4102,13 @@
       <c r="A56">
         <v>2042</v>
       </c>
-      <c r="AC56" s="41">
+      <c r="AC56" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD56" s="41">
+      <c r="AD56" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE56" s="41">
+      <c r="AE56" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2837,13 +4116,13 @@
       <c r="A57">
         <v>2043</v>
       </c>
-      <c r="AC57" s="41">
+      <c r="AC57" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD57" s="41">
+      <c r="AD57" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE57" s="41">
+      <c r="AE57" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2851,13 +4130,13 @@
       <c r="A58">
         <v>2044</v>
       </c>
-      <c r="AC58" s="41">
+      <c r="AC58" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD58" s="41">
+      <c r="AD58" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE58" s="41">
+      <c r="AE58" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2865,13 +4144,13 @@
       <c r="A59">
         <v>2045</v>
       </c>
-      <c r="AC59" s="41">
+      <c r="AC59" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD59" s="41">
+      <c r="AD59" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE59" s="41">
+      <c r="AE59" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2879,13 +4158,13 @@
       <c r="A60">
         <v>2046</v>
       </c>
-      <c r="AC60" s="41">
+      <c r="AC60" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD60" s="41">
+      <c r="AD60" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE60" s="41">
+      <c r="AE60" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2893,13 +4172,13 @@
       <c r="A61">
         <v>2047</v>
       </c>
-      <c r="AC61" s="41">
+      <c r="AC61" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD61" s="41">
+      <c r="AD61" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE61" s="41">
+      <c r="AE61" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2907,13 +4186,13 @@
       <c r="A62">
         <v>2048</v>
       </c>
-      <c r="AC62" s="41">
+      <c r="AC62" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD62" s="41">
+      <c r="AD62" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE62" s="41">
+      <c r="AE62" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2921,13 +4200,13 @@
       <c r="A63">
         <v>2049</v>
       </c>
-      <c r="AC63" s="41">
+      <c r="AC63" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD63" s="41">
+      <c r="AD63" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE63" s="41">
+      <c r="AE63" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -2935,13 +4214,13 @@
       <c r="A64">
         <v>2050</v>
       </c>
-      <c r="AC64" s="41">
+      <c r="AC64" s="40">
         <v>0.85668734806738545</v>
       </c>
-      <c r="AD64" s="41">
+      <c r="AD64" s="40">
         <v>0.13371819005753083</v>
       </c>
-      <c r="AE64" s="41">
+      <c r="AE64" s="40">
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
@@ -3204,6 +4483,7 @@
     <hyperlink ref="N39" r:id="rId4" xr:uid="{7B120840-CD9C-400D-9838-2232DE726815}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -3230,12 +4510,12 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
@@ -3607,10 +4887,10 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="45" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="35"/>
+      <c r="C18" s="45"/>
       <c r="D18" t="s">
         <v>64</v>
       </c>
@@ -3894,27 +5174,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="45" t="s">
         <v>159</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="I1" s="35" t="s">
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="I1" s="45" t="s">
         <v>163</v>
       </c>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
       <c r="M1" t="s">
         <v>164</v>
       </c>
-      <c r="T1" s="35" t="s">
+      <c r="T1" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="B2" s="4"/>
@@ -9386,27 +10666,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ProcessName xmlns="d382aed9-cc96-421a-b6d1-bad087b40ea5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d382aed9-cc96-421a-b6d1-bad087b40ea5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3c3bb480-5c86-45a4-be90-daa3829a93c5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E1D7978D1E43DE4EA43DBD7340A406DC" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d2a0579b8367a5d14f15657bceede69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d382aed9-cc96-421a-b6d1-bad087b40ea5" xmlns:ns3="3c3bb480-5c86-45a4-be90-daa3829a93c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6184784662eaf13c68ab2ee7ade41035" ns2:_="" ns3:_="">
     <xsd:import namespace="d382aed9-cc96-421a-b6d1-bad087b40ea5"/>
@@ -9649,32 +10908,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2355CD45-2F25-4965-9590-C756C8D0B153}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3c3bb480-5c86-45a4-be90-daa3829a93c5"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="d382aed9-cc96-421a-b6d1-bad087b40ea5"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D15763B-BC3F-44A0-B84D-0D65F1925A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ProcessName xmlns="d382aed9-cc96-421a-b6d1-bad087b40ea5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d382aed9-cc96-421a-b6d1-bad087b40ea5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3c3bb480-5c86-45a4-be90-daa3829a93c5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A8357D9-61C4-4864-BD66-2D2D973EC6D9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9693,6 +10948,31 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D15763B-BC3F-44A0-B84D-0D65F1925A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2355CD45-2F25-4965-9590-C756C8D0B153}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3c3bb480-5c86-45a4-be90-daa3829a93c5"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="d382aed9-cc96-421a-b6d1-bad087b40ea5"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{95965d95-ecc0-4720-b759-1f33c42ed7da}" enabled="1" method="Standard" siteId="{a0f29d7e-28cd-4f54-8442-7885aee7c080}" removed="0"/>

--- a/PV_ICE/baselines/SupportingMaterial/Manual Files/Inverter_Gallium_Calcs.xlsx
+++ b/PV_ICE/baselines/SupportingMaterial/Manual Files/Inverter_Gallium_Calcs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmirletz\Documents\GitHub\PV_ICE\PV_ICE\baselines\SupportingMaterial\Manual Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9BC423E-1638-441F-9E90-A5B8A3074F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1366EB-F0EC-4CCD-815A-553FDFD7478A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Maths" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="179">
   <si>
     <t>year</t>
   </si>
@@ -716,6 +716,9 @@
   </si>
   <si>
     <t>Utility [kg/MWac]</t>
+  </si>
+  <si>
+    <t>Large Non-Res ILR</t>
   </si>
 </sst>
 </file>
@@ -1685,6 +1688,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1692,7 +1696,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2622,7 +2625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG114"/>
+  <dimension ref="A1:AL114"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.81640625" bestFit="1" customWidth="1"/>
@@ -2908,7 +2911,7 @@
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2003</v>
       </c>
@@ -2922,7 +2925,7 @@
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2004</v>
       </c>
@@ -2936,7 +2939,7 @@
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2005</v>
       </c>
@@ -2950,7 +2953,7 @@
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2006</v>
       </c>
@@ -2964,7 +2967,7 @@
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2007</v>
       </c>
@@ -2978,7 +2981,7 @@
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2008</v>
       </c>
@@ -2992,7 +2995,7 @@
         <v>4.8503749441697556E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2009</v>
       </c>
@@ -3005,8 +3008,11 @@
       <c r="AE23" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
-    </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="AI23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2010</v>
       </c>
@@ -3019,8 +3025,22 @@
       <c r="AE24" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
-    </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="AI24">
+        <v>2010.04157061054</v>
+      </c>
+      <c r="AJ24">
+        <v>1.02831858407079</v>
+      </c>
+      <c r="AK24">
+        <f>ROUND(AI24,0)</f>
+        <v>2010</v>
+      </c>
+      <c r="AL24">
+        <f>ROUND(AJ24,2)</f>
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2011</v>
       </c>
@@ -3033,8 +3053,22 @@
       <c r="AE25" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
-    </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="AI25">
+        <v>2011.0358816092801</v>
+      </c>
+      <c r="AJ25">
+        <v>1.0893805309734399</v>
+      </c>
+      <c r="AK25">
+        <f t="shared" ref="AK25:AL37" si="0">ROUND(AI25,0)</f>
+        <v>2011</v>
+      </c>
+      <c r="AL25">
+        <f t="shared" ref="AL25:AL37" si="1">ROUND(AJ25,2)</f>
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2012</v>
       </c>
@@ -3047,8 +3081,22 @@
       <c r="AE26" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
-    </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="AI26">
+        <v>2012.07780545846</v>
+      </c>
+      <c r="AJ26">
+        <v>1.1119469026548601</v>
+      </c>
+      <c r="AK26">
+        <f t="shared" si="0"/>
+        <v>2012</v>
+      </c>
+      <c r="AL26">
+        <f t="shared" si="1"/>
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2013</v>
       </c>
@@ -3061,8 +3109,22 @@
       <c r="AE27" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
-    </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="AI27">
+        <v>2013.09531865843</v>
+      </c>
+      <c r="AJ27">
+        <v>1.1504424778761</v>
+      </c>
+      <c r="AK27">
+        <f t="shared" si="0"/>
+        <v>2013</v>
+      </c>
+      <c r="AL27">
+        <f t="shared" si="1"/>
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2014</v>
       </c>
@@ -3081,8 +3143,22 @@
       <c r="AE28" s="41">
         <v>4.8503749441697556E-3</v>
       </c>
-    </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="AI28">
+        <v>2014.0874544507999</v>
+      </c>
+      <c r="AJ28">
+        <v>1.1995575221238799</v>
+      </c>
+      <c r="AK28">
+        <f t="shared" si="0"/>
+        <v>2014</v>
+      </c>
+      <c r="AL28">
+        <f t="shared" si="1"/>
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2015</v>
       </c>
@@ -3110,8 +3186,22 @@
         <f>WoodMacInverterCompany!V4</f>
         <v>4.8503749441697556E-3</v>
       </c>
-    </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="AI29">
+        <v>2015.07282293448</v>
+      </c>
+      <c r="AJ29">
+        <v>1.2115044247787501</v>
+      </c>
+      <c r="AK29">
+        <f t="shared" si="0"/>
+        <v>2015</v>
+      </c>
+      <c r="AL29">
+        <f t="shared" si="1"/>
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2016</v>
       </c>
@@ -3140,8 +3230,22 @@
         <f>WoodMacInverterCompany!V5</f>
         <v>5.7589593033124976E-3</v>
       </c>
-    </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="AI30">
+        <v>2016.11716367963</v>
+      </c>
+      <c r="AJ30">
+        <v>1.24734513274335</v>
+      </c>
+      <c r="AK30">
+        <f t="shared" si="0"/>
+        <v>2016</v>
+      </c>
+      <c r="AL30">
+        <f t="shared" si="1"/>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2017</v>
       </c>
@@ -3160,8 +3264,22 @@
         <f>WoodMacInverterCompany!V6</f>
         <v>2.8711770168524066E-3</v>
       </c>
-    </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="AI31">
+        <v>2017.0728043429699</v>
+      </c>
+      <c r="AJ31">
+        <v>1.24601769911503</v>
+      </c>
+      <c r="AK31">
+        <f t="shared" si="0"/>
+        <v>2017</v>
+      </c>
+      <c r="AL31">
+        <f t="shared" si="1"/>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2018</v>
       </c>
@@ -3186,7 +3304,7 @@
         <v>6.4508946322067582E-9</v>
       </c>
       <c r="W32" s="36">
-        <f t="shared" ref="W32:W37" si="0">$B$39*$G$38*$H$38*P32</f>
+        <f t="shared" ref="W32:W37" si="2">$B$39*$G$38*$H$38*P32</f>
         <v>1.9352683896620274E-8</v>
       </c>
       <c r="X32" s="27"/>
@@ -3219,8 +3337,22 @@
         <f>(Y32*AC32)+(Z32*AD32)+(AA32*AE32)</f>
         <v>5.3661361814351366E-9</v>
       </c>
-    </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="AI32">
+        <v>2018.1350301182399</v>
+      </c>
+      <c r="AJ32">
+        <v>1.2300884955752101</v>
+      </c>
+      <c r="AK32">
+        <f t="shared" si="0"/>
+        <v>2018</v>
+      </c>
+      <c r="AL32">
+        <f t="shared" si="1"/>
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2019</v>
       </c>
@@ -3241,11 +3373,11 @@
         <v>1.0286844708209693E-8</v>
       </c>
       <c r="V33" s="36">
-        <f t="shared" ref="V33:V42" si="1">$B$39*$G$36*P33</f>
+        <f t="shared" ref="V33:V42" si="3">$B$39*$G$36*P33</f>
         <v>6.1721068249258155E-9</v>
       </c>
       <c r="W33" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.8516320474777446E-8</v>
       </c>
       <c r="X33" s="27"/>
@@ -3254,11 +3386,11 @@
         <v>6.4292779426310583E-9</v>
       </c>
       <c r="Z33" s="36">
-        <f t="shared" ref="Z33:Z42" si="2">V33/1000/$Z$1</f>
+        <f t="shared" ref="Z33:Z42" si="4">V33/1000/$Z$1</f>
         <v>6.1721068249258161E-10</v>
       </c>
       <c r="AA33" s="36">
-        <f t="shared" ref="AA33:AA42" si="3">W33/1000/$AA$1</f>
+        <f t="shared" ref="AA33:AA42" si="5">W33/1000/$AA$1</f>
         <v>1.8516320474777447E-11</v>
       </c>
       <c r="AB33" s="27"/>
@@ -3275,11 +3407,25 @@
         <v>3.7343167375427193E-3</v>
       </c>
       <c r="AG33" s="36">
-        <f t="shared" ref="AG33:AG42" si="4">(Y33*AC33)+(Z33*AD33)+(AA33*AE33)</f>
+        <f t="shared" ref="AG33:AG42" si="6">(Y33*AC33)+(Z33*AD33)+(AA33*AE33)</f>
         <v>5.3434114050482815E-9</v>
       </c>
-    </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="AI33">
+        <v>2019.12088198111</v>
+      </c>
+      <c r="AJ33">
+        <v>1.24469026548672</v>
+      </c>
+      <c r="AK33">
+        <f t="shared" si="0"/>
+        <v>2019</v>
+      </c>
+      <c r="AL33">
+        <f t="shared" si="1"/>
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2020</v>
       </c>
@@ -3296,28 +3442,28 @@
         <v>73</v>
       </c>
       <c r="U34" s="36">
-        <f t="shared" ref="U34:U42" si="5">$B$39*$G$37*P34</f>
+        <f t="shared" ref="U34:U42" si="7">$B$39*$G$37*P34</f>
         <v>1.8316946659441044E-8</v>
       </c>
       <c r="V34" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.0990167995664626E-8</v>
       </c>
       <c r="W34" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3.2970503986993881E-8</v>
       </c>
       <c r="X34" s="27"/>
       <c r="Y34" s="36">
-        <f t="shared" ref="Y34:Y42" si="6">U34/1000/$Y$1</f>
+        <f t="shared" ref="Y34:Y42" si="8">U34/1000/$Y$1</f>
         <v>1.1448091662150651E-8</v>
       </c>
       <c r="Z34" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.0990167995664627E-9</v>
       </c>
       <c r="AA34" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3.2970503986993881E-11</v>
       </c>
       <c r="AB34" s="27"/>
@@ -3334,11 +3480,25 @@
         <v>7.1361510773210171E-3</v>
       </c>
       <c r="AG34" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>9.5065958395668732E-9</v>
       </c>
-    </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="AI34">
+        <v>2020.24111325946</v>
+      </c>
+      <c r="AJ34">
+        <v>1.24734513274335</v>
+      </c>
+      <c r="AK34">
+        <f t="shared" si="0"/>
+        <v>2020</v>
+      </c>
+      <c r="AL34">
+        <f t="shared" si="1"/>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2021</v>
       </c>
@@ -3368,28 +3528,28 @@
         <v>73</v>
       </c>
       <c r="U35" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2.7236099919419822E-8</v>
       </c>
       <c r="V35" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.6341659951651891E-8</v>
       </c>
       <c r="W35" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4.9024979854955677E-8</v>
       </c>
       <c r="X35" s="27"/>
       <c r="Y35" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.7022562449637387E-8</v>
       </c>
       <c r="Z35" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6341659951651892E-9</v>
       </c>
       <c r="AA35" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4.9024979854955678E-11</v>
       </c>
       <c r="AB35" s="27"/>
@@ -3406,11 +3566,25 @@
         <v>3.8070870635134027E-3</v>
       </c>
       <c r="AG35" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.5031625680352174E-8</v>
       </c>
-    </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="AI35">
+        <v>2021.1704097568199</v>
+      </c>
+      <c r="AJ35">
+        <v>1.25132743362831</v>
+      </c>
+      <c r="AK35">
+        <f t="shared" si="0"/>
+        <v>2021</v>
+      </c>
+      <c r="AL35">
+        <f t="shared" si="1"/>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2022</v>
       </c>
@@ -3449,28 +3623,28 @@
         <v>73</v>
       </c>
       <c r="U36" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>6.6089385474860326E-8</v>
       </c>
       <c r="V36" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.9653631284916192E-8</v>
       </c>
       <c r="W36" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.1896089385474858E-7</v>
       </c>
       <c r="X36" s="27"/>
       <c r="Y36" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>4.13058659217877E-8</v>
       </c>
       <c r="Z36" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.9653631284916193E-9</v>
       </c>
       <c r="AA36" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1.1896089385474859E-10</v>
       </c>
       <c r="AB36" s="27"/>
@@ -3487,11 +3661,25 @@
         <v>3.4344048825351459E-3</v>
       </c>
       <c r="AG36" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3.723590270124415E-8</v>
       </c>
-    </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="AI36">
+        <v>2022.0997062541801</v>
+      </c>
+      <c r="AJ36">
+        <v>1.25530973451326</v>
+      </c>
+      <c r="AK36">
+        <f t="shared" si="0"/>
+        <v>2022</v>
+      </c>
+      <c r="AL36">
+        <f t="shared" si="1"/>
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2023</v>
       </c>
@@ -3530,28 +3718,28 @@
         <v>73</v>
       </c>
       <c r="U37" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1.1387513751375138E-7</v>
       </c>
       <c r="V37" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6.8325082508250822E-8</v>
       </c>
       <c r="W37" s="36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.0497524752475247E-7</v>
       </c>
       <c r="X37" s="27"/>
       <c r="Y37" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>7.1171960946094613E-8</v>
       </c>
       <c r="Z37" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.8325082508250815E-9</v>
       </c>
       <c r="AA37" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.0497524752475247E-10</v>
       </c>
       <c r="AB37" s="27"/>
@@ -3568,11 +3756,25 @@
         <v>9.5944618750836153E-3</v>
       </c>
       <c r="AG37" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6.1887715743716504E-8</v>
       </c>
-    </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="AI37">
+        <v>2023.10972707667</v>
+      </c>
+      <c r="AJ37">
+        <v>1.25265486725663</v>
+      </c>
+      <c r="AK37">
+        <f t="shared" si="0"/>
+        <v>2023</v>
+      </c>
+      <c r="AL37">
+        <f t="shared" si="1"/>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2024</v>
       </c>
@@ -3626,11 +3828,11 @@
         <v>73</v>
       </c>
       <c r="U38" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1.6262852623253359E-7</v>
       </c>
       <c r="V38" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9.7577115739520148E-8</v>
       </c>
       <c r="W38" s="36">
@@ -3639,15 +3841,15 @@
       </c>
       <c r="X38" s="27"/>
       <c r="Y38" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.016428288953335E-7</v>
       </c>
       <c r="Z38" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.7577115739520142E-9</v>
       </c>
       <c r="AA38" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2.9273134721856047E-10</v>
       </c>
       <c r="AB38" s="27"/>
@@ -3661,11 +3863,11 @@
         <v>9.5944618750836153E-3</v>
       </c>
       <c r="AG38" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>8.8383717666933081E-8</v>
       </c>
     </row>
-    <row r="39" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:38" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>2025</v>
       </c>
@@ -3709,28 +3911,28 @@
         <v>73</v>
       </c>
       <c r="U39" s="37">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>2.2211791212917761E-7</v>
       </c>
       <c r="V39" s="37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3327074727750656E-7</v>
       </c>
       <c r="W39" s="36">
-        <f t="shared" ref="W39:W42" si="7">$B$39*$G$38*$H$38*P39</f>
+        <f t="shared" ref="W39:W42" si="9">$B$39*$G$38*$H$38*P39</f>
         <v>3.9981224183251968E-7</v>
       </c>
       <c r="X39" s="35"/>
       <c r="Y39" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.3882369508073601E-7</v>
       </c>
       <c r="Z39" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.3327074727750655E-8</v>
       </c>
       <c r="AA39" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3.9981224183251968E-10</v>
       </c>
       <c r="AB39" s="27"/>
@@ -3744,11 +3946,11 @@
         <v>9.5944618750836153E-3</v>
       </c>
       <c r="AG39" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.207144114822988E-7</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2026</v>
       </c>
@@ -3765,28 +3967,28 @@
         <v>73</v>
       </c>
       <c r="U40" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>3.1044086276368805E-7</v>
       </c>
       <c r="V40" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.8626451765821281E-7</v>
       </c>
       <c r="W40" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>5.5879355297463852E-7</v>
       </c>
       <c r="X40" s="27"/>
       <c r="Y40" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1.9402553922730501E-7</v>
       </c>
       <c r="Z40" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.862645176582128E-8</v>
       </c>
       <c r="AA40" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5.5879355297463856E-10</v>
       </c>
       <c r="AB40" s="27"/>
@@ -3800,11 +4002,11 @@
         <v>9.5944618750836153E-3</v>
       </c>
       <c r="AG40" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.6871528139874396E-7</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2027</v>
       </c>
@@ -3821,28 +4023,28 @@
         <v>73</v>
       </c>
       <c r="U41" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>3.4756765918978473E-7</v>
       </c>
       <c r="V41" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.085405955138708E-7</v>
       </c>
       <c r="W41" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>6.2562178654161249E-7</v>
       </c>
       <c r="X41" s="27"/>
       <c r="Y41" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.1722978699361545E-7</v>
       </c>
       <c r="Z41" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.085405955138708E-8</v>
       </c>
       <c r="AA41" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6.2562178654161252E-10</v>
       </c>
       <c r="AB41" s="27"/>
@@ -3856,11 +4058,11 @@
         <v>9.5944618750836153E-3</v>
       </c>
       <c r="AG41" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1.8889257974374607E-7</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2028</v>
       </c>
@@ -3877,28 +4079,28 @@
         <v>73</v>
       </c>
       <c r="U42" s="36">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>3.9990275526742293E-7</v>
       </c>
       <c r="V42" s="36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.3994165316045375E-7</v>
       </c>
       <c r="W42" s="36">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>7.1982495948136129E-7</v>
       </c>
       <c r="X42" s="27"/>
       <c r="Y42" s="36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2.4993922204213932E-7</v>
       </c>
       <c r="Z42" s="36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.3994165316045373E-8</v>
       </c>
       <c r="AA42" s="36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7.1982495948136124E-10</v>
       </c>
       <c r="AB42" s="27"/>
@@ -3912,11 +4114,11 @@
         <v>9.5944618750836153E-3</v>
       </c>
       <c r="AG42" s="36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2.1733513200043898E-7</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2029</v>
       </c>
@@ -3930,7 +4132,7 @@
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2030</v>
       </c>
@@ -3944,7 +4146,7 @@
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2031</v>
       </c>
@@ -3958,7 +4160,7 @@
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2032</v>
       </c>
@@ -3972,7 +4174,7 @@
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2033</v>
       </c>
@@ -3986,7 +4188,7 @@
         <v>9.5944618750836153E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2034</v>
       </c>
@@ -10666,6 +10868,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <ProcessName xmlns="d382aed9-cc96-421a-b6d1-bad087b40ea5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d382aed9-cc96-421a-b6d1-bad087b40ea5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3c3bb480-5c86-45a4-be90-daa3829a93c5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E1D7978D1E43DE4EA43DBD7340A406DC" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d2a0579b8367a5d14f15657bceede69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d382aed9-cc96-421a-b6d1-bad087b40ea5" xmlns:ns3="3c3bb480-5c86-45a4-be90-daa3829a93c5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6184784662eaf13c68ab2ee7ade41035" ns2:_="" ns3:_="">
     <xsd:import namespace="d382aed9-cc96-421a-b6d1-bad087b40ea5"/>
@@ -10908,28 +11131,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2355CD45-2F25-4965-9590-C756C8D0B153}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3c3bb480-5c86-45a4-be90-daa3829a93c5"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="d382aed9-cc96-421a-b6d1-bad087b40ea5"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ProcessName xmlns="d382aed9-cc96-421a-b6d1-bad087b40ea5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d382aed9-cc96-421a-b6d1-bad087b40ea5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3c3bb480-5c86-45a4-be90-daa3829a93c5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D15763B-BC3F-44A0-B84D-0D65F1925A17}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A8357D9-61C4-4864-BD66-2D2D973EC6D9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10948,31 +11175,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D15763B-BC3F-44A0-B84D-0D65F1925A17}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2355CD45-2F25-4965-9590-C756C8D0B153}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3c3bb480-5c86-45a4-be90-daa3829a93c5"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="d382aed9-cc96-421a-b6d1-bad087b40ea5"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{95965d95-ecc0-4720-b759-1f33c42ed7da}" enabled="1" method="Standard" siteId="{a0f29d7e-28cd-4f54-8442-7885aee7c080}" removed="0"/>
